--- a/main.xlsx
+++ b/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBCCA23-7016-9F41-B894-3F14A3CEFC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16DEBDC-FC2C-D64F-B45B-A2E9525ECC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="28300" windowHeight="16940" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>年齢（歳）</t>
   </si>
@@ -147,41 +147,18 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>4W前退院</t>
-    <rPh sb="2" eb="5">
-      <t>マエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+    <t>PCS_sum_pre</t>
   </si>
   <si>
-    <t>25日</t>
-    <rPh sb="2" eb="3">
-      <t>ニティ</t>
+    <t>術後評価実施日</t>
+    <rPh sb="0" eb="2">
+      <t>ジュテゥ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>24日</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>24日</t>
-    <rPh sb="2" eb="3">
-      <t xml:space="preserve">ヒ </t>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>22日</t>
-    <rPh sb="2" eb="3">
-      <t>ニティ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>39日</t>
-    <rPh sb="2" eb="3">
-      <t>ニティ</t>
+    <rPh sb="4" eb="7">
+      <t>z</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -190,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -235,6 +212,14 @@
       <color rgb="FF000000"/>
       <name val="Hiragino Kaku Gothic ProN"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -244,12 +229,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -258,7 +258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -277,6 +277,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -591,30 +595,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:V526"/>
+  <dimension ref="A1:W526"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="2" max="3" width="15.7109375" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
-    <col min="15" max="15" width="22.42578125" customWidth="1"/>
-    <col min="16" max="16" width="23.7109375" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
-    <col min="18" max="19" width="22.42578125" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="18.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.42578125" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="18" max="18" width="24" customWidth="1"/>
+    <col min="19" max="20" width="22.42578125" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
-        <v>30</v>
+      <c r="C1" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -634,53 +639,56 @@
       <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="2">
         <v>110993</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>35</v>
+      <c r="C2" s="7">
+        <v>39</v>
       </c>
       <c r="D2" s="2">
         <v>74</v>
@@ -701,50 +709,56 @@
         <v>8.75</v>
       </c>
       <c r="J2" s="2">
+        <v>28</v>
+      </c>
+      <c r="K2" s="2">
         <v>18</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>124</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>9.2200000000000006</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>125</v>
       </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
       <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <v>125</v>
       </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
       <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
         <v>23</v>
       </c>
-      <c r="R2" s="2">
+      <c r="S2" s="2">
         <v>32</v>
       </c>
-      <c r="S2" s="2">
+      <c r="T2" s="2">
         <v>58</v>
       </c>
-      <c r="T2" s="2">
+      <c r="U2" s="2">
         <v>3</v>
       </c>
-      <c r="U2" s="2">
+      <c r="V2" s="2">
         <v>11</v>
       </c>
-      <c r="V2" s="1"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="2">
         <v>508469</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3" s="7">
+        <v>29</v>
+      </c>
       <c r="D3" s="2">
         <v>86</v>
       </c>
@@ -764,50 +778,56 @@
         <v>14.03</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
         <v>131</v>
       </c>
-      <c r="L3" s="2">
+      <c r="M3" s="2">
         <v>16.170000000000002</v>
       </c>
-      <c r="M3" s="2">
+      <c r="N3" s="2">
         <v>135</v>
       </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
       <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
         <v>120</v>
       </c>
-      <c r="P3" s="2">
+      <c r="Q3" s="2">
         <v>-10</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>25</v>
       </c>
-      <c r="R3" s="2">
+      <c r="S3" s="2">
         <v>40</v>
       </c>
-      <c r="S3" s="2">
+      <c r="T3" s="2">
         <v>56</v>
       </c>
-      <c r="T3" s="2">
+      <c r="U3" s="2">
         <v>11</v>
       </c>
-      <c r="U3" s="2">
+      <c r="V3" s="2">
         <v>10</v>
       </c>
-      <c r="V3" s="1"/>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3" s="1"/>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="2">
         <v>910870</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="C4" s="7">
+        <v>31</v>
+      </c>
       <c r="D4" s="2">
         <v>73</v>
       </c>
@@ -827,50 +847,56 @@
         <v>9.1</v>
       </c>
       <c r="J4" s="2">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2">
         <v>17</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <v>111</v>
       </c>
-      <c r="L4" s="2">
+      <c r="M4" s="2">
         <v>9.1</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <v>120</v>
       </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
       <c r="O4" s="2">
+        <v>0</v>
+      </c>
+      <c r="P4" s="2">
         <v>130</v>
       </c>
-      <c r="P4" s="2">
+      <c r="Q4" s="2">
         <v>-10</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>21</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>18</v>
       </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>62</v>
-      </c>
-      <c r="T4" s="2">
-        <v>10</v>
       </c>
       <c r="U4" s="2">
         <v>10</v>
       </c>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="V4" s="2">
+        <v>10</v>
+      </c>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="2">
         <v>1400396</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="C5" s="7">
+        <v>29</v>
+      </c>
       <c r="D5" s="2">
         <v>69</v>
       </c>
@@ -890,50 +916,56 @@
         <v>10.55</v>
       </c>
       <c r="J5" s="2">
+        <v>33</v>
+      </c>
+      <c r="K5" s="2">
         <v>15</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>113</v>
       </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2">
         <v>10.55</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>125</v>
       </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
       <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
         <v>145</v>
       </c>
-      <c r="P5" s="2">
+      <c r="Q5" s="2">
         <v>-5</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>15</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>20</v>
       </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>63</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>14</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>15</v>
       </c>
-      <c r="V5" s="2"/>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="2">
         <v>1403057</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
+      <c r="C6" s="7">
+        <v>29</v>
+      </c>
       <c r="D6" s="2">
         <v>79</v>
       </c>
@@ -953,50 +985,56 @@
         <v>18.350000000000001</v>
       </c>
       <c r="J6" s="2">
+        <v>29</v>
+      </c>
+      <c r="K6" s="2">
         <v>11</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="2">
         <v>123</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>18.03</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>110</v>
       </c>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
       <c r="O6" s="2">
+        <v>0</v>
+      </c>
+      <c r="P6" s="2">
         <v>70</v>
       </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
         <v>-30</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>23</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>32</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>58</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>12</v>
       </c>
-      <c r="U6" s="2">
+      <c r="V6" s="2">
         <v>10</v>
       </c>
-      <c r="V6" s="2"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="2">
         <v>1501605</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
+      <c r="C7" s="7">
+        <v>29</v>
+      </c>
       <c r="D7" s="2">
         <v>80</v>
       </c>
@@ -1016,50 +1054,56 @@
         <v>27.25</v>
       </c>
       <c r="J7" s="2">
+        <v>38</v>
+      </c>
+      <c r="K7" s="2">
         <v>34</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>62</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>27.25</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>120</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>-5</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>120</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>-10</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>14</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>12</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>26</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>13</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>10</v>
       </c>
-      <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="2">
         <v>1900753</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
+      <c r="C8" s="7">
+        <v>29</v>
+      </c>
       <c r="D8" s="2">
         <v>65</v>
       </c>
@@ -1079,50 +1123,56 @@
         <v>9.1300000000000008</v>
       </c>
       <c r="J8" s="2">
+        <v>28</v>
+      </c>
+      <c r="K8" s="2">
         <v>19</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>119</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>9.1300000000000008</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>90</v>
       </c>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
       <c r="O8" s="2">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
         <v>110</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>-5</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>19</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>22</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>72</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>15</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>6</v>
       </c>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="2">
         <v>1902085</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
+      <c r="C9" s="7">
+        <v>28</v>
+      </c>
       <c r="D9" s="2">
         <v>75</v>
       </c>
@@ -1145,47 +1195,53 @@
         <v>22</v>
       </c>
       <c r="K9" s="2">
+        <v>22</v>
+      </c>
+      <c r="L9" s="2">
         <v>138</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>8.0399999999999991</v>
       </c>
-      <c r="M9" s="2">
+      <c r="N9" s="2">
         <v>125</v>
       </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
       <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
         <v>120</v>
       </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2">
         <v>-5</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>22</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>28</v>
       </c>
-      <c r="S9" s="2">
+      <c r="T9" s="2">
         <v>79</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>12</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>9</v>
       </c>
-      <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" s="2">
         <v>1902300</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
+      <c r="C10" s="7">
+        <v>29</v>
+      </c>
       <c r="D10" s="2">
         <v>75</v>
       </c>
@@ -1205,50 +1261,56 @@
         <v>13.24</v>
       </c>
       <c r="J10" s="2">
+        <v>14</v>
+      </c>
+      <c r="K10" s="2">
         <v>15</v>
       </c>
-      <c r="K10" s="2">
+      <c r="L10" s="2">
         <v>81</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>13.24</v>
       </c>
-      <c r="M10" s="2">
+      <c r="N10" s="2">
         <v>120</v>
       </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
       <c r="O10" s="2">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
         <v>120</v>
       </c>
-      <c r="P10" s="2">
+      <c r="Q10" s="2">
         <v>-10</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>22</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <v>16</v>
       </c>
-      <c r="S10" s="2">
+      <c r="T10" s="2">
         <v>34</v>
       </c>
-      <c r="T10" s="2">
+      <c r="U10" s="2">
         <v>14</v>
       </c>
-      <c r="U10" s="2">
+      <c r="V10" s="2">
         <v>9</v>
       </c>
-      <c r="V10" s="2"/>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="2">
         <v>1905031</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
+      <c r="C11" s="7">
+        <v>29</v>
+      </c>
       <c r="D11" s="2">
         <v>75</v>
       </c>
@@ -1268,50 +1330,56 @@
         <v>11.05</v>
       </c>
       <c r="J11" s="2">
+        <v>30</v>
+      </c>
+      <c r="K11" s="2">
         <v>31</v>
       </c>
-      <c r="K11" s="2">
+      <c r="L11" s="2">
         <v>125</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>11.05</v>
       </c>
-      <c r="M11" s="2">
+      <c r="N11" s="2">
         <v>115</v>
       </c>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
       <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
         <v>120</v>
       </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
       <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
         <v>20</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
         <v>28</v>
       </c>
-      <c r="S11" s="2">
+      <c r="T11" s="2">
         <v>66</v>
       </c>
-      <c r="T11" s="2">
+      <c r="U11" s="2">
         <v>10</v>
       </c>
-      <c r="U11" s="2">
+      <c r="V11" s="2">
         <v>11</v>
       </c>
-      <c r="V11" s="2"/>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="2">
         <v>2001975</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
+      <c r="C12" s="7">
+        <v>29</v>
+      </c>
       <c r="D12" s="2">
         <v>60</v>
       </c>
@@ -1331,50 +1399,56 @@
         <v>9.48</v>
       </c>
       <c r="J12" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" s="2">
         <v>7</v>
       </c>
-      <c r="K12" s="2">
+      <c r="L12" s="2">
         <v>130</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>9.48</v>
       </c>
-      <c r="M12" s="2">
+      <c r="N12" s="2">
         <v>125</v>
       </c>
-      <c r="N12" s="2">
-        <v>0</v>
-      </c>
       <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
         <v>105</v>
       </c>
-      <c r="P12" s="2">
+      <c r="Q12" s="2">
         <v>-15</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="R12" s="2">
         <v>22</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="2">
         <v>28</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <v>71</v>
       </c>
-      <c r="T12" s="2">
+      <c r="U12" s="2">
         <v>14</v>
       </c>
-      <c r="U12" s="2">
+      <c r="V12" s="2">
         <v>9</v>
       </c>
-      <c r="V12" s="2"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="2">
         <v>2002759</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
+      <c r="C13" s="7">
+        <v>32</v>
+      </c>
       <c r="D13" s="2">
         <v>69</v>
       </c>
@@ -1394,50 +1468,56 @@
         <v>35.83</v>
       </c>
       <c r="J13" s="2">
+        <v>25</v>
+      </c>
+      <c r="K13" s="2">
         <v>18</v>
       </c>
-      <c r="K13" s="2">
+      <c r="L13" s="2">
         <v>61</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M13" s="2">
         <v>32.07</v>
       </c>
-      <c r="M13" s="2">
+      <c r="N13" s="2">
         <v>100</v>
       </c>
-      <c r="N13" s="2">
+      <c r="O13" s="2">
         <v>-10</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>80</v>
       </c>
-      <c r="P13" s="2">
+      <c r="Q13" s="2">
         <v>-10</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="R13" s="2">
         <v>9</v>
       </c>
-      <c r="R13" s="2">
+      <c r="S13" s="2">
         <v>10</v>
       </c>
-      <c r="S13" s="2">
+      <c r="T13" s="2">
         <v>36</v>
       </c>
-      <c r="T13" s="2">
+      <c r="U13" s="2">
         <v>14</v>
       </c>
-      <c r="U13" s="2">
+      <c r="V13" s="2">
         <v>6</v>
       </c>
-      <c r="V13" s="2"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="2">
         <v>2003119</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
+      <c r="C14" s="7">
+        <v>29</v>
+      </c>
       <c r="D14" s="2">
         <v>69</v>
       </c>
@@ -1457,50 +1537,56 @@
         <v>8.59</v>
       </c>
       <c r="J14" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
         <v>114</v>
       </c>
-      <c r="L14" s="2">
+      <c r="M14" s="2">
         <v>8.89</v>
       </c>
-      <c r="M14" s="2">
+      <c r="N14" s="2">
         <v>120</v>
       </c>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
       <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
         <v>125</v>
       </c>
-      <c r="P14" s="2">
+      <c r="Q14" s="2">
         <v>-10</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="R14" s="2">
         <v>22</v>
       </c>
-      <c r="R14" s="2">
+      <c r="S14" s="2">
         <v>30</v>
       </c>
-      <c r="S14" s="2">
+      <c r="T14" s="2">
         <v>53</v>
       </c>
-      <c r="T14" s="2">
+      <c r="U14" s="2">
         <v>14</v>
       </c>
-      <c r="U14" s="2">
+      <c r="V14" s="2">
         <v>9</v>
       </c>
-      <c r="V14" s="2"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="2">
         <v>2003509</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
+      <c r="C15" s="7">
+        <v>28</v>
+      </c>
       <c r="D15" s="2">
         <v>67</v>
       </c>
@@ -1520,50 +1606,56 @@
         <v>9.39</v>
       </c>
       <c r="J15" s="2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
         <v>114</v>
       </c>
-      <c r="L15" s="2">
+      <c r="M15" s="2">
         <v>9.39</v>
       </c>
-      <c r="M15" s="2">
+      <c r="N15" s="2">
         <v>125</v>
       </c>
-      <c r="N15" s="2">
-        <v>0</v>
-      </c>
       <c r="O15" s="2">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2">
         <v>130</v>
       </c>
-      <c r="P15" s="2">
+      <c r="Q15" s="2">
         <v>5</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="R15" s="2">
         <v>20</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S15" s="2">
         <v>30</v>
       </c>
-      <c r="S15" s="2">
+      <c r="T15" s="2">
         <v>55</v>
       </c>
-      <c r="T15" s="2">
+      <c r="U15" s="2">
         <v>10</v>
       </c>
-      <c r="U15" s="2">
+      <c r="V15" s="2">
         <v>9</v>
       </c>
-      <c r="V15" s="2"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="2">
         <v>2003509</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
+      <c r="C16" s="7">
+        <v>28</v>
+      </c>
       <c r="D16" s="2">
         <v>67</v>
       </c>
@@ -1583,52 +1675,55 @@
         <v>10.42</v>
       </c>
       <c r="J16" s="2">
+        <v>49</v>
+      </c>
+      <c r="K16" s="2">
         <v>7</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="2">
         <v>128</v>
       </c>
-      <c r="L16" s="2">
+      <c r="M16" s="2">
         <v>8.7200000000000006</v>
       </c>
-      <c r="M16" s="2">
+      <c r="N16" s="2">
         <v>130</v>
       </c>
-      <c r="N16" s="2">
-        <v>0</v>
-      </c>
       <c r="O16" s="2">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
         <v>140</v>
       </c>
-      <c r="P16" s="2">
+      <c r="Q16" s="2">
         <v>10</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="R16" s="2">
         <v>24</v>
       </c>
-      <c r="R16" s="2">
+      <c r="S16" s="2">
         <v>40</v>
       </c>
-      <c r="S16" s="2">
+      <c r="T16" s="2">
         <v>55</v>
       </c>
-      <c r="T16" s="2">
+      <c r="U16" s="2">
         <v>11</v>
       </c>
-      <c r="U16" s="2">
+      <c r="V16" s="2">
         <v>9</v>
       </c>
-      <c r="V16" s="2"/>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="2">
         <v>2003643</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
-        <v>31</v>
+      <c r="C17" s="7">
+        <v>25</v>
       </c>
       <c r="D17" s="2">
         <v>78</v>
@@ -1649,50 +1744,56 @@
         <v>10.17</v>
       </c>
       <c r="J17" s="2">
+        <v>28</v>
+      </c>
+      <c r="K17" s="2">
         <v>12</v>
       </c>
-      <c r="K17" s="2">
+      <c r="L17" s="2">
         <v>120</v>
       </c>
-      <c r="L17" s="2">
+      <c r="M17" s="2">
         <v>11.2</v>
       </c>
-      <c r="M17" s="2">
+      <c r="N17" s="2">
         <v>130</v>
       </c>
-      <c r="N17" s="2">
-        <v>0</v>
-      </c>
       <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
         <v>130</v>
       </c>
-      <c r="P17" s="2">
+      <c r="Q17" s="2">
         <v>-10</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="R17" s="2">
         <v>17</v>
       </c>
-      <c r="R17" s="2">
+      <c r="S17" s="2">
         <v>24</v>
       </c>
-      <c r="S17" s="2">
+      <c r="T17" s="2">
         <v>69</v>
       </c>
-      <c r="T17" s="2">
+      <c r="U17" s="2">
         <v>15</v>
       </c>
-      <c r="U17" s="2">
+      <c r="V17" s="2">
         <v>10</v>
       </c>
-      <c r="V17" s="2"/>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="2">
         <v>2004241</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
+      <c r="C18" s="7">
+        <v>28</v>
+      </c>
       <c r="D18" s="2">
         <v>81</v>
       </c>
@@ -1712,50 +1813,56 @@
         <v>15.04</v>
       </c>
       <c r="J18" s="2">
+        <v>35</v>
+      </c>
+      <c r="K18" s="2">
         <v>25</v>
       </c>
-      <c r="K18" s="2">
+      <c r="L18" s="2">
         <v>99</v>
       </c>
-      <c r="L18" s="2">
+      <c r="M18" s="2">
         <v>15.04</v>
       </c>
-      <c r="M18" s="2">
+      <c r="N18" s="2">
         <v>130</v>
       </c>
-      <c r="N18" s="2">
-        <v>0</v>
-      </c>
       <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
         <v>125</v>
       </c>
-      <c r="P18" s="2">
+      <c r="Q18" s="2">
         <v>-10</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="R18" s="2">
         <v>23</v>
       </c>
-      <c r="R18" s="2">
+      <c r="S18" s="2">
         <v>26</v>
       </c>
-      <c r="S18" s="2">
+      <c r="T18" s="2">
         <v>40</v>
       </c>
-      <c r="T18" s="2">
+      <c r="U18" s="2">
         <v>13</v>
       </c>
-      <c r="U18" s="2">
+      <c r="V18" s="2">
         <v>10</v>
       </c>
-      <c r="V18" s="2"/>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="2">
         <v>2004528</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
+      <c r="C19" s="7">
+        <v>32</v>
+      </c>
       <c r="D19" s="2">
         <v>70</v>
       </c>
@@ -1775,50 +1882,56 @@
         <v>8.9</v>
       </c>
       <c r="J19" s="2">
+        <v>44</v>
+      </c>
+      <c r="K19" s="2">
         <v>25</v>
       </c>
-      <c r="K19" s="2">
+      <c r="L19" s="2">
         <v>129</v>
       </c>
-      <c r="L19" s="2">
+      <c r="M19" s="2">
         <v>8.9</v>
       </c>
-      <c r="M19" s="2">
+      <c r="N19" s="2">
         <v>125</v>
       </c>
-      <c r="N19" s="2">
-        <v>0</v>
-      </c>
       <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
         <v>110</v>
       </c>
-      <c r="P19" s="2">
+      <c r="Q19" s="2">
         <v>-20</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="R19" s="2">
         <v>17</v>
       </c>
-      <c r="R19" s="2">
+      <c r="S19" s="2">
         <v>28</v>
       </c>
-      <c r="S19" s="2">
+      <c r="T19" s="2">
         <v>74</v>
       </c>
-      <c r="T19" s="2">
+      <c r="U19" s="2">
         <v>15</v>
       </c>
-      <c r="U19" s="2">
+      <c r="V19" s="2">
         <v>10</v>
       </c>
-      <c r="V19" s="2"/>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="2">
         <v>2101216</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
+      <c r="C20" s="7">
+        <v>30</v>
+      </c>
       <c r="D20" s="2">
         <v>74</v>
       </c>
@@ -1838,50 +1951,56 @@
         <v>6</v>
       </c>
       <c r="J20" s="2">
+        <v>22</v>
+      </c>
+      <c r="K20" s="2">
         <v>16</v>
       </c>
-      <c r="K20" s="2">
+      <c r="L20" s="2">
         <v>109</v>
       </c>
-      <c r="L20" s="2">
+      <c r="M20" s="2">
         <v>11.59</v>
       </c>
-      <c r="M20" s="2">
+      <c r="N20" s="2">
         <v>115</v>
       </c>
-      <c r="N20" s="2">
+      <c r="O20" s="2">
         <v>-10</v>
       </c>
-      <c r="O20" s="2">
+      <c r="P20" s="2">
         <v>100</v>
       </c>
-      <c r="P20" s="2">
+      <c r="Q20" s="2">
         <v>-25</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="R20" s="2">
         <v>18</v>
       </c>
-      <c r="R20" s="2">
+      <c r="S20" s="2">
         <v>20</v>
       </c>
-      <c r="S20" s="2">
+      <c r="T20" s="2">
         <v>62</v>
       </c>
-      <c r="T20" s="2">
+      <c r="U20" s="2">
         <v>13</v>
       </c>
-      <c r="U20" s="2">
+      <c r="V20" s="2">
         <v>9</v>
       </c>
-      <c r="V20" s="2"/>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="2">
         <v>2101383</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
+      <c r="C21" s="7">
+        <v>29</v>
+      </c>
       <c r="D21" s="2">
         <v>68</v>
       </c>
@@ -1901,50 +2020,56 @@
         <v>9.89</v>
       </c>
       <c r="J21" s="2">
+        <v>29</v>
+      </c>
+      <c r="K21" s="2">
         <v>24</v>
       </c>
-      <c r="K21" s="2">
+      <c r="L21" s="2">
         <v>127</v>
       </c>
-      <c r="L21" s="2">
+      <c r="M21" s="2">
         <v>9.9</v>
       </c>
-      <c r="M21" s="2">
+      <c r="N21" s="2">
         <v>120</v>
       </c>
-      <c r="N21" s="2">
-        <v>0</v>
-      </c>
       <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
         <v>120</v>
       </c>
-      <c r="P21" s="2">
+      <c r="Q21" s="2">
         <v>-5</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="R21" s="2">
         <v>17</v>
       </c>
-      <c r="R21" s="2">
+      <c r="S21" s="2">
         <v>24</v>
       </c>
-      <c r="S21" s="2">
+      <c r="T21" s="2">
         <v>72</v>
       </c>
-      <c r="T21" s="2">
+      <c r="U21" s="2">
         <v>10</v>
       </c>
-      <c r="U21" s="2">
+      <c r="V21" s="2">
         <v>14</v>
       </c>
-      <c r="V21" s="2"/>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="2">
         <v>2101501</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
+      <c r="C22" s="7">
+        <v>32</v>
+      </c>
       <c r="D22" s="2">
         <v>74</v>
       </c>
@@ -1964,50 +2089,56 @@
         <v>9.31</v>
       </c>
       <c r="J22" s="2">
+        <v>39</v>
+      </c>
+      <c r="K22" s="2">
         <v>16</v>
       </c>
-      <c r="K22" s="2">
+      <c r="L22" s="2">
         <v>109</v>
       </c>
-      <c r="L22" s="2">
+      <c r="M22" s="2">
         <v>10.31</v>
       </c>
-      <c r="M22" s="2">
+      <c r="N22" s="2">
         <v>120</v>
       </c>
-      <c r="N22" s="2">
-        <v>0</v>
-      </c>
       <c r="O22" s="2">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2">
         <v>130</v>
       </c>
-      <c r="P22" s="2">
+      <c r="Q22" s="2">
         <v>-5</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="R22" s="2">
         <v>17</v>
       </c>
-      <c r="R22" s="2">
+      <c r="S22" s="2">
         <v>16</v>
       </c>
-      <c r="S22" s="2">
+      <c r="T22" s="2">
         <v>67</v>
       </c>
-      <c r="T22" s="2">
+      <c r="U22" s="2">
         <v>15</v>
       </c>
-      <c r="U22" s="2">
+      <c r="V22" s="2">
         <v>9</v>
       </c>
-      <c r="V22" s="2"/>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="2">
         <v>2101972</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
+      <c r="C23" s="7">
+        <v>28</v>
+      </c>
       <c r="D23" s="2">
         <v>68</v>
       </c>
@@ -2027,50 +2158,56 @@
         <v>8.39</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
         <v>139</v>
       </c>
-      <c r="L23" s="2">
+      <c r="M23" s="2">
         <v>9.0500000000000007</v>
       </c>
-      <c r="M23" s="2">
+      <c r="N23" s="2">
         <v>120</v>
       </c>
-      <c r="N23" s="2">
-        <v>0</v>
-      </c>
       <c r="O23" s="2">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2">
         <v>125</v>
       </c>
-      <c r="P23" s="2">
-        <v>0</v>
-      </c>
       <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
         <v>25</v>
       </c>
-      <c r="R23" s="2">
+      <c r="S23" s="2">
         <v>36</v>
       </c>
-      <c r="S23" s="2">
+      <c r="T23" s="2">
         <v>69</v>
       </c>
-      <c r="T23" s="2">
+      <c r="U23" s="2">
         <v>13</v>
       </c>
-      <c r="U23" s="2">
+      <c r="V23" s="2">
         <v>9</v>
       </c>
-      <c r="V23" s="2"/>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24" s="2">
         <v>2103619</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
+      <c r="C24" s="7">
+        <v>29</v>
+      </c>
       <c r="D24" s="2">
         <v>82</v>
       </c>
@@ -2090,52 +2227,55 @@
         <v>19.46</v>
       </c>
       <c r="J24" s="2">
+        <v>48</v>
+      </c>
+      <c r="K24" s="2">
         <v>2</v>
       </c>
-      <c r="K24" s="2">
+      <c r="L24" s="2">
         <v>100</v>
       </c>
-      <c r="L24" s="2">
+      <c r="M24" s="2">
         <v>19.46</v>
       </c>
-      <c r="M24" s="2">
+      <c r="N24" s="2">
         <v>125</v>
       </c>
-      <c r="N24" s="2">
-        <v>0</v>
-      </c>
       <c r="O24" s="2">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2">
         <v>125</v>
       </c>
-      <c r="P24" s="2">
+      <c r="Q24" s="2">
         <v>-5</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="R24" s="2">
         <v>23</v>
       </c>
-      <c r="R24" s="2">
+      <c r="S24" s="2">
         <v>36</v>
       </c>
-      <c r="S24" s="2">
+      <c r="T24" s="2">
         <v>32</v>
       </c>
-      <c r="T24" s="2">
+      <c r="U24" s="2">
         <v>14</v>
       </c>
-      <c r="U24" s="2">
+      <c r="V24" s="2">
         <v>9</v>
       </c>
-      <c r="V24" s="2"/>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="W24" s="2"/>
+    </row>
+    <row r="25" spans="1:23">
       <c r="A25" s="2">
         <v>2201384</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" t="s">
-        <v>31</v>
+      <c r="C25" s="7">
+        <v>25</v>
       </c>
       <c r="D25" s="2">
         <v>76</v>
@@ -2156,50 +2296,56 @@
         <v>7</v>
       </c>
       <c r="J25" s="2">
+        <v>28</v>
+      </c>
+      <c r="K25" s="2">
         <v>13</v>
       </c>
-      <c r="K25" s="2">
+      <c r="L25" s="2">
         <v>126</v>
       </c>
-      <c r="L25" s="2">
+      <c r="M25" s="2">
         <v>10.3</v>
       </c>
-      <c r="M25" s="2">
+      <c r="N25" s="2">
         <v>130</v>
       </c>
-      <c r="N25" s="2">
-        <v>0</v>
-      </c>
       <c r="O25" s="2">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2">
         <v>130</v>
       </c>
-      <c r="P25" s="2">
-        <v>0</v>
-      </c>
       <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2">
         <v>21</v>
       </c>
-      <c r="R25" s="2">
+      <c r="S25" s="2">
         <v>30</v>
       </c>
-      <c r="S25" s="2">
+      <c r="T25" s="2">
         <v>66</v>
       </c>
-      <c r="T25" s="2">
+      <c r="U25" s="2">
         <v>12</v>
       </c>
-      <c r="U25" s="2">
+      <c r="V25" s="2">
         <v>9</v>
       </c>
-      <c r="V25" s="2"/>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="W25" s="2"/>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26" s="2">
         <v>2201884</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
+      <c r="C26" s="7">
+        <v>29</v>
+      </c>
       <c r="D26" s="2">
         <v>67</v>
       </c>
@@ -2219,52 +2365,55 @@
         <v>8.77</v>
       </c>
       <c r="J26" s="2">
+        <v>17</v>
+      </c>
+      <c r="K26" s="2">
         <v>7</v>
       </c>
-      <c r="K26" s="2">
+      <c r="L26" s="2">
         <v>132</v>
       </c>
-      <c r="L26" s="2">
+      <c r="M26" s="2">
         <v>8.77</v>
       </c>
-      <c r="M26" s="2">
+      <c r="N26" s="2">
         <v>120</v>
       </c>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
       <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
         <v>125</v>
       </c>
-      <c r="P26" s="2">
+      <c r="Q26" s="2">
         <v>-15</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="R26" s="2">
         <v>18</v>
       </c>
-      <c r="R26" s="2">
+      <c r="S26" s="2">
         <v>26</v>
       </c>
-      <c r="S26" s="2">
+      <c r="T26" s="2">
         <v>79</v>
       </c>
-      <c r="T26" s="2">
+      <c r="U26" s="2">
         <v>15</v>
       </c>
-      <c r="U26" s="2">
+      <c r="V26" s="2">
         <v>9</v>
       </c>
-      <c r="V26" s="2"/>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="W26" s="2"/>
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27" s="2">
         <v>2202167</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" t="s">
-        <v>32</v>
+      <c r="C27" s="7">
+        <v>24</v>
       </c>
       <c r="D27" s="2">
         <v>75</v>
@@ -2285,50 +2434,56 @@
         <v>10.24</v>
       </c>
       <c r="J27" s="2">
+        <v>32</v>
+      </c>
+      <c r="K27" s="2">
         <v>17</v>
       </c>
-      <c r="K27" s="2">
+      <c r="L27" s="2">
         <v>131</v>
       </c>
-      <c r="L27" s="2">
+      <c r="M27" s="2">
         <v>10.69</v>
       </c>
-      <c r="M27" s="2">
+      <c r="N27" s="2">
         <v>130</v>
       </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
       <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
         <v>110</v>
       </c>
-      <c r="P27" s="2">
+      <c r="Q27" s="2">
         <v>-5</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="R27" s="2">
         <v>21</v>
       </c>
-      <c r="R27" s="2">
+      <c r="S27" s="2">
         <v>26</v>
       </c>
-      <c r="S27" s="2">
+      <c r="T27" s="2">
         <v>69</v>
-      </c>
-      <c r="T27" s="2">
-        <v>15</v>
       </c>
       <c r="U27" s="2">
         <v>15</v>
       </c>
-      <c r="V27" s="2"/>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="V27" s="2">
+        <v>15</v>
+      </c>
+      <c r="W27" s="2"/>
+    </row>
+    <row r="28" spans="1:23">
       <c r="A28" s="2">
         <v>2202692</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
+      <c r="C28" s="7">
+        <v>29</v>
+      </c>
       <c r="D28" s="2">
         <v>84</v>
       </c>
@@ -2348,50 +2503,56 @@
         <v>10.39</v>
       </c>
       <c r="J28" s="2">
+        <v>25</v>
+      </c>
+      <c r="K28" s="2">
         <v>18</v>
       </c>
-      <c r="K28" s="2">
+      <c r="L28" s="2">
         <v>138</v>
       </c>
-      <c r="L28" s="2">
+      <c r="M28" s="2">
         <v>10.35</v>
       </c>
-      <c r="M28" s="2">
+      <c r="N28" s="2">
         <v>125</v>
       </c>
-      <c r="N28" s="2">
-        <v>0</v>
-      </c>
       <c r="O28" s="2">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2">
         <v>110</v>
       </c>
-      <c r="P28" s="2">
-        <v>0</v>
-      </c>
       <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2">
         <v>23</v>
       </c>
-      <c r="R28" s="2">
+      <c r="S28" s="2">
         <v>32</v>
       </c>
-      <c r="S28" s="2">
+      <c r="T28" s="2">
         <v>69</v>
       </c>
-      <c r="T28" s="2">
+      <c r="U28" s="2">
         <v>15</v>
       </c>
-      <c r="U28" s="2">
+      <c r="V28" s="2">
         <v>14</v>
       </c>
-      <c r="V28" s="2"/>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="W28" s="2"/>
+    </row>
+    <row r="29" spans="1:23">
       <c r="A29" s="2">
         <v>2203257</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
+      <c r="C29" s="7">
+        <v>29</v>
+      </c>
       <c r="D29" s="2">
         <v>74</v>
       </c>
@@ -2411,50 +2572,56 @@
         <v>8</v>
       </c>
       <c r="J29" s="2">
+        <v>31</v>
+      </c>
+      <c r="K29" s="2">
         <v>4</v>
       </c>
-      <c r="K29" s="2">
+      <c r="L29" s="2">
         <v>142</v>
       </c>
-      <c r="L29" s="2">
+      <c r="M29" s="2">
         <v>9.59</v>
       </c>
-      <c r="M29" s="2">
+      <c r="N29" s="2">
         <v>125</v>
       </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
       <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
         <v>105</v>
       </c>
-      <c r="P29" s="2">
+      <c r="Q29" s="2">
         <v>-10</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="R29" s="2">
         <v>23</v>
       </c>
-      <c r="R29" s="2">
+      <c r="S29" s="2">
         <v>38</v>
       </c>
-      <c r="S29" s="2">
+      <c r="T29" s="2">
         <v>72</v>
       </c>
-      <c r="T29" s="2">
+      <c r="U29" s="2">
         <v>14</v>
       </c>
-      <c r="U29" s="2">
+      <c r="V29" s="2">
         <v>9</v>
       </c>
-      <c r="V29" s="2"/>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29" s="2"/>
+    </row>
+    <row r="30" spans="1:23">
       <c r="A30" s="2">
         <v>2203370</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
+      <c r="C30" s="7">
+        <v>31</v>
+      </c>
       <c r="D30" s="2">
         <v>69</v>
       </c>
@@ -2477,47 +2644,53 @@
         <v>34</v>
       </c>
       <c r="K30" s="2">
+        <v>34</v>
+      </c>
+      <c r="L30" s="2">
         <v>65</v>
       </c>
-      <c r="L30" s="2">
+      <c r="M30" s="2">
         <v>13.29</v>
       </c>
-      <c r="M30" s="2">
+      <c r="N30" s="2">
         <v>115</v>
       </c>
-      <c r="N30" s="2">
+      <c r="O30" s="2">
         <v>-5</v>
       </c>
-      <c r="O30" s="2">
+      <c r="P30" s="2">
         <v>120</v>
       </c>
-      <c r="P30" s="2">
+      <c r="Q30" s="2">
         <v>-15</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="R30" s="2">
         <v>12</v>
       </c>
-      <c r="R30" s="2">
+      <c r="S30" s="2">
         <v>14</v>
       </c>
-      <c r="S30" s="2">
+      <c r="T30" s="2">
         <v>28</v>
       </c>
-      <c r="T30" s="2">
+      <c r="U30" s="2">
         <v>15</v>
       </c>
-      <c r="U30" s="2">
+      <c r="V30" s="2">
         <v>11</v>
       </c>
-      <c r="V30" s="2"/>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="W30" s="2"/>
+    </row>
+    <row r="31" spans="1:23">
       <c r="A31" s="2">
         <v>2204023</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
+      <c r="C31" s="7">
+        <v>29</v>
+      </c>
       <c r="D31" s="2">
         <v>77</v>
       </c>
@@ -2537,50 +2710,56 @@
         <v>9</v>
       </c>
       <c r="J31" s="2">
+        <v>38</v>
+      </c>
+      <c r="K31" s="2">
         <v>15</v>
       </c>
-      <c r="K31" s="2">
+      <c r="L31" s="2">
         <v>121</v>
       </c>
-      <c r="L31" s="2">
+      <c r="M31" s="2">
         <v>10.94</v>
       </c>
-      <c r="M31" s="2">
+      <c r="N31" s="2">
         <v>125</v>
       </c>
-      <c r="N31" s="2">
-        <v>0</v>
-      </c>
       <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
         <v>115</v>
       </c>
-      <c r="P31" s="2">
+      <c r="Q31" s="2">
         <v>-15</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="R31" s="2">
         <v>18</v>
       </c>
-      <c r="R31" s="2">
+      <c r="S31" s="2">
         <v>26</v>
       </c>
-      <c r="S31" s="2">
+      <c r="T31" s="2">
         <v>66</v>
       </c>
-      <c r="T31" s="2">
+      <c r="U31" s="2">
         <v>12</v>
       </c>
-      <c r="U31" s="2">
+      <c r="V31" s="2">
         <v>11</v>
       </c>
-      <c r="V31" s="2"/>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="W31" s="2"/>
+    </row>
+    <row r="32" spans="1:23">
       <c r="A32" s="2">
         <v>2204202</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
+      <c r="C32" s="7">
+        <v>29</v>
+      </c>
       <c r="D32" s="2">
         <v>70</v>
       </c>
@@ -2600,50 +2779,56 @@
         <v>11.23</v>
       </c>
       <c r="J32" s="2">
+        <v>28</v>
+      </c>
+      <c r="K32" s="2">
         <v>1</v>
       </c>
-      <c r="K32" s="2">
+      <c r="L32" s="2">
         <v>134</v>
       </c>
-      <c r="L32" s="2">
+      <c r="M32" s="2">
         <v>11.23</v>
       </c>
-      <c r="M32" s="2">
+      <c r="N32" s="2">
         <v>125</v>
       </c>
-      <c r="N32" s="2">
-        <v>0</v>
-      </c>
       <c r="O32" s="2">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2">
         <v>120</v>
       </c>
-      <c r="P32" s="2">
+      <c r="Q32" s="2">
         <v>-5</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="R32" s="2">
         <v>23</v>
       </c>
-      <c r="R32" s="2">
+      <c r="S32" s="2">
         <v>26</v>
       </c>
-      <c r="S32" s="2">
+      <c r="T32" s="2">
         <v>75</v>
       </c>
-      <c r="T32" s="2">
+      <c r="U32" s="2">
         <v>13</v>
       </c>
-      <c r="U32" s="2">
+      <c r="V32" s="2">
         <v>10</v>
       </c>
-      <c r="V32" s="2"/>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="W32" s="2"/>
+    </row>
+    <row r="33" spans="1:23">
       <c r="A33" s="2">
         <v>2204531</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
+      <c r="C33" s="7">
+        <v>29</v>
+      </c>
       <c r="D33" s="2">
         <v>74</v>
       </c>
@@ -2663,50 +2848,56 @@
         <v>11.75</v>
       </c>
       <c r="J33" s="2">
+        <v>25</v>
+      </c>
+      <c r="K33" s="2">
         <v>13</v>
       </c>
-      <c r="K33" s="2">
+      <c r="L33" s="2">
         <v>102</v>
       </c>
-      <c r="L33" s="2">
+      <c r="M33" s="2">
         <v>11.75</v>
       </c>
-      <c r="M33" s="2">
+      <c r="N33" s="2">
         <v>120</v>
       </c>
-      <c r="N33" s="2">
-        <v>0</v>
-      </c>
       <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2">
         <v>95</v>
       </c>
-      <c r="P33" s="2">
+      <c r="Q33" s="2">
         <v>-5</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="R33" s="2">
         <v>17</v>
       </c>
-      <c r="R33" s="2">
+      <c r="S33" s="2">
         <v>28</v>
       </c>
-      <c r="S33" s="2">
+      <c r="T33" s="2">
         <v>48</v>
       </c>
-      <c r="T33" s="2">
+      <c r="U33" s="2">
         <v>13</v>
       </c>
-      <c r="U33" s="2">
+      <c r="V33" s="2">
         <v>9</v>
       </c>
-      <c r="V33" s="2"/>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="W33" s="2"/>
+    </row>
+    <row r="34" spans="1:23">
       <c r="A34" s="2">
         <v>2204625</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
+      <c r="C34" s="7">
+        <v>25</v>
+      </c>
       <c r="D34" s="2">
         <v>69</v>
       </c>
@@ -2726,50 +2917,56 @@
         <v>10.69</v>
       </c>
       <c r="J34" s="2">
+        <v>4</v>
+      </c>
+      <c r="K34" s="2">
         <v>16</v>
       </c>
-      <c r="K34" s="2">
+      <c r="L34" s="2">
         <v>112</v>
       </c>
-      <c r="L34" s="2">
+      <c r="M34" s="2">
         <v>10.69</v>
       </c>
-      <c r="M34" s="2">
+      <c r="N34" s="2">
         <v>120</v>
       </c>
-      <c r="N34" s="2">
+      <c r="O34" s="2">
         <v>-10</v>
       </c>
-      <c r="O34" s="2">
+      <c r="P34" s="2">
         <v>140</v>
       </c>
-      <c r="P34" s="2">
+      <c r="Q34" s="2">
         <v>-10</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="R34" s="2">
         <v>22</v>
       </c>
-      <c r="R34" s="2">
+      <c r="S34" s="2">
         <v>30</v>
       </c>
-      <c r="S34" s="2">
+      <c r="T34" s="2">
         <v>51</v>
       </c>
-      <c r="T34" s="2">
+      <c r="U34" s="2">
         <v>15</v>
       </c>
-      <c r="U34" s="2">
+      <c r="V34" s="2">
         <v>9</v>
       </c>
-      <c r="V34" s="2"/>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="W34" s="2"/>
+    </row>
+    <row r="35" spans="1:23">
       <c r="A35" s="2">
         <v>2204766</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
+      <c r="C35" s="7">
+        <v>29</v>
+      </c>
       <c r="D35" s="2">
         <v>72</v>
       </c>
@@ -2789,50 +2986,56 @@
         <v>10.54</v>
       </c>
       <c r="J35" s="2">
+        <v>12</v>
+      </c>
+      <c r="K35" s="2">
         <v>24</v>
       </c>
-      <c r="K35" s="2">
+      <c r="L35" s="2">
         <v>110</v>
       </c>
-      <c r="L35" s="2">
+      <c r="M35" s="2">
         <v>9.49</v>
       </c>
-      <c r="M35" s="2">
+      <c r="N35" s="2">
         <v>130</v>
       </c>
-      <c r="N35" s="2">
-        <v>0</v>
-      </c>
       <c r="O35" s="2">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2">
         <v>120</v>
       </c>
-      <c r="P35" s="2">
+      <c r="Q35" s="2">
         <v>-10</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="R35" s="2">
         <v>20</v>
       </c>
-      <c r="R35" s="2">
+      <c r="S35" s="2">
         <v>16</v>
       </c>
-      <c r="S35" s="2">
+      <c r="T35" s="2">
         <v>65</v>
       </c>
-      <c r="T35" s="2">
+      <c r="U35" s="2">
         <v>10</v>
       </c>
-      <c r="U35" s="2">
+      <c r="V35" s="2">
         <v>9</v>
       </c>
-      <c r="V35" s="2"/>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="W35" s="2"/>
+    </row>
+    <row r="36" spans="1:23">
       <c r="A36" s="2">
         <v>2300143</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
+      <c r="C36" s="7">
+        <v>32</v>
+      </c>
       <c r="D36" s="2">
         <v>79</v>
       </c>
@@ -2852,52 +3055,55 @@
         <v>12.89</v>
       </c>
       <c r="J36" s="2">
+        <v>48</v>
+      </c>
+      <c r="K36" s="2">
         <v>12</v>
       </c>
-      <c r="K36" s="2">
+      <c r="L36" s="2">
         <v>125</v>
       </c>
-      <c r="L36" s="2">
+      <c r="M36" s="2">
         <v>12.56</v>
       </c>
-      <c r="M36" s="2">
+      <c r="N36" s="2">
         <v>110</v>
       </c>
-      <c r="N36" s="2">
+      <c r="O36" s="2">
         <v>-5</v>
       </c>
-      <c r="O36" s="2">
+      <c r="P36" s="2">
         <v>120</v>
       </c>
-      <c r="P36" s="2">
-        <v>0</v>
-      </c>
       <c r="Q36" s="2">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2">
         <v>20</v>
       </c>
-      <c r="R36" s="2">
+      <c r="S36" s="2">
         <v>32</v>
       </c>
-      <c r="S36" s="2">
+      <c r="T36" s="2">
         <v>59</v>
-      </c>
-      <c r="T36" s="2">
-        <v>14</v>
       </c>
       <c r="U36" s="2">
         <v>14</v>
       </c>
-      <c r="V36" s="2"/>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="V36" s="2">
+        <v>14</v>
+      </c>
+      <c r="W36" s="2"/>
+    </row>
+    <row r="37" spans="1:23">
       <c r="A37" s="2">
         <v>2300143</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
-      <c r="C37" t="s">
-        <v>32</v>
+      <c r="C37" s="7">
+        <v>24</v>
       </c>
       <c r="D37" s="2">
         <v>79</v>
@@ -2918,50 +3124,56 @@
         <v>10</v>
       </c>
       <c r="J37" s="2">
+        <v>44</v>
+      </c>
+      <c r="K37" s="2">
         <v>19</v>
       </c>
-      <c r="K37" s="2">
+      <c r="L37" s="2">
         <v>138</v>
       </c>
-      <c r="L37" s="2">
+      <c r="M37" s="2">
         <v>11.75</v>
       </c>
-      <c r="M37" s="2">
+      <c r="N37" s="2">
         <v>115</v>
       </c>
-      <c r="N37" s="2">
+      <c r="O37" s="2">
         <v>-5</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="2">
         <v>115</v>
       </c>
-      <c r="P37" s="2">
+      <c r="Q37" s="2">
         <v>-5</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="R37" s="2">
         <v>19</v>
       </c>
-      <c r="R37" s="2">
+      <c r="S37" s="2">
         <v>34</v>
       </c>
-      <c r="S37" s="2">
+      <c r="T37" s="2">
         <v>74</v>
       </c>
-      <c r="T37" s="2">
+      <c r="U37" s="2">
         <v>14</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>11</v>
       </c>
-      <c r="V37" s="2"/>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="W37" s="2"/>
+    </row>
+    <row r="38" spans="1:23">
       <c r="A38" s="2">
         <v>2300176</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
+      <c r="C38" s="7">
+        <v>30</v>
+      </c>
       <c r="D38" s="2">
         <v>82</v>
       </c>
@@ -2981,50 +3193,56 @@
         <v>11.68</v>
       </c>
       <c r="J38" s="2">
+        <v>29</v>
+      </c>
+      <c r="K38" s="2">
         <v>33</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>106</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>11.68</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>115</v>
       </c>
-      <c r="N38" s="2">
-        <v>0</v>
-      </c>
       <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
         <v>120</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>-5</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>21</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>20</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>53</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>13</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>12</v>
       </c>
-      <c r="V38" s="2"/>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="W38" s="2"/>
+    </row>
+    <row r="39" spans="1:23">
       <c r="A39" s="2">
         <v>2300484</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
+      <c r="C39" s="7">
+        <v>29</v>
+      </c>
       <c r="D39" s="2">
         <v>76</v>
       </c>
@@ -3044,50 +3262,56 @@
         <v>13.33</v>
       </c>
       <c r="J39" s="2">
+        <v>24</v>
+      </c>
+      <c r="K39" s="2">
         <v>17</v>
       </c>
-      <c r="K39" s="2">
+      <c r="L39" s="2">
         <v>121</v>
       </c>
-      <c r="L39" s="2">
+      <c r="M39" s="2">
         <v>13.33</v>
       </c>
-      <c r="M39" s="2">
+      <c r="N39" s="2">
         <v>120</v>
       </c>
-      <c r="N39" s="2">
-        <v>0</v>
-      </c>
       <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
         <v>135</v>
       </c>
-      <c r="P39" s="2">
+      <c r="Q39" s="2">
         <v>-10</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="R39" s="2">
         <v>22</v>
       </c>
-      <c r="R39" s="2">
+      <c r="S39" s="2">
         <v>20</v>
       </c>
-      <c r="S39" s="2">
+      <c r="T39" s="2">
         <v>70</v>
       </c>
-      <c r="T39" s="2">
+      <c r="U39" s="2">
         <v>13</v>
       </c>
-      <c r="U39" s="2">
+      <c r="V39" s="2">
         <v>9</v>
       </c>
-      <c r="V39" s="2"/>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="W39" s="2"/>
+    </row>
+    <row r="40" spans="1:23">
       <c r="A40" s="2">
         <v>2300760</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
+      <c r="C40" s="7">
+        <v>30</v>
+      </c>
       <c r="D40" s="2">
         <v>74</v>
       </c>
@@ -3107,50 +3331,56 @@
         <v>10.94</v>
       </c>
       <c r="J40" s="2">
+        <v>30</v>
+      </c>
+      <c r="K40" s="2">
         <v>21</v>
       </c>
-      <c r="K40" s="2">
+      <c r="L40" s="2">
         <v>105</v>
       </c>
-      <c r="L40" s="2">
+      <c r="M40" s="2">
         <v>12.29</v>
       </c>
-      <c r="M40" s="2">
+      <c r="N40" s="2">
         <v>115</v>
       </c>
-      <c r="N40" s="2">
+      <c r="O40" s="2">
         <v>-5</v>
       </c>
-      <c r="O40" s="2">
+      <c r="P40" s="2">
         <v>100</v>
       </c>
-      <c r="P40" s="2">
+      <c r="Q40" s="2">
         <v>-20</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="R40" s="2">
         <v>8</v>
       </c>
-      <c r="R40" s="2">
+      <c r="S40" s="2">
         <v>24</v>
       </c>
-      <c r="S40" s="2">
+      <c r="T40" s="2">
         <v>62</v>
       </c>
-      <c r="T40" s="2">
+      <c r="U40" s="2">
         <v>14</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>11</v>
       </c>
-      <c r="V40" s="2"/>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="W40" s="2"/>
+    </row>
+    <row r="41" spans="1:23">
       <c r="A41" s="2">
         <v>2301202</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
+      <c r="C41" s="7">
+        <v>29</v>
+      </c>
       <c r="D41" s="2">
         <v>74</v>
       </c>
@@ -3170,50 +3400,56 @@
         <v>9.3800000000000008</v>
       </c>
       <c r="J41" s="2">
+        <v>34</v>
+      </c>
+      <c r="K41" s="2">
         <v>6</v>
       </c>
-      <c r="K41" s="2">
+      <c r="L41" s="2">
         <v>108</v>
       </c>
-      <c r="L41" s="2">
+      <c r="M41" s="2">
         <v>9.31</v>
       </c>
-      <c r="M41" s="2">
+      <c r="N41" s="2">
         <v>125</v>
       </c>
-      <c r="N41" s="2">
-        <v>0</v>
-      </c>
       <c r="O41" s="2">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2">
         <v>120</v>
       </c>
-      <c r="P41" s="2">
+      <c r="Q41" s="2">
         <v>15</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="R41" s="2">
         <v>18</v>
       </c>
-      <c r="R41" s="2">
+      <c r="S41" s="2">
         <v>24</v>
       </c>
-      <c r="S41" s="2">
+      <c r="T41" s="2">
         <v>56</v>
       </c>
-      <c r="T41" s="2">
+      <c r="U41" s="2">
         <v>12</v>
       </c>
-      <c r="U41" s="2">
+      <c r="V41" s="2">
         <v>10</v>
       </c>
-      <c r="V41" s="2"/>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="W41" s="2"/>
+    </row>
+    <row r="42" spans="1:23">
       <c r="A42" s="2">
         <v>2301202</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
+      <c r="C42" s="7">
+        <v>33</v>
+      </c>
       <c r="D42" s="2">
         <v>74</v>
       </c>
@@ -3233,50 +3469,56 @@
         <v>8.2100000000000009</v>
       </c>
       <c r="J42" s="2">
+        <v>11</v>
+      </c>
+      <c r="K42" s="2">
         <v>2</v>
       </c>
-      <c r="K42" s="2">
+      <c r="L42" s="2">
         <v>129</v>
       </c>
-      <c r="L42" s="2">
+      <c r="M42" s="2">
         <v>8.2100000000000009</v>
       </c>
-      <c r="M42" s="2">
+      <c r="N42" s="2">
         <v>130</v>
       </c>
-      <c r="N42" s="2">
-        <v>0</v>
-      </c>
       <c r="O42" s="2">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2">
         <v>125</v>
       </c>
-      <c r="P42" s="2">
+      <c r="Q42" s="2">
         <v>-5</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="R42" s="2">
         <v>22</v>
       </c>
-      <c r="R42" s="2">
+      <c r="S42" s="2">
         <v>28</v>
       </c>
-      <c r="S42" s="2">
+      <c r="T42" s="2">
         <v>71</v>
       </c>
-      <c r="T42" s="2">
+      <c r="U42" s="2">
         <v>11</v>
       </c>
-      <c r="U42" s="2">
+      <c r="V42" s="2">
         <v>8</v>
       </c>
-      <c r="V42" s="2"/>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="W42" s="2"/>
+    </row>
+    <row r="43" spans="1:23">
       <c r="A43" s="2">
         <v>2301430</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
+      <c r="C43" s="7">
+        <v>29</v>
+      </c>
       <c r="D43" s="2">
         <v>84</v>
       </c>
@@ -3296,52 +3538,55 @@
         <v>11</v>
       </c>
       <c r="J43" s="2">
+        <v>29</v>
+      </c>
+      <c r="K43" s="2">
         <v>24</v>
       </c>
-      <c r="K43" s="2">
+      <c r="L43" s="2">
         <v>109</v>
       </c>
-      <c r="L43" s="2">
+      <c r="M43" s="2">
         <v>16.91</v>
       </c>
-      <c r="M43" s="2">
+      <c r="N43" s="2">
         <v>115</v>
       </c>
-      <c r="N43" s="2">
-        <v>0</v>
-      </c>
       <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
         <v>115</v>
       </c>
-      <c r="P43" s="2">
+      <c r="Q43" s="2">
         <v>-15</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="R43" s="2">
         <v>17</v>
       </c>
-      <c r="R43" s="2">
+      <c r="S43" s="2">
         <v>26</v>
       </c>
-      <c r="S43" s="2">
+      <c r="T43" s="2">
         <v>57</v>
       </c>
-      <c r="T43" s="2">
+      <c r="U43" s="2">
         <v>15</v>
       </c>
-      <c r="U43" s="2">
+      <c r="V43" s="2">
         <v>9</v>
       </c>
-      <c r="V43" s="2"/>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="W43" s="2"/>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44" s="2">
         <v>2301506</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
-      <c r="C44" t="s">
-        <v>35</v>
+      <c r="C44" s="7">
+        <v>39</v>
       </c>
       <c r="D44" s="2">
         <v>75</v>
@@ -3365,47 +3610,53 @@
         <v>1</v>
       </c>
       <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2">
         <v>150</v>
       </c>
-      <c r="L44" s="2">
+      <c r="M44" s="2">
         <v>9.9</v>
       </c>
-      <c r="M44" s="2">
+      <c r="N44" s="2">
         <v>125</v>
       </c>
-      <c r="N44" s="2">
-        <v>0</v>
-      </c>
       <c r="O44" s="2">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2">
         <v>120</v>
       </c>
-      <c r="P44" s="2">
+      <c r="Q44" s="2">
         <v>-5</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="R44" s="2">
         <v>24</v>
       </c>
-      <c r="R44" s="2">
+      <c r="S44" s="2">
         <v>38</v>
       </c>
-      <c r="S44" s="2">
+      <c r="T44" s="2">
         <v>79</v>
       </c>
-      <c r="T44" s="2">
+      <c r="U44" s="2">
         <v>15</v>
       </c>
-      <c r="U44" s="2">
+      <c r="V44" s="2">
         <v>9</v>
       </c>
-      <c r="V44" s="2"/>
-    </row>
-    <row r="45" spans="1:22">
+      <c r="W44" s="2"/>
+    </row>
+    <row r="45" spans="1:23">
       <c r="A45" s="2">
         <v>2301620</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
+      <c r="C45" s="7">
+        <v>29</v>
+      </c>
       <c r="D45" s="2">
         <v>70</v>
       </c>
@@ -3425,50 +3676,56 @@
         <v>9.9</v>
       </c>
       <c r="J45" s="2">
+        <v>42</v>
+      </c>
+      <c r="K45" s="2">
         <v>6</v>
       </c>
-      <c r="K45" s="2">
+      <c r="L45" s="2">
         <v>120</v>
       </c>
-      <c r="L45" s="2">
+      <c r="M45" s="2">
         <v>9.9</v>
       </c>
-      <c r="M45" s="2">
+      <c r="N45" s="2">
         <v>110</v>
       </c>
-      <c r="N45" s="2">
+      <c r="O45" s="2">
         <v>-15</v>
       </c>
-      <c r="O45" s="2">
+      <c r="P45" s="2">
         <v>115</v>
       </c>
-      <c r="P45" s="2">
+      <c r="Q45" s="2">
         <v>-25</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="R45" s="2">
         <v>18</v>
       </c>
-      <c r="R45" s="2">
+      <c r="S45" s="2">
         <v>28</v>
       </c>
-      <c r="S45" s="2">
+      <c r="T45" s="2">
         <v>66</v>
       </c>
-      <c r="T45" s="2">
+      <c r="U45" s="2">
         <v>15</v>
       </c>
-      <c r="U45" s="2">
+      <c r="V45" s="2">
         <v>8</v>
       </c>
-      <c r="V45" s="2"/>
-    </row>
-    <row r="46" spans="1:22">
+      <c r="W45" s="2"/>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46" s="2">
         <v>2301878</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
+      <c r="C46" s="7">
+        <v>28</v>
+      </c>
       <c r="D46" s="2">
         <v>77</v>
       </c>
@@ -3488,50 +3745,56 @@
         <v>12.19</v>
       </c>
       <c r="J46" s="2">
+        <v>28</v>
+      </c>
+      <c r="K46" s="2">
         <v>30</v>
       </c>
-      <c r="K46" s="2">
+      <c r="L46" s="2">
         <v>76</v>
       </c>
-      <c r="L46" s="2">
+      <c r="M46" s="2">
         <v>12.19</v>
       </c>
-      <c r="M46" s="2">
+      <c r="N46" s="2">
         <v>115</v>
       </c>
-      <c r="N46" s="2">
-        <v>0</v>
-      </c>
       <c r="O46" s="2">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2">
         <v>120</v>
       </c>
-      <c r="P46" s="2">
-        <v>0</v>
-      </c>
       <c r="Q46" s="2">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2">
         <v>16</v>
       </c>
-      <c r="R46" s="2">
+      <c r="S46" s="2">
         <v>18</v>
       </c>
-      <c r="S46" s="2">
+      <c r="T46" s="2">
         <v>31</v>
       </c>
-      <c r="T46" s="2">
+      <c r="U46" s="2">
         <v>14</v>
       </c>
-      <c r="U46" s="2">
+      <c r="V46" s="2">
         <v>11</v>
       </c>
-      <c r="V46" s="2"/>
-    </row>
-    <row r="47" spans="1:22">
+      <c r="W46" s="2"/>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47" s="2">
         <v>2301974</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
+      <c r="C47" s="7">
+        <v>32</v>
+      </c>
       <c r="D47" s="2">
         <v>74</v>
       </c>
@@ -3551,50 +3814,56 @@
         <v>12</v>
       </c>
       <c r="J47" s="2">
+        <v>25</v>
+      </c>
+      <c r="K47" s="2">
         <v>1</v>
       </c>
-      <c r="K47" s="2">
+      <c r="L47" s="2">
         <v>118</v>
       </c>
-      <c r="L47" s="2">
+      <c r="M47" s="2">
         <v>9.5399999999999991</v>
       </c>
-      <c r="M47" s="2">
+      <c r="N47" s="2">
         <v>130</v>
       </c>
-      <c r="N47" s="2">
-        <v>0</v>
-      </c>
       <c r="O47" s="2">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2">
         <v>105</v>
       </c>
-      <c r="P47" s="2">
+      <c r="Q47" s="2">
         <v>-10</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="R47" s="2">
         <v>23</v>
       </c>
-      <c r="R47" s="2">
+      <c r="S47" s="2">
         <v>32</v>
       </c>
-      <c r="S47" s="2">
+      <c r="T47" s="2">
         <v>53</v>
       </c>
-      <c r="T47" s="2">
+      <c r="U47" s="2">
         <v>12</v>
       </c>
-      <c r="U47" s="2">
+      <c r="V47" s="2">
         <v>10</v>
       </c>
-      <c r="V47" s="2"/>
-    </row>
-    <row r="48" spans="1:22">
+      <c r="W47" s="2"/>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48" s="2">
         <v>2303599</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
+      <c r="C48" s="7">
+        <v>31</v>
+      </c>
       <c r="D48" s="2">
         <v>72</v>
       </c>
@@ -3614,50 +3883,56 @@
         <v>12.44</v>
       </c>
       <c r="J48" s="2">
+        <v>41</v>
+      </c>
+      <c r="K48" s="2">
         <v>31</v>
       </c>
-      <c r="K48" s="2">
+      <c r="L48" s="2">
         <v>83</v>
       </c>
-      <c r="L48" s="2">
+      <c r="M48" s="2">
         <v>12.33</v>
       </c>
-      <c r="M48" s="2">
+      <c r="N48" s="2">
         <v>120</v>
       </c>
-      <c r="N48" s="2">
+      <c r="O48" s="2">
         <v>-5</v>
       </c>
-      <c r="O48" s="2">
+      <c r="P48" s="2">
         <v>-15</v>
       </c>
-      <c r="P48" s="2">
+      <c r="Q48" s="2">
         <v>130</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="R48" s="2">
         <v>16</v>
       </c>
-      <c r="R48" s="2">
+      <c r="S48" s="2">
         <v>22</v>
       </c>
-      <c r="S48" s="2">
+      <c r="T48" s="2">
         <v>34</v>
       </c>
-      <c r="T48" s="2">
+      <c r="U48" s="2">
         <v>15</v>
       </c>
-      <c r="U48" s="2">
+      <c r="V48" s="2">
         <v>11</v>
       </c>
-      <c r="V48" s="2"/>
-    </row>
-    <row r="49" spans="1:22">
+      <c r="W48" s="2"/>
+    </row>
+    <row r="49" spans="1:23">
       <c r="A49" s="2">
         <v>2304093</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
+      <c r="C49" s="7">
+        <v>32</v>
+      </c>
       <c r="D49" s="2">
         <v>79</v>
       </c>
@@ -3677,50 +3952,56 @@
         <v>13</v>
       </c>
       <c r="J49" s="2">
+        <v>28</v>
+      </c>
+      <c r="K49" s="2">
         <v>1</v>
       </c>
-      <c r="K49" s="2">
+      <c r="L49" s="2">
         <v>157</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M49" s="2">
         <v>11.69</v>
       </c>
-      <c r="M49" s="2">
+      <c r="N49" s="2">
         <v>130</v>
       </c>
-      <c r="N49" s="2">
-        <v>0</v>
-      </c>
       <c r="O49" s="2">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2">
         <v>130</v>
       </c>
-      <c r="P49" s="2">
+      <c r="Q49" s="2">
         <v>20</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="R49" s="2">
         <v>23</v>
       </c>
-      <c r="R49" s="2">
+      <c r="S49" s="2">
         <v>38</v>
       </c>
-      <c r="S49" s="2">
+      <c r="T49" s="2">
         <v>89</v>
       </c>
-      <c r="T49" s="2">
+      <c r="U49" s="2">
         <v>14</v>
       </c>
-      <c r="U49" s="2">
+      <c r="V49" s="2">
         <v>7</v>
       </c>
-      <c r="V49" s="2"/>
-    </row>
-    <row r="50" spans="1:22">
+      <c r="W49" s="2"/>
+    </row>
+    <row r="50" spans="1:23">
       <c r="A50" s="2">
         <v>2304321</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
+      <c r="C50" s="7">
+        <v>29</v>
+      </c>
       <c r="D50" s="2">
         <v>70</v>
       </c>
@@ -3740,50 +4021,56 @@
         <v>14.5</v>
       </c>
       <c r="J50" s="2">
+        <v>45</v>
+      </c>
+      <c r="K50" s="2">
         <v>23</v>
       </c>
-      <c r="K50" s="2">
+      <c r="L50" s="2">
         <v>98</v>
       </c>
-      <c r="L50" s="2">
+      <c r="M50" s="2">
         <v>14.5</v>
       </c>
-      <c r="M50" s="2">
+      <c r="N50" s="2">
         <v>120</v>
       </c>
-      <c r="N50" s="2">
-        <v>0</v>
-      </c>
       <c r="O50" s="2">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2">
         <v>120</v>
       </c>
-      <c r="P50" s="2">
+      <c r="Q50" s="2">
         <v>-15</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="R50" s="2">
         <v>16</v>
       </c>
-      <c r="R50" s="2">
+      <c r="S50" s="2">
         <v>20</v>
       </c>
-      <c r="S50" s="2">
+      <c r="T50" s="2">
         <v>53</v>
       </c>
-      <c r="T50" s="2">
+      <c r="U50" s="2">
         <v>15</v>
       </c>
-      <c r="U50" s="2">
+      <c r="V50" s="2">
         <v>9</v>
       </c>
-      <c r="V50" s="2"/>
-    </row>
-    <row r="51" spans="1:22">
+      <c r="W50" s="2"/>
+    </row>
+    <row r="51" spans="1:23">
       <c r="A51" s="2">
         <v>2304321</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
+      <c r="C51" s="7">
+        <v>29</v>
+      </c>
       <c r="D51" s="2">
         <v>70</v>
       </c>
@@ -3803,50 +4090,56 @@
         <v>12.28</v>
       </c>
       <c r="J51" s="2">
+        <v>18</v>
+      </c>
+      <c r="K51" s="2">
         <v>27</v>
       </c>
-      <c r="K51" s="2">
+      <c r="L51" s="2">
         <v>102</v>
       </c>
-      <c r="L51" s="2">
+      <c r="M51" s="2">
         <v>11.94</v>
       </c>
-      <c r="M51" s="2">
+      <c r="N51" s="2">
         <v>120</v>
       </c>
-      <c r="N51" s="2">
-        <v>0</v>
-      </c>
       <c r="O51" s="2">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2">
         <v>110</v>
       </c>
-      <c r="P51" s="2">
+      <c r="Q51" s="2">
         <v>-10</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="R51" s="2">
         <v>16</v>
       </c>
-      <c r="R51" s="2">
+      <c r="S51" s="2">
         <v>20</v>
       </c>
-      <c r="S51" s="2">
+      <c r="T51" s="2">
         <v>55</v>
       </c>
-      <c r="T51" s="2">
+      <c r="U51" s="2">
         <v>10</v>
       </c>
-      <c r="U51" s="2">
+      <c r="V51" s="2">
         <v>11</v>
       </c>
-      <c r="V51" s="2"/>
-    </row>
-    <row r="52" spans="1:22">
+      <c r="W51" s="2"/>
+    </row>
+    <row r="52" spans="1:23">
       <c r="A52" s="2">
         <v>2304669</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
+      <c r="C52" s="7">
+        <v>29</v>
+      </c>
       <c r="D52" s="2">
         <v>55</v>
       </c>
@@ -3866,48 +4159,54 @@
         <v>0</v>
       </c>
       <c r="J52" s="2">
+        <v>41</v>
+      </c>
+      <c r="K52" s="2">
         <v>38</v>
       </c>
-      <c r="K52" s="2">
+      <c r="L52" s="2">
         <v>107</v>
       </c>
-      <c r="L52" s="1"/>
-      <c r="M52" s="2">
+      <c r="M52" s="1"/>
+      <c r="N52" s="2">
         <v>120</v>
       </c>
-      <c r="N52" s="2">
-        <v>0</v>
-      </c>
       <c r="O52" s="2">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2">
         <v>125</v>
       </c>
-      <c r="P52" s="2">
+      <c r="Q52" s="2">
         <v>-5</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="R52" s="2">
         <v>19</v>
       </c>
-      <c r="R52" s="2">
+      <c r="S52" s="2">
         <v>24</v>
       </c>
-      <c r="S52" s="2">
+      <c r="T52" s="2">
         <v>53</v>
       </c>
-      <c r="T52" s="2">
+      <c r="U52" s="2">
         <v>13</v>
       </c>
-      <c r="U52" s="2">
+      <c r="V52" s="2">
         <v>11</v>
       </c>
-      <c r="V52" s="2"/>
-    </row>
-    <row r="53" spans="1:22">
+      <c r="W52" s="2"/>
+    </row>
+    <row r="53" spans="1:23">
       <c r="A53" s="2">
         <v>2304770</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
+      <c r="C53" s="7">
+        <v>29</v>
+      </c>
       <c r="D53" s="2">
         <v>72</v>
       </c>
@@ -3927,52 +4226,55 @@
         <v>6.93</v>
       </c>
       <c r="J53" s="2">
+        <v>42</v>
+      </c>
+      <c r="K53" s="2">
         <v>22</v>
       </c>
-      <c r="K53" s="2">
+      <c r="L53" s="2">
         <v>79</v>
       </c>
-      <c r="L53" s="2">
+      <c r="M53" s="2">
         <v>6.93</v>
       </c>
-      <c r="M53" s="2">
+      <c r="N53" s="2">
         <v>120</v>
       </c>
-      <c r="N53" s="2">
-        <v>0</v>
-      </c>
       <c r="O53" s="2">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2">
         <v>120</v>
       </c>
-      <c r="P53" s="2">
+      <c r="Q53" s="2">
         <v>-5</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="R53" s="2">
         <v>16</v>
       </c>
-      <c r="R53" s="2">
+      <c r="S53" s="2">
         <v>20</v>
       </c>
-      <c r="S53" s="2">
+      <c r="T53" s="2">
         <v>32</v>
       </c>
-      <c r="T53" s="2">
+      <c r="U53" s="2">
         <v>15</v>
       </c>
-      <c r="U53" s="2">
+      <c r="V53" s="2">
         <v>11</v>
       </c>
-      <c r="V53" s="2"/>
-    </row>
-    <row r="54" spans="1:22">
+      <c r="W53" s="2"/>
+    </row>
+    <row r="54" spans="1:23">
       <c r="A54" s="2">
         <v>2400005</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
-      <c r="C54" t="s">
-        <v>33</v>
+      <c r="C54" s="7">
+        <v>24</v>
       </c>
       <c r="D54" s="2">
         <v>86</v>
@@ -3993,50 +4295,56 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="J54" s="2">
+        <v>50</v>
+      </c>
+      <c r="K54" s="2">
         <v>2</v>
       </c>
-      <c r="K54" s="2">
+      <c r="L54" s="2">
         <v>147</v>
       </c>
-      <c r="L54" s="2">
+      <c r="M54" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="M54" s="2">
+      <c r="N54" s="2">
         <v>130</v>
       </c>
-      <c r="N54" s="2">
+      <c r="O54" s="2">
         <v>-5</v>
       </c>
-      <c r="O54" s="2">
+      <c r="P54" s="2">
         <v>120</v>
       </c>
-      <c r="P54" s="2">
+      <c r="Q54" s="2">
         <v>-10</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="R54" s="2">
         <v>23</v>
       </c>
-      <c r="R54" s="2">
+      <c r="S54" s="2">
         <v>32</v>
       </c>
-      <c r="S54" s="2">
+      <c r="T54" s="2">
         <v>81</v>
       </c>
-      <c r="T54" s="2">
+      <c r="U54" s="2">
         <v>14</v>
       </c>
-      <c r="U54" s="2">
+      <c r="V54" s="2">
         <v>11</v>
       </c>
-      <c r="V54" s="2"/>
-    </row>
-    <row r="55" spans="1:22">
+      <c r="W54" s="2"/>
+    </row>
+    <row r="55" spans="1:23">
       <c r="A55" s="2">
         <v>2400788</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
+      <c r="C55" s="7">
+        <v>31</v>
+      </c>
       <c r="D55" s="2">
         <v>73</v>
       </c>
@@ -4056,50 +4364,56 @@
         <v>7.77</v>
       </c>
       <c r="J55" s="2">
+        <v>37</v>
+      </c>
+      <c r="K55" s="2">
         <v>5</v>
       </c>
-      <c r="K55" s="2">
+      <c r="L55" s="2">
         <v>146</v>
       </c>
-      <c r="L55" s="2">
+      <c r="M55" s="2">
         <v>7.77</v>
       </c>
-      <c r="M55" s="2">
+      <c r="N55" s="2">
         <v>115</v>
       </c>
-      <c r="N55" s="2">
-        <v>0</v>
-      </c>
       <c r="O55" s="2">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2">
         <v>120</v>
       </c>
-      <c r="P55" s="2">
-        <v>0</v>
-      </c>
       <c r="Q55" s="2">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2">
         <v>23</v>
       </c>
-      <c r="R55" s="2">
+      <c r="S55" s="2">
         <v>38</v>
       </c>
-      <c r="S55" s="2">
+      <c r="T55" s="2">
         <v>75</v>
       </c>
-      <c r="T55" s="2">
+      <c r="U55" s="2">
         <v>14</v>
       </c>
-      <c r="U55" s="2">
+      <c r="V55" s="2">
         <v>10</v>
       </c>
-      <c r="V55" s="2"/>
-    </row>
-    <row r="56" spans="1:22">
+      <c r="W55" s="2"/>
+    </row>
+    <row r="56" spans="1:23">
       <c r="A56" s="2">
         <v>2401195</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
+      <c r="C56" s="7">
+        <v>29</v>
+      </c>
       <c r="D56" s="2">
         <v>69</v>
       </c>
@@ -4119,50 +4433,56 @@
         <v>8.58</v>
       </c>
       <c r="J56" s="2">
+        <v>44</v>
+      </c>
+      <c r="K56" s="2">
         <v>7</v>
       </c>
-      <c r="K56" s="2">
+      <c r="L56" s="2">
         <v>125</v>
       </c>
-      <c r="L56" s="2">
+      <c r="M56" s="2">
         <v>8.58</v>
       </c>
-      <c r="M56" s="2">
+      <c r="N56" s="2">
         <v>125</v>
       </c>
-      <c r="N56" s="2">
-        <v>0</v>
-      </c>
       <c r="O56" s="2">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2">
         <v>125</v>
       </c>
-      <c r="P56" s="2">
+      <c r="Q56" s="2">
         <v>-10</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="R56" s="2">
         <v>20</v>
       </c>
-      <c r="R56" s="2">
+      <c r="S56" s="2">
         <v>28</v>
       </c>
-      <c r="S56" s="2">
+      <c r="T56" s="2">
         <v>69</v>
       </c>
-      <c r="T56" s="2">
+      <c r="U56" s="2">
         <v>11</v>
       </c>
-      <c r="U56" s="2">
+      <c r="V56" s="2">
         <v>8</v>
       </c>
-      <c r="V56" s="2"/>
-    </row>
-    <row r="57" spans="1:22">
+      <c r="W56" s="2"/>
+    </row>
+    <row r="57" spans="1:23">
       <c r="A57" s="2">
         <v>2401295</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
+      <c r="C57" s="7">
+        <v>28</v>
+      </c>
       <c r="D57" s="2">
         <v>62</v>
       </c>
@@ -4182,50 +4502,56 @@
         <v>8.92</v>
       </c>
       <c r="J57" s="2">
+        <v>24</v>
+      </c>
+      <c r="K57" s="2">
         <v>50</v>
       </c>
-      <c r="K57" s="2">
+      <c r="L57" s="2">
         <v>121</v>
       </c>
-      <c r="L57" s="2">
+      <c r="M57" s="2">
         <v>8.92</v>
       </c>
-      <c r="M57" s="2">
+      <c r="N57" s="2">
         <v>120</v>
       </c>
-      <c r="N57" s="2">
-        <v>0</v>
-      </c>
       <c r="O57" s="2">
+        <v>0</v>
+      </c>
+      <c r="P57" s="2">
         <v>115</v>
       </c>
-      <c r="P57" s="2">
+      <c r="Q57" s="2">
         <v>-20</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="R57" s="2">
         <v>23</v>
       </c>
-      <c r="R57" s="2">
+      <c r="S57" s="2">
         <v>16</v>
       </c>
-      <c r="S57" s="2">
+      <c r="T57" s="2">
         <v>67</v>
-      </c>
-      <c r="T57" s="2">
-        <v>15</v>
       </c>
       <c r="U57" s="2">
         <v>15</v>
       </c>
-      <c r="V57" s="2"/>
-    </row>
-    <row r="58" spans="1:22">
+      <c r="V57" s="2">
+        <v>15</v>
+      </c>
+      <c r="W57" s="2"/>
+    </row>
+    <row r="58" spans="1:23">
       <c r="A58" s="2">
         <v>2401295</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
+      <c r="C58" s="7">
+        <v>30</v>
+      </c>
       <c r="D58" s="2">
         <v>63</v>
       </c>
@@ -4245,50 +4571,56 @@
         <v>8.93</v>
       </c>
       <c r="J58" s="2">
+        <v>50</v>
+      </c>
+      <c r="K58" s="2">
         <v>47</v>
       </c>
-      <c r="K58" s="2">
+      <c r="L58" s="2">
         <v>93</v>
       </c>
-      <c r="L58" s="2">
+      <c r="M58" s="2">
         <v>8.93</v>
       </c>
-      <c r="M58" s="2">
+      <c r="N58" s="2">
         <v>110</v>
       </c>
-      <c r="N58" s="2">
-        <v>0</v>
-      </c>
       <c r="O58" s="2">
+        <v>0</v>
+      </c>
+      <c r="P58" s="2">
         <v>115</v>
       </c>
-      <c r="P58" s="2">
+      <c r="Q58" s="2">
         <v>-15</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="R58" s="2">
         <v>23</v>
       </c>
-      <c r="R58" s="2">
+      <c r="S58" s="2">
         <v>18</v>
       </c>
-      <c r="S58" s="2">
+      <c r="T58" s="2">
         <v>37</v>
-      </c>
-      <c r="T58" s="2">
-        <v>15</v>
       </c>
       <c r="U58" s="2">
         <v>15</v>
       </c>
-      <c r="V58" s="2"/>
-    </row>
-    <row r="59" spans="1:22">
+      <c r="V58" s="2">
+        <v>15</v>
+      </c>
+      <c r="W58" s="2"/>
+    </row>
+    <row r="59" spans="1:23">
       <c r="A59" s="2">
         <v>2401534</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
+      <c r="C59" s="7">
+        <v>29</v>
+      </c>
       <c r="D59" s="2">
         <v>81</v>
       </c>
@@ -4308,50 +4640,56 @@
         <v>10.86</v>
       </c>
       <c r="J59" s="2">
+        <v>25</v>
+      </c>
+      <c r="K59" s="2">
         <v>10</v>
       </c>
-      <c r="K59" s="2">
+      <c r="L59" s="2">
         <v>125</v>
       </c>
-      <c r="L59" s="2">
+      <c r="M59" s="2">
         <v>10.91</v>
       </c>
-      <c r="M59" s="2">
+      <c r="N59" s="2">
         <v>120</v>
       </c>
-      <c r="N59" s="2">
-        <v>0</v>
-      </c>
       <c r="O59" s="2">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2">
         <v>120</v>
       </c>
-      <c r="P59" s="2">
+      <c r="Q59" s="2">
         <v>-10</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="R59" s="2">
         <v>18</v>
       </c>
-      <c r="R59" s="2">
+      <c r="S59" s="2">
         <v>30</v>
       </c>
-      <c r="S59" s="2">
+      <c r="T59" s="2">
         <v>68</v>
       </c>
-      <c r="T59" s="2">
+      <c r="U59" s="2">
         <v>13</v>
       </c>
-      <c r="U59" s="2">
+      <c r="V59" s="2">
         <v>9</v>
       </c>
-      <c r="V59" s="2"/>
-    </row>
-    <row r="60" spans="1:22">
+      <c r="W59" s="2"/>
+    </row>
+    <row r="60" spans="1:23">
       <c r="A60" s="2">
         <v>2401730</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
+      <c r="C60" s="7">
+        <v>29</v>
+      </c>
       <c r="D60" s="2">
         <v>69</v>
       </c>
@@ -4371,50 +4709,56 @@
         <v>39.229999999999997</v>
       </c>
       <c r="J60" s="2">
+        <v>29</v>
+      </c>
+      <c r="K60" s="2">
         <v>14</v>
       </c>
-      <c r="K60" s="2">
+      <c r="L60" s="2">
         <v>78</v>
       </c>
-      <c r="L60" s="2">
+      <c r="M60" s="2">
         <v>32.799999999999997</v>
       </c>
-      <c r="M60" s="2">
+      <c r="N60" s="2">
         <v>130</v>
       </c>
-      <c r="N60" s="2">
+      <c r="O60" s="2">
         <v>-5</v>
       </c>
-      <c r="O60" s="2">
+      <c r="P60" s="2">
         <v>120</v>
       </c>
-      <c r="P60" s="2">
+      <c r="Q60" s="2">
         <v>-35</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="R60" s="2">
         <v>17</v>
       </c>
-      <c r="R60" s="2">
+      <c r="S60" s="2">
         <v>12</v>
       </c>
-      <c r="S60" s="2">
+      <c r="T60" s="2">
         <v>38</v>
-      </c>
-      <c r="T60" s="2">
-        <v>11</v>
       </c>
       <c r="U60" s="2">
         <v>11</v>
       </c>
-      <c r="V60" s="2"/>
-    </row>
-    <row r="61" spans="1:22">
+      <c r="V60" s="2">
+        <v>11</v>
+      </c>
+      <c r="W60" s="2"/>
+    </row>
+    <row r="61" spans="1:23">
       <c r="A61" s="2">
         <v>2401922</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
+      <c r="C61" s="7">
+        <v>29</v>
+      </c>
       <c r="D61" s="2">
         <v>81</v>
       </c>
@@ -4434,50 +4778,56 @@
         <v>17.829999999999998</v>
       </c>
       <c r="J61" s="2">
+        <v>29</v>
+      </c>
+      <c r="K61" s="2">
         <v>19</v>
       </c>
-      <c r="K61" s="2">
+      <c r="L61" s="2">
         <v>74</v>
       </c>
-      <c r="L61" s="2">
+      <c r="M61" s="2">
         <v>18.649999999999999</v>
       </c>
-      <c r="M61" s="2">
+      <c r="N61" s="2">
         <v>110</v>
       </c>
-      <c r="N61" s="2">
-        <v>0</v>
-      </c>
       <c r="O61" s="2">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2">
         <v>95</v>
       </c>
-      <c r="P61" s="2">
+      <c r="Q61" s="2">
         <v>-15</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="R61" s="2">
         <v>12</v>
       </c>
-      <c r="R61" s="2">
+      <c r="S61" s="2">
         <v>24</v>
       </c>
-      <c r="S61" s="2">
+      <c r="T61" s="2">
         <v>29</v>
       </c>
-      <c r="T61" s="2">
+      <c r="U61" s="2">
         <v>12</v>
       </c>
-      <c r="U61" s="2">
+      <c r="V61" s="2">
         <v>9</v>
       </c>
-      <c r="V61" s="2"/>
-    </row>
-    <row r="62" spans="1:22">
+      <c r="W61" s="2"/>
+    </row>
+    <row r="62" spans="1:23">
       <c r="A62" s="2">
         <v>2402032</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
+      <c r="C62" s="7">
+        <v>31</v>
+      </c>
       <c r="D62" s="2">
         <v>72</v>
       </c>
@@ -4497,50 +4847,56 @@
         <v>9.26</v>
       </c>
       <c r="J62" s="2">
+        <v>40</v>
+      </c>
+      <c r="K62" s="2">
         <v>26</v>
       </c>
-      <c r="K62" s="2">
+      <c r="L62" s="2">
         <v>135</v>
       </c>
-      <c r="L62" s="2">
+      <c r="M62" s="2">
         <v>9.0299999999999994</v>
       </c>
-      <c r="M62" s="2">
+      <c r="N62" s="2">
         <v>110</v>
       </c>
-      <c r="N62" s="2">
-        <v>0</v>
-      </c>
       <c r="O62" s="2">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2">
         <v>100</v>
       </c>
-      <c r="P62" s="2">
-        <v>0</v>
-      </c>
       <c r="Q62" s="2">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2">
         <v>19</v>
       </c>
-      <c r="R62" s="2">
+      <c r="S62" s="2">
         <v>28</v>
       </c>
-      <c r="S62" s="2">
+      <c r="T62" s="2">
         <v>79</v>
       </c>
-      <c r="T62" s="2">
+      <c r="U62" s="2">
         <v>13</v>
       </c>
-      <c r="U62" s="2">
+      <c r="V62" s="2">
         <v>9</v>
       </c>
-      <c r="V62" s="2"/>
-    </row>
-    <row r="63" spans="1:22">
+      <c r="W62" s="2"/>
+    </row>
+    <row r="63" spans="1:23">
       <c r="A63" s="2">
         <v>2402281</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
+      <c r="C63" s="7">
+        <v>31</v>
+      </c>
       <c r="D63" s="2">
         <v>79</v>
       </c>
@@ -4560,52 +4916,55 @@
         <v>13.88</v>
       </c>
       <c r="J63" s="2">
+        <v>49</v>
+      </c>
+      <c r="K63" s="2">
         <v>20</v>
       </c>
-      <c r="K63" s="2">
+      <c r="L63" s="2">
         <v>101</v>
       </c>
-      <c r="L63" s="2">
+      <c r="M63" s="2">
         <v>13.88</v>
       </c>
-      <c r="M63" s="2">
+      <c r="N63" s="2">
         <v>120</v>
       </c>
-      <c r="N63" s="2">
+      <c r="O63" s="2">
         <v>-5</v>
       </c>
-      <c r="O63" s="2">
+      <c r="P63" s="2">
         <v>130</v>
       </c>
-      <c r="P63" s="2">
+      <c r="Q63" s="2">
         <v>-20</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="R63" s="2">
         <v>20</v>
       </c>
-      <c r="R63" s="2">
+      <c r="S63" s="2">
         <v>26</v>
       </c>
-      <c r="S63" s="2">
+      <c r="T63" s="2">
         <v>47</v>
       </c>
-      <c r="T63" s="2">
+      <c r="U63" s="2">
         <v>14</v>
       </c>
-      <c r="U63" s="2">
+      <c r="V63" s="2">
         <v>8</v>
       </c>
-      <c r="V63" s="2"/>
-    </row>
-    <row r="64" spans="1:22">
+      <c r="W63" s="2"/>
+    </row>
+    <row r="64" spans="1:23">
       <c r="A64" s="2">
         <v>2402895</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
-      <c r="C64" t="s">
-        <v>34</v>
+      <c r="C64" s="7">
+        <v>22</v>
       </c>
       <c r="D64" s="2">
         <v>79</v>
@@ -4626,50 +4985,56 @@
         <v>14.13</v>
       </c>
       <c r="J64" s="2">
+        <v>37</v>
+      </c>
+      <c r="K64" s="2">
         <v>28</v>
       </c>
-      <c r="K64" s="2">
+      <c r="L64" s="2">
         <v>90</v>
       </c>
-      <c r="L64" s="2">
+      <c r="M64" s="2">
         <v>14.49</v>
       </c>
-      <c r="M64" s="2">
+      <c r="N64" s="2">
         <v>120</v>
       </c>
-      <c r="N64" s="2">
-        <v>0</v>
-      </c>
       <c r="O64" s="2">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2">
         <v>120</v>
       </c>
-      <c r="P64" s="2">
+      <c r="Q64" s="2">
         <v>-10</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="R64" s="2">
         <v>18</v>
       </c>
-      <c r="R64" s="2">
+      <c r="S64" s="2">
         <v>22</v>
       </c>
-      <c r="S64" s="2">
+      <c r="T64" s="2">
         <v>42</v>
       </c>
-      <c r="T64" s="2">
+      <c r="U64" s="2">
         <v>12</v>
       </c>
-      <c r="U64" s="2">
+      <c r="V64" s="2">
         <v>8</v>
       </c>
-      <c r="V64" s="2"/>
-    </row>
-    <row r="65" spans="1:22">
+      <c r="W64" s="2"/>
+    </row>
+    <row r="65" spans="1:23">
       <c r="A65" s="2">
         <v>2403315</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
+      <c r="C65" s="7">
+        <v>29</v>
+      </c>
       <c r="D65" s="2">
         <v>64</v>
       </c>
@@ -4689,50 +5054,56 @@
         <v>12.89</v>
       </c>
       <c r="J65" s="2">
+        <v>17</v>
+      </c>
+      <c r="K65" s="2">
         <v>7</v>
       </c>
-      <c r="K65" s="2">
+      <c r="L65" s="2">
         <v>135</v>
       </c>
-      <c r="L65" s="2">
+      <c r="M65" s="2">
         <v>12.89</v>
       </c>
-      <c r="M65" s="2">
+      <c r="N65" s="2">
         <v>120</v>
       </c>
-      <c r="N65" s="2">
-        <v>0</v>
-      </c>
       <c r="O65" s="2">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2">
         <v>120</v>
       </c>
-      <c r="P65" s="2">
+      <c r="Q65" s="2">
         <v>-10</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="R65" s="2">
         <v>20</v>
       </c>
-      <c r="R65" s="2">
+      <c r="S65" s="2">
         <v>28</v>
       </c>
-      <c r="S65" s="2">
+      <c r="T65" s="2">
         <v>78</v>
       </c>
-      <c r="T65" s="2">
+      <c r="U65" s="2">
         <v>14</v>
       </c>
-      <c r="U65" s="2">
+      <c r="V65" s="2">
         <v>9</v>
       </c>
-      <c r="V65" s="2"/>
-    </row>
-    <row r="66" spans="1:22">
+      <c r="W65" s="2"/>
+    </row>
+    <row r="66" spans="1:23">
       <c r="A66" s="2">
         <v>2403413</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
+      <c r="C66" s="7">
+        <v>26</v>
+      </c>
       <c r="D66" s="2">
         <v>81</v>
       </c>
@@ -4752,50 +5123,56 @@
         <v>12.39</v>
       </c>
       <c r="J66" s="2">
+        <v>19</v>
+      </c>
+      <c r="K66" s="2">
         <v>14</v>
       </c>
-      <c r="K66" s="2">
+      <c r="L66" s="2">
         <v>102</v>
       </c>
-      <c r="L66" s="2">
+      <c r="M66" s="2">
         <v>12.39</v>
       </c>
-      <c r="M66" s="2">
+      <c r="N66" s="2">
         <v>120</v>
       </c>
-      <c r="N66" s="2">
-        <v>0</v>
-      </c>
       <c r="O66" s="2">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2">
         <v>120</v>
       </c>
-      <c r="P66" s="2">
+      <c r="Q66" s="2">
         <v>-15</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="R66" s="2">
         <v>21</v>
       </c>
-      <c r="R66" s="2">
+      <c r="S66" s="2">
         <v>22</v>
       </c>
-      <c r="S66" s="2">
+      <c r="T66" s="2">
         <v>51</v>
       </c>
-      <c r="T66" s="2">
+      <c r="U66" s="2">
         <v>10</v>
       </c>
-      <c r="U66" s="2">
+      <c r="V66" s="2">
         <v>8</v>
       </c>
-      <c r="V66" s="2"/>
-    </row>
-    <row r="67" spans="1:22">
+      <c r="W66" s="2"/>
+    </row>
+    <row r="67" spans="1:23">
       <c r="A67" s="2">
         <v>2403725</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
+      <c r="C67" s="7">
+        <v>30</v>
+      </c>
       <c r="D67" s="2">
         <v>71</v>
       </c>
@@ -4815,50 +5192,56 @@
         <v>9.64</v>
       </c>
       <c r="J67" s="2">
+        <v>30</v>
+      </c>
+      <c r="K67" s="2">
         <v>23</v>
       </c>
-      <c r="K67" s="2">
+      <c r="L67" s="2">
         <v>110</v>
       </c>
-      <c r="L67" s="2">
+      <c r="M67" s="2">
         <v>9.64</v>
       </c>
-      <c r="M67" s="2">
+      <c r="N67" s="2">
         <v>125</v>
       </c>
-      <c r="N67" s="2">
-        <v>0</v>
-      </c>
       <c r="O67" s="2">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2">
         <v>120</v>
       </c>
-      <c r="P67" s="2">
+      <c r="Q67" s="2">
         <v>-5</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="R67" s="2">
         <v>19</v>
       </c>
-      <c r="R67" s="2">
+      <c r="S67" s="2">
         <v>16</v>
       </c>
-      <c r="S67" s="2">
+      <c r="T67" s="2">
         <v>66</v>
       </c>
-      <c r="T67" s="2">
+      <c r="U67" s="2">
         <v>12</v>
       </c>
-      <c r="U67" s="2">
+      <c r="V67" s="2">
         <v>9</v>
       </c>
-      <c r="V67" s="2"/>
-    </row>
-    <row r="68" spans="1:22">
+      <c r="W67" s="2"/>
+    </row>
+    <row r="68" spans="1:23">
       <c r="A68" s="2">
         <v>2403883</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
+      <c r="C68" s="7">
+        <v>29</v>
+      </c>
       <c r="D68" s="2">
         <v>64</v>
       </c>
@@ -4878,52 +5261,55 @@
         <v>9.93</v>
       </c>
       <c r="J68" s="2">
+        <v>27</v>
+      </c>
+      <c r="K68" s="2">
         <v>25</v>
       </c>
-      <c r="K68" s="2">
+      <c r="L68" s="2">
         <v>120</v>
       </c>
-      <c r="L68" s="2">
+      <c r="M68" s="2">
         <v>9.93</v>
       </c>
-      <c r="M68" s="2">
+      <c r="N68" s="2">
         <v>120</v>
       </c>
-      <c r="N68" s="2">
-        <v>0</v>
-      </c>
       <c r="O68" s="2">
+        <v>0</v>
+      </c>
+      <c r="P68" s="2">
         <v>100</v>
       </c>
-      <c r="P68" s="2">
+      <c r="Q68" s="2">
         <v>-10</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="R68" s="2">
         <v>21</v>
       </c>
-      <c r="R68" s="2">
+      <c r="S68" s="2">
         <v>14</v>
       </c>
-      <c r="S68" s="2">
+      <c r="T68" s="2">
         <v>76</v>
       </c>
-      <c r="T68" s="2">
+      <c r="U68" s="2">
         <v>15</v>
       </c>
-      <c r="U68" s="2">
+      <c r="V68" s="2">
         <v>9</v>
       </c>
-      <c r="V68" s="2"/>
-    </row>
-    <row r="69" spans="1:22">
+      <c r="W68" s="2"/>
+    </row>
+    <row r="69" spans="1:23">
       <c r="A69" s="2">
         <v>8805135</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
-      <c r="C69" t="s">
-        <v>33</v>
+      <c r="C69" s="7">
+        <v>24</v>
       </c>
       <c r="D69" s="2">
         <v>63</v>
@@ -4944,50 +5330,56 @@
         <v>7.9</v>
       </c>
       <c r="J69" s="2">
+        <v>30</v>
+      </c>
+      <c r="K69" s="2">
         <v>12</v>
       </c>
-      <c r="K69" s="2">
+      <c r="L69" s="2">
         <v>142</v>
       </c>
-      <c r="L69" s="2">
+      <c r="M69" s="2">
         <v>6.34</v>
       </c>
-      <c r="M69" s="2">
+      <c r="N69" s="2">
         <v>130</v>
       </c>
-      <c r="N69" s="2">
-        <v>0</v>
-      </c>
       <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
         <v>130</v>
       </c>
-      <c r="P69" s="2">
+      <c r="Q69" s="2">
         <v>-10</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="R69" s="2">
         <v>23</v>
       </c>
-      <c r="R69" s="2">
+      <c r="S69" s="2">
         <v>30</v>
       </c>
-      <c r="S69" s="2">
+      <c r="T69" s="2">
         <v>78</v>
-      </c>
-      <c r="T69" s="2">
-        <v>11</v>
       </c>
       <c r="U69" s="2">
         <v>11</v>
       </c>
-      <c r="V69" s="2"/>
-    </row>
-    <row r="70" spans="1:22">
+      <c r="V69" s="2">
+        <v>11</v>
+      </c>
+      <c r="W69" s="2"/>
+    </row>
+    <row r="70" spans="1:23">
       <c r="A70" s="2">
         <v>8811223</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
+      <c r="C70" s="7">
+        <v>30</v>
+      </c>
       <c r="D70" s="2">
         <v>78</v>
       </c>
@@ -5007,50 +5399,56 @@
         <v>9.11</v>
       </c>
       <c r="J70" s="2">
+        <v>41</v>
+      </c>
+      <c r="K70" s="2">
         <v>7</v>
       </c>
-      <c r="K70" s="2">
+      <c r="L70" s="2">
         <v>145</v>
       </c>
-      <c r="L70" s="2">
+      <c r="M70" s="2">
         <v>10.89</v>
       </c>
-      <c r="M70" s="2">
+      <c r="N70" s="2">
         <v>125</v>
       </c>
-      <c r="N70" s="2">
-        <v>0</v>
-      </c>
       <c r="O70" s="2">
+        <v>0</v>
+      </c>
+      <c r="P70" s="2">
         <v>120</v>
       </c>
-      <c r="P70" s="2">
+      <c r="Q70" s="2">
         <v>-10</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="R70" s="2">
         <v>21</v>
       </c>
-      <c r="R70" s="2">
+      <c r="S70" s="2">
         <v>26</v>
       </c>
-      <c r="S70" s="2">
+      <c r="T70" s="2">
         <v>88</v>
       </c>
-      <c r="T70" s="2">
+      <c r="U70" s="2">
         <v>15</v>
       </c>
-      <c r="U70" s="2">
+      <c r="V70" s="2">
         <v>10</v>
       </c>
-      <c r="V70" s="2"/>
-    </row>
-    <row r="71" spans="1:22">
+      <c r="W70" s="2"/>
+    </row>
+    <row r="71" spans="1:23">
       <c r="A71" s="2">
         <v>8852227</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
+      <c r="C71" s="7">
+        <v>29</v>
+      </c>
       <c r="D71" s="2">
         <v>76</v>
       </c>
@@ -5070,50 +5468,56 @@
         <v>10.27</v>
       </c>
       <c r="J71" s="2">
+        <v>42</v>
+      </c>
+      <c r="K71" s="2">
         <v>15</v>
       </c>
-      <c r="K71" s="2">
+      <c r="L71" s="2">
         <v>123</v>
       </c>
-      <c r="L71" s="2">
+      <c r="M71" s="2">
         <v>11.38</v>
       </c>
-      <c r="M71" s="2">
+      <c r="N71" s="2">
         <v>120</v>
       </c>
-      <c r="N71" s="2">
-        <v>0</v>
-      </c>
       <c r="O71" s="2">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2">
         <v>115</v>
       </c>
-      <c r="P71" s="2">
+      <c r="Q71" s="2">
         <v>-5</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="R71" s="2">
         <v>18</v>
       </c>
-      <c r="R71" s="2">
+      <c r="S71" s="2">
         <v>26</v>
       </c>
-      <c r="S71" s="2">
+      <c r="T71" s="2">
         <v>66</v>
       </c>
-      <c r="T71" s="2">
+      <c r="U71" s="2">
         <v>10</v>
       </c>
-      <c r="U71" s="2">
+      <c r="V71" s="2">
         <v>13</v>
       </c>
-      <c r="V71" s="2"/>
-    </row>
-    <row r="72" spans="1:22">
+      <c r="W71" s="2"/>
+    </row>
+    <row r="72" spans="1:23">
       <c r="A72" s="2">
         <v>8852227</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
+      <c r="C72" s="7">
+        <v>30</v>
+      </c>
       <c r="D72" s="2">
         <v>77</v>
       </c>
@@ -5133,50 +5537,56 @@
         <v>10.63</v>
       </c>
       <c r="J72" s="2">
+        <v>35</v>
+      </c>
+      <c r="K72" s="2">
         <v>25</v>
       </c>
-      <c r="K72" s="2">
+      <c r="L72" s="2">
         <v>90</v>
       </c>
-      <c r="L72" s="2">
+      <c r="M72" s="2">
         <v>10.63</v>
       </c>
-      <c r="M72" s="2">
+      <c r="N72" s="2">
         <v>120</v>
       </c>
-      <c r="N72" s="2">
-        <v>0</v>
-      </c>
       <c r="O72" s="2">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2">
         <v>120</v>
       </c>
-      <c r="P72" s="2">
-        <v>0</v>
-      </c>
       <c r="Q72" s="2">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2">
         <v>16</v>
       </c>
-      <c r="R72" s="2">
+      <c r="S72" s="2">
         <v>22</v>
       </c>
-      <c r="S72" s="2">
+      <c r="T72" s="2">
         <v>43</v>
       </c>
-      <c r="T72" s="2">
+      <c r="U72" s="2">
         <v>15</v>
       </c>
-      <c r="U72" s="2">
+      <c r="V72" s="2">
         <v>9</v>
       </c>
-      <c r="V72" s="2"/>
-    </row>
-    <row r="73" spans="1:22">
+      <c r="W72" s="2"/>
+    </row>
+    <row r="73" spans="1:23">
       <c r="A73" s="2">
         <v>9005400</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
+      <c r="C73" s="7">
+        <v>30</v>
+      </c>
       <c r="D73" s="2">
         <v>71</v>
       </c>
@@ -5196,50 +5606,56 @@
         <v>17.73</v>
       </c>
       <c r="J73" s="2">
+        <v>41</v>
+      </c>
+      <c r="K73" s="2">
         <v>33</v>
       </c>
-      <c r="K73" s="2">
+      <c r="L73" s="2">
         <v>82</v>
       </c>
-      <c r="L73" s="2">
+      <c r="M73" s="2">
         <v>17.73</v>
       </c>
-      <c r="M73" s="2">
+      <c r="N73" s="2">
         <v>120</v>
       </c>
-      <c r="N73" s="2">
+      <c r="O73" s="2">
         <v>-5</v>
       </c>
-      <c r="O73" s="2">
+      <c r="P73" s="2">
         <v>110</v>
       </c>
-      <c r="P73" s="2">
-        <v>0</v>
-      </c>
       <c r="Q73" s="2">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2">
         <v>12</v>
       </c>
-      <c r="R73" s="2">
+      <c r="S73" s="2">
         <v>14</v>
       </c>
-      <c r="S73" s="2">
+      <c r="T73" s="2">
         <v>46</v>
       </c>
-      <c r="T73" s="2">
+      <c r="U73" s="2">
         <v>12</v>
       </c>
-      <c r="U73" s="2">
+      <c r="V73" s="2">
         <v>10</v>
       </c>
-      <c r="V73" s="2"/>
-    </row>
-    <row r="74" spans="1:22">
+      <c r="W73" s="2"/>
+    </row>
+    <row r="74" spans="1:23">
       <c r="A74" s="2">
         <v>9209245</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
+      <c r="C74" s="7">
+        <v>27</v>
+      </c>
       <c r="D74" s="2">
         <v>68</v>
       </c>
@@ -5259,50 +5675,56 @@
         <v>10.62</v>
       </c>
       <c r="J74" s="2">
+        <v>25</v>
+      </c>
+      <c r="K74" s="2">
         <v>12</v>
       </c>
-      <c r="K74" s="2">
+      <c r="L74" s="2">
         <v>104</v>
       </c>
-      <c r="L74" s="2">
+      <c r="M74" s="2">
         <v>10.67</v>
       </c>
-      <c r="M74" s="2">
+      <c r="N74" s="2">
         <v>125</v>
       </c>
-      <c r="N74" s="2">
-        <v>0</v>
-      </c>
       <c r="O74" s="2">
+        <v>0</v>
+      </c>
+      <c r="P74" s="2">
         <v>130</v>
       </c>
-      <c r="P74" s="2">
+      <c r="Q74" s="2">
         <v>-5</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="R74" s="2">
         <v>19</v>
       </c>
-      <c r="R74" s="2">
+      <c r="S74" s="2">
         <v>14</v>
       </c>
-      <c r="S74" s="2">
+      <c r="T74" s="2">
         <v>61</v>
-      </c>
-      <c r="T74" s="2">
-        <v>10</v>
       </c>
       <c r="U74" s="2">
         <v>10</v>
       </c>
-      <c r="V74" s="2"/>
-    </row>
-    <row r="75" spans="1:22">
+      <c r="V74" s="2">
+        <v>10</v>
+      </c>
+      <c r="W74" s="2"/>
+    </row>
+    <row r="75" spans="1:23">
       <c r="A75" s="2">
         <v>9301565</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
+      <c r="C75" s="7">
+        <v>29</v>
+      </c>
       <c r="D75" s="2">
         <v>58</v>
       </c>
@@ -5322,50 +5744,56 @@
         <v>14</v>
       </c>
       <c r="J75" s="2">
+        <v>44</v>
+      </c>
+      <c r="K75" s="2">
         <v>22</v>
       </c>
-      <c r="K75" s="2">
+      <c r="L75" s="2">
         <v>127</v>
       </c>
-      <c r="L75" s="2">
+      <c r="M75" s="2">
         <v>9.0500000000000007</v>
       </c>
-      <c r="M75" s="2">
+      <c r="N75" s="2">
         <v>130</v>
       </c>
-      <c r="N75" s="2">
-        <v>0</v>
-      </c>
       <c r="O75" s="2">
+        <v>0</v>
+      </c>
+      <c r="P75" s="2">
         <v>120</v>
       </c>
-      <c r="P75" s="2">
+      <c r="Q75" s="2">
         <v>-20</v>
       </c>
-      <c r="Q75" s="2">
+      <c r="R75" s="2">
         <v>19</v>
       </c>
-      <c r="R75" s="2">
+      <c r="S75" s="2">
         <v>24</v>
       </c>
-      <c r="S75" s="2">
+      <c r="T75" s="2">
         <v>71</v>
       </c>
-      <c r="T75" s="2">
+      <c r="U75" s="2">
         <v>12</v>
       </c>
-      <c r="U75" s="2">
+      <c r="V75" s="2">
         <v>13</v>
       </c>
-      <c r="V75" s="2"/>
-    </row>
-    <row r="76" spans="1:22">
+      <c r="W75" s="2"/>
+    </row>
+    <row r="76" spans="1:23">
       <c r="A76" s="2">
         <v>9301565</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
+      <c r="C76" s="7">
+        <v>29</v>
+      </c>
       <c r="D76" s="2">
         <v>58</v>
       </c>
@@ -5385,50 +5813,56 @@
         <v>15</v>
       </c>
       <c r="J76" s="2">
+        <v>29</v>
+      </c>
+      <c r="K76" s="2">
         <v>15</v>
       </c>
-      <c r="K76" s="2">
+      <c r="L76" s="2">
         <v>127</v>
       </c>
-      <c r="L76" s="2">
+      <c r="M76" s="2">
         <v>8.59</v>
       </c>
-      <c r="M76" s="2">
+      <c r="N76" s="2">
         <v>115</v>
       </c>
-      <c r="N76" s="2">
-        <v>0</v>
-      </c>
       <c r="O76" s="2">
+        <v>0</v>
+      </c>
+      <c r="P76" s="2">
         <v>105</v>
       </c>
-      <c r="P76" s="2">
+      <c r="Q76" s="2">
         <v>-10</v>
       </c>
-      <c r="Q76" s="2">
+      <c r="R76" s="2">
         <v>20</v>
       </c>
-      <c r="R76" s="2">
+      <c r="S76" s="2">
         <v>30</v>
       </c>
-      <c r="S76" s="2">
+      <c r="T76" s="2">
         <v>64</v>
-      </c>
-      <c r="T76" s="2">
-        <v>13</v>
       </c>
       <c r="U76" s="2">
         <v>13</v>
       </c>
-      <c r="V76" s="2"/>
-    </row>
-    <row r="77" spans="1:22">
+      <c r="V76" s="2">
+        <v>13</v>
+      </c>
+      <c r="W76" s="2"/>
+    </row>
+    <row r="77" spans="1:23">
       <c r="A77" s="2">
         <v>9508610</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
+      <c r="C77" s="7">
+        <v>29</v>
+      </c>
       <c r="D77" s="2">
         <v>72</v>
       </c>
@@ -5448,44 +5882,47 @@
         <v>7.96</v>
       </c>
       <c r="J77" s="2">
+        <v>34</v>
+      </c>
+      <c r="K77" s="2">
         <v>17</v>
       </c>
-      <c r="K77" s="2">
+      <c r="L77" s="2">
         <v>115</v>
       </c>
-      <c r="L77" s="2">
+      <c r="M77" s="2">
         <v>8.09</v>
       </c>
-      <c r="M77" s="2">
+      <c r="N77" s="2">
         <v>125</v>
       </c>
-      <c r="N77" s="2">
-        <v>0</v>
-      </c>
       <c r="O77" s="2">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2">
         <v>120</v>
       </c>
-      <c r="P77" s="2">
+      <c r="Q77" s="2">
         <v>-15</v>
       </c>
-      <c r="Q77" s="2">
+      <c r="R77" s="2">
         <v>19</v>
       </c>
-      <c r="R77" s="2">
+      <c r="S77" s="2">
         <v>28</v>
       </c>
-      <c r="S77" s="2">
+      <c r="T77" s="2">
         <v>59</v>
       </c>
-      <c r="T77" s="2">
+      <c r="U77" s="2">
         <v>13</v>
       </c>
-      <c r="U77" s="2">
+      <c r="V77" s="2">
         <v>9</v>
       </c>
-      <c r="V77" s="2"/>
-    </row>
-    <row r="78" spans="1:22">
+      <c r="W77" s="2"/>
+    </row>
+    <row r="78" spans="1:23">
       <c r="A78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -5502,72 +5939,73 @@
       <c r="P78" s="1"/>
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="2"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="2"/>
+      <c r="U78" s="1"/>
       <c r="V78" s="2"/>
-    </row>
-    <row r="79" spans="1:22">
+      <c r="W78" s="2"/>
+    </row>
+    <row r="79" spans="1:23">
       <c r="A79" s="1"/>
-      <c r="S79" s="2"/>
-      <c r="U79" s="2"/>
+      <c r="T79" s="2"/>
       <c r="V79" s="2"/>
-    </row>
-    <row r="80" spans="1:22">
+      <c r="W79" s="2"/>
+    </row>
+    <row r="80" spans="1:23">
       <c r="A80" s="1"/>
-      <c r="S80" s="2"/>
-      <c r="U80" s="2"/>
+      <c r="T80" s="2"/>
       <c r="V80" s="2"/>
-    </row>
-    <row r="81" spans="1:22">
+      <c r="W80" s="2"/>
+    </row>
+    <row r="81" spans="1:23">
       <c r="A81" s="1"/>
-      <c r="S81" s="4"/>
-      <c r="U81" s="1"/>
+      <c r="T81" s="4"/>
       <c r="V81" s="1"/>
-    </row>
-    <row r="82" spans="1:22">
+      <c r="W81" s="1"/>
+    </row>
+    <row r="82" spans="1:23">
       <c r="A82" s="1"/>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:23">
       <c r="A83" s="1"/>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:23">
       <c r="A84" s="1"/>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:23">
       <c r="A85" s="1"/>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:23">
       <c r="A86" s="1"/>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:23">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:23">
       <c r="A88" s="1"/>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:23">
       <c r="A89" s="1"/>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:23">
       <c r="A90" s="1"/>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:23">
       <c r="A91" s="1"/>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:23">
       <c r="A92" s="1"/>
     </row>
-    <row r="93" spans="1:22">
+    <row r="93" spans="1:23">
       <c r="A93" s="1"/>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:23">
       <c r="A94" s="1"/>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:23">
       <c r="A95" s="1"/>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:23">
       <c r="A96" s="1"/>
     </row>
     <row r="97" spans="1:1">

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16DEBDC-FC2C-D64F-B45B-A2E9525ECC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EBF2A6-77B7-6F4B-A1E0-E848DE671D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>年齢（歳）</t>
   </si>
@@ -134,19 +134,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>性別(男０女性１)</t>
-    <rPh sb="0" eb="2">
-      <t>セイベテゥ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>オトコ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>PCS_sum_pre</t>
   </si>
   <si>
@@ -159,6 +146,20 @@
     </rPh>
     <rPh sb="4" eb="7">
       <t>z</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sex</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>女性1 男性０</t>
+    <rPh sb="0" eb="2">
+      <t>ジョセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダンセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -595,11 +596,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:W526"/>
+  <dimension ref="A1:X526"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="23.7109375" customWidth="1"/>
     <col min="16" max="16" width="22.42578125" customWidth="1"/>
@@ -611,15 +613,15 @@
     <col min="23" max="23" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -640,7 +642,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>16</v>
@@ -679,8 +681,11 @@
         <v>27</v>
       </c>
       <c r="W1" s="1"/>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="2">
         <v>110993</v>
       </c>
@@ -748,8 +753,11 @@
         <v>11</v>
       </c>
       <c r="W2" s="1"/>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="X2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="2">
         <v>508469</v>
       </c>
@@ -818,7 +826,7 @@
       </c>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="2">
         <v>910870</v>
       </c>
@@ -887,7 +895,7 @@
       </c>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="2">
         <v>1400396</v>
       </c>
@@ -956,7 +964,7 @@
       </c>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="2">
         <v>1403057</v>
       </c>
@@ -1025,7 +1033,7 @@
       </c>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="2">
         <v>1501605</v>
       </c>
@@ -1094,7 +1102,7 @@
       </c>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="2">
         <v>1900753</v>
       </c>
@@ -1163,7 +1171,7 @@
       </c>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="2">
         <v>1902085</v>
       </c>
@@ -1232,7 +1240,7 @@
       </c>
       <c r="W9" s="2"/>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="2">
         <v>1902300</v>
       </c>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="2">
         <v>1905031</v>
       </c>
@@ -1370,7 +1378,7 @@
       </c>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="2">
         <v>2001975</v>
       </c>
@@ -1439,7 +1447,7 @@
       </c>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="2">
         <v>2002759</v>
       </c>
@@ -1508,7 +1516,7 @@
       </c>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="2">
         <v>2003119</v>
       </c>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="2">
         <v>2003509</v>
       </c>
@@ -1646,7 +1654,7 @@
       </c>
       <c r="W15" s="2"/>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="2">
         <v>2003509</v>
       </c>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EBF2A6-77B7-6F4B-A1E0-E848DE671D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED1BA3-8C8E-9044-BEA9-B5A1E8BB0E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>年齢（歳）</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>10’94</t>
-  </si>
-  <si>
-    <t>11’75</t>
   </si>
   <si>
     <t>16’26</t>
@@ -151,16 +148,6 @@
   </si>
   <si>
     <t>sex</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>女性1 男性０</t>
-    <rPh sb="0" eb="2">
-      <t>ジョセイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ダンセイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -596,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:X526"/>
+  <dimension ref="A1:X522"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -615,13 +602,13 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -642,262 +629,259 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="W1" s="1"/>
       <c r="X1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="2">
-        <v>110993</v>
+        <v>508469</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="7">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E2" s="2">
-        <v>140.5</v>
+        <v>146.5</v>
       </c>
       <c r="F2" s="2">
-        <v>42.4</v>
+        <v>68.5</v>
       </c>
       <c r="G2" s="2">
-        <v>21.47895797</v>
+        <v>31.91650456</v>
       </c>
       <c r="H2" s="2">
-        <v>0.29716981100000001</v>
+        <v>9.1970803000000004E-2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.75</v>
+        <v>14.03</v>
       </c>
       <c r="J2" s="2">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K2" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M2" s="2">
-        <v>9.2200000000000006</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="N2" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="O2" s="2">
         <v>0</v>
       </c>
       <c r="P2" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q2" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R2" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S2" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="T2" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U2" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="V2" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" s="1"/>
-      <c r="X2" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="2">
-        <v>508469</v>
+        <v>910870</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2">
-        <v>146.5</v>
+        <v>154</v>
       </c>
       <c r="F3" s="2">
-        <v>68.5</v>
+        <v>54</v>
       </c>
       <c r="G3" s="2">
-        <v>31.91650456</v>
+        <v>22.769438350000001</v>
       </c>
       <c r="H3" s="2">
-        <v>9.1970803000000004E-2</v>
+        <v>0.27962963000000002</v>
       </c>
       <c r="I3" s="2">
-        <v>14.03</v>
+        <v>9.1</v>
       </c>
       <c r="J3" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L3" s="2">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="M3" s="2">
-        <v>16.170000000000002</v>
+        <v>9.1</v>
       </c>
       <c r="N3" s="2">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="O3" s="2">
         <v>0</v>
       </c>
       <c r="P3" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q3" s="2">
         <v>-10</v>
       </c>
       <c r="R3" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="S3" s="2">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="T3" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="U3" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V3" s="2">
         <v>10</v>
       </c>
-      <c r="W3" s="1"/>
+      <c r="W3" s="2"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="2">
-        <v>910870</v>
+        <v>1400396</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E4" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F4" s="2">
-        <v>54</v>
+        <v>62.75</v>
       </c>
       <c r="G4" s="2">
-        <v>22.769438350000001</v>
+        <v>26.118626429999999</v>
       </c>
       <c r="H4" s="2">
-        <v>0.27962963000000002</v>
+        <v>0.278884462</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>10.55</v>
       </c>
       <c r="J4" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K4" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L4" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M4" s="2">
-        <v>9.1</v>
+        <v>10.55</v>
       </c>
       <c r="N4" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O4" s="2">
         <v>0</v>
       </c>
       <c r="P4" s="2">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="Q4" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R4" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S4" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T4" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U4" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V4" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W4" s="2"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="2">
-        <v>1400396</v>
+        <v>1403057</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -906,67 +890,67 @@
         <v>29</v>
       </c>
       <c r="D5" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F5" s="2">
-        <v>62.75</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="G5" s="2">
-        <v>26.118626429999999</v>
+        <v>30.540439110000001</v>
       </c>
       <c r="H5" s="2">
-        <v>0.278884462</v>
+        <v>0.19047618999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>10.55</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="J5" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K5" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="M5" s="2">
-        <v>10.55</v>
+        <v>18.03</v>
       </c>
       <c r="N5" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
       </c>
       <c r="P5" s="2">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="Q5" s="2">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="R5" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="S5" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="T5" s="2">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="U5" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V5" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W5" s="2"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="2">
-        <v>1403057</v>
+        <v>1501605</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -975,58 +959,58 @@
         <v>29</v>
       </c>
       <c r="D6" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" s="2">
-        <v>146</v>
+        <v>149.5</v>
       </c>
       <c r="F6" s="2">
-        <v>65.099999999999994</v>
+        <v>57.85</v>
       </c>
       <c r="G6" s="2">
-        <v>30.540439110000001</v>
+        <v>25.883379380000001</v>
       </c>
       <c r="H6" s="2">
-        <v>0.19047618999999999</v>
+        <v>6.3958512999999995E-2</v>
       </c>
       <c r="I6" s="2">
-        <v>18.350000000000001</v>
+        <v>27.25</v>
       </c>
       <c r="J6" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K6" s="2">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="L6" s="2">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="M6" s="2">
-        <v>18.03</v>
+        <v>27.25</v>
       </c>
       <c r="N6" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O6" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P6" s="2">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="Q6" s="2">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="R6" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="S6" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="T6" s="2">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="U6" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V6" s="2">
         <v>10</v>
@@ -1035,184 +1019,184 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="2">
-        <v>1501605</v>
+        <v>1900753</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="7">
         <v>29</v>
       </c>
       <c r="D7" s="2">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2">
-        <v>149.5</v>
+        <v>163.19999999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>57.85</v>
+        <v>99.2</v>
       </c>
       <c r="G7" s="2">
-        <v>25.883379380000001</v>
+        <v>37.245290269999998</v>
       </c>
       <c r="H7" s="2">
-        <v>6.3958512999999995E-2</v>
+        <v>0.251008065</v>
       </c>
       <c r="I7" s="2">
-        <v>27.25</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="J7" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K7" s="2">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="M7" s="2">
-        <v>27.25</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="N7" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="O7" s="2">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2">
+        <v>110</v>
+      </c>
+      <c r="Q7" s="2">
         <v>-5</v>
       </c>
-      <c r="P7" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>-10</v>
-      </c>
       <c r="R7" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="S7" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T7" s="2">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="U7" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V7" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W7" s="2"/>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="2">
-        <v>1900753</v>
+        <v>1902085</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2">
-        <v>163.19999999999999</v>
+        <v>156.5</v>
       </c>
       <c r="F8" s="2">
-        <v>99.2</v>
+        <v>60.9</v>
       </c>
       <c r="G8" s="2">
-        <v>37.245290269999998</v>
+        <v>24.865008320000001</v>
       </c>
       <c r="H8" s="2">
-        <v>0.251008065</v>
+        <v>0.26108374400000001</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1300000000000008</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="J8" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K8" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L8" s="2">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="M8" s="2">
-        <v>9.1300000000000008</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="N8" s="2">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2">
         <v>0</v>
       </c>
       <c r="P8" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="2">
         <v>-5</v>
       </c>
       <c r="R8" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S8" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="T8" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U8" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V8" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W8" s="2"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="2">
-        <v>1902085</v>
+        <v>1902300</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2">
         <v>75</v>
       </c>
       <c r="E9" s="2">
-        <v>156.5</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="F9" s="2">
-        <v>60.9</v>
+        <v>62.3</v>
       </c>
       <c r="G9" s="2">
-        <v>24.865008320000001</v>
+        <v>27.215116049999999</v>
       </c>
       <c r="H9" s="2">
-        <v>0.26108374400000001</v>
+        <v>0.170144462</v>
       </c>
       <c r="I9" s="2">
-        <v>8.0399999999999991</v>
+        <v>13.24</v>
       </c>
       <c r="J9" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K9" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L9" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="M9" s="2">
-        <v>8.0399999999999991</v>
+        <v>13.24</v>
       </c>
       <c r="N9" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
@@ -1221,19 +1205,19 @@
         <v>120</v>
       </c>
       <c r="Q9" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R9" s="2">
         <v>22</v>
       </c>
       <c r="S9" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T9" s="2">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="U9" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V9" s="2">
         <v>9</v>
@@ -1242,7 +1226,7 @@
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="2">
-        <v>1902300</v>
+        <v>1905031</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1254,34 +1238,34 @@
         <v>75</v>
       </c>
       <c r="E10" s="2">
-        <v>151.30000000000001</v>
+        <v>148</v>
       </c>
       <c r="F10" s="2">
-        <v>62.3</v>
+        <v>43.5</v>
       </c>
       <c r="G10" s="2">
-        <v>27.215116049999999</v>
+        <v>19.859386409999999</v>
       </c>
       <c r="H10" s="2">
-        <v>0.170144462</v>
+        <v>8.045977E-2</v>
       </c>
       <c r="I10" s="2">
-        <v>13.24</v>
+        <v>11.05</v>
       </c>
       <c r="J10" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K10" s="2">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L10" s="2">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="M10" s="2">
-        <v>13.24</v>
+        <v>11.05</v>
       </c>
       <c r="N10" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O10" s="2">
         <v>0</v>
@@ -1290,28 +1274,28 @@
         <v>120</v>
       </c>
       <c r="Q10" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R10" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S10" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="T10" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="U10" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V10" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W10" s="2"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="2">
-        <v>1905031</v>
+        <v>2001975</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1320,232 +1304,232 @@
         <v>29</v>
       </c>
       <c r="D11" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2">
-        <v>148</v>
+        <v>157.9</v>
       </c>
       <c r="F11" s="2">
-        <v>43.5</v>
+        <v>92.2</v>
       </c>
       <c r="G11" s="2">
-        <v>19.859386409999999</v>
+        <v>36.979979069999999</v>
       </c>
       <c r="H11" s="2">
-        <v>8.045977E-2</v>
+        <v>0.221258134</v>
       </c>
       <c r="I11" s="2">
-        <v>11.05</v>
+        <v>9.48</v>
       </c>
       <c r="J11" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="L11" s="2">
+        <v>130</v>
+      </c>
+      <c r="M11" s="2">
+        <v>9.48</v>
+      </c>
+      <c r="N11" s="2">
         <v>125</v>
       </c>
-      <c r="M11" s="2">
-        <v>11.05</v>
-      </c>
-      <c r="N11" s="2">
-        <v>115</v>
-      </c>
       <c r="O11" s="2">
         <v>0</v>
       </c>
       <c r="P11" s="2">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q11" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="R11" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S11" s="2">
         <v>28</v>
       </c>
       <c r="T11" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="U11" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V11" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W11" s="2"/>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="2">
-        <v>2001975</v>
+        <v>2002759</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2">
-        <v>157.9</v>
+        <v>163</v>
       </c>
       <c r="F12" s="2">
-        <v>92.2</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="G12" s="2">
-        <v>36.979979069999999</v>
+        <v>30.33610599</v>
       </c>
       <c r="H12" s="2">
-        <v>0.221258134</v>
+        <v>6.0794044999999998E-2</v>
       </c>
       <c r="I12" s="2">
-        <v>9.48</v>
+        <v>35.83</v>
       </c>
       <c r="J12" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K12" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L12" s="2">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="M12" s="2">
-        <v>9.48</v>
+        <v>32.07</v>
       </c>
       <c r="N12" s="2">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="O12" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="P12" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R12" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="S12" s="2">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T12" s="2">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="U12" s="2">
         <v>14</v>
       </c>
       <c r="V12" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W12" s="2"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="2">
-        <v>2002759</v>
+        <v>2003119</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" s="7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2">
         <v>69</v>
       </c>
       <c r="E13" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F13" s="2">
-        <v>80.599999999999994</v>
+        <v>78.3</v>
       </c>
       <c r="G13" s="2">
-        <v>30.33610599</v>
+        <v>31.765994559999999</v>
       </c>
       <c r="H13" s="2">
-        <v>6.0794044999999998E-2</v>
+        <v>0.18263090700000001</v>
       </c>
       <c r="I13" s="2">
-        <v>35.83</v>
+        <v>8.59</v>
       </c>
       <c r="J13" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K13" s="2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="M13" s="2">
-        <v>32.07</v>
+        <v>8.89</v>
       </c>
       <c r="N13" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="O13" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="P13" s="2">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="Q13" s="2">
         <v>-10</v>
       </c>
       <c r="R13" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="S13" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T13" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="U13" s="2">
         <v>14</v>
       </c>
       <c r="V13" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W13" s="2"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="2">
-        <v>2003119</v>
+        <v>2003509</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="7">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2">
+        <v>67</v>
+      </c>
+      <c r="E14" s="2">
+        <v>162</v>
+      </c>
+      <c r="F14" s="2">
+        <v>63.6</v>
+      </c>
+      <c r="G14" s="2">
+        <v>24.234110650000002</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.117924528</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.39</v>
+      </c>
+      <c r="J14" s="2">
         <v>29</v>
-      </c>
-      <c r="D14" s="2">
-        <v>69</v>
-      </c>
-      <c r="E14" s="2">
-        <v>157</v>
-      </c>
-      <c r="F14" s="2">
-        <v>78.3</v>
-      </c>
-      <c r="G14" s="2">
-        <v>31.765994559999999</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0.18263090700000001</v>
-      </c>
-      <c r="I14" s="2">
-        <v>8.59</v>
-      </c>
-      <c r="J14" s="2">
-        <v>24</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -1554,31 +1538,31 @@
         <v>114</v>
       </c>
       <c r="M14" s="2">
-        <v>8.89</v>
+        <v>9.39</v>
       </c>
       <c r="N14" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
       </c>
       <c r="P14" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Q14" s="2">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="R14" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S14" s="2">
         <v>30</v>
       </c>
       <c r="T14" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U14" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V14" s="2">
         <v>9</v>
@@ -1602,52 +1586,52 @@
         <v>162</v>
       </c>
       <c r="F15" s="2">
-        <v>63.6</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2">
-        <v>24.234110650000002</v>
+        <v>24.767565919999999</v>
       </c>
       <c r="H15" s="2">
-        <v>0.117924528</v>
+        <v>0.127692308</v>
       </c>
       <c r="I15" s="2">
-        <v>9.39</v>
+        <v>10.42</v>
       </c>
       <c r="J15" s="2">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K15" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L15" s="2">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="M15" s="2">
-        <v>9.39</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="N15" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
       </c>
       <c r="P15" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="Q15" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R15" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S15" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T15" s="2">
         <v>55</v>
       </c>
       <c r="U15" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V15" s="2">
         <v>9</v>
@@ -1656,43 +1640,43 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="2">
-        <v>2003509</v>
+        <v>2003643</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="7">
+        <v>25</v>
+      </c>
+      <c r="D16" s="2">
+        <v>78</v>
+      </c>
+      <c r="E16" s="2">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="F16" s="2">
+        <v>51.1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>19.886293980000001</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0.219178082</v>
+      </c>
+      <c r="I16" s="2">
+        <v>10.17</v>
+      </c>
+      <c r="J16" s="2">
         <v>28</v>
       </c>
-      <c r="D16" s="2">
-        <v>67</v>
-      </c>
-      <c r="E16" s="2">
-        <v>162</v>
-      </c>
-      <c r="F16" s="2">
-        <v>65</v>
-      </c>
-      <c r="G16" s="2">
-        <v>24.767565919999999</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0.127692308</v>
-      </c>
-      <c r="I16" s="2">
-        <v>10.42</v>
-      </c>
-      <c r="J16" s="2">
-        <v>49</v>
-      </c>
       <c r="K16" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L16" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M16" s="2">
-        <v>8.7200000000000006</v>
+        <v>11.2</v>
       </c>
       <c r="N16" s="2">
         <v>130</v>
@@ -1701,67 +1685,67 @@
         <v>0</v>
       </c>
       <c r="P16" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Q16" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R16" s="2">
+        <v>17</v>
+      </c>
+      <c r="S16" s="2">
+        <v>24</v>
+      </c>
+      <c r="T16" s="2">
+        <v>69</v>
+      </c>
+      <c r="U16" s="2">
+        <v>15</v>
+      </c>
+      <c r="V16" s="2">
         <v>10</v>
-      </c>
-      <c r="R16" s="2">
-        <v>24</v>
-      </c>
-      <c r="S16" s="2">
-        <v>40</v>
-      </c>
-      <c r="T16" s="2">
-        <v>55</v>
-      </c>
-      <c r="U16" s="2">
-        <v>11</v>
-      </c>
-      <c r="V16" s="2">
-        <v>9</v>
       </c>
       <c r="W16" s="2"/>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="2">
-        <v>2003643</v>
+        <v>2004241</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" s="7">
+        <v>28</v>
+      </c>
+      <c r="D17" s="2">
+        <v>81</v>
+      </c>
+      <c r="E17" s="2">
+        <v>150</v>
+      </c>
+      <c r="F17" s="2">
+        <v>56</v>
+      </c>
+      <c r="G17" s="2">
+        <v>24.88888889</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.15178571399999999</v>
+      </c>
+      <c r="I17" s="2">
+        <v>15.04</v>
+      </c>
+      <c r="J17" s="2">
+        <v>35</v>
+      </c>
+      <c r="K17" s="2">
         <v>25</v>
       </c>
-      <c r="D17" s="2">
-        <v>78</v>
-      </c>
-      <c r="E17" s="2">
-        <v>160.30000000000001</v>
-      </c>
-      <c r="F17" s="2">
-        <v>51.1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>19.886293980000001</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0.219178082</v>
-      </c>
-      <c r="I17" s="2">
-        <v>10.17</v>
-      </c>
-      <c r="J17" s="2">
-        <v>28</v>
-      </c>
-      <c r="K17" s="2">
-        <v>12</v>
-      </c>
       <c r="L17" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="M17" s="2">
-        <v>11.2</v>
+        <v>15.04</v>
       </c>
       <c r="N17" s="2">
         <v>130</v>
@@ -1770,22 +1754,22 @@
         <v>0</v>
       </c>
       <c r="P17" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="2">
         <v>-10</v>
       </c>
       <c r="R17" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S17" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T17" s="2">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="U17" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V17" s="2">
         <v>10</v>
@@ -1794,67 +1778,67 @@
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="2">
-        <v>2004241</v>
+        <v>2004528</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" s="7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F18" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G18" s="2">
-        <v>24.88888889</v>
+        <v>26.56434475</v>
       </c>
       <c r="H18" s="2">
-        <v>0.15178571399999999</v>
+        <v>0.242857143</v>
       </c>
       <c r="I18" s="2">
-        <v>15.04</v>
+        <v>8.9</v>
       </c>
       <c r="J18" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K18" s="2">
         <v>25</v>
       </c>
       <c r="L18" s="2">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="M18" s="2">
-        <v>15.04</v>
+        <v>8.9</v>
       </c>
       <c r="N18" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O18" s="2">
         <v>0</v>
       </c>
       <c r="P18" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="Q18" s="2">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="R18" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S18" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T18" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="U18" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V18" s="2">
         <v>10</v>
@@ -1863,181 +1847,181 @@
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="2">
-        <v>2004528</v>
+        <v>2101216</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F19" s="2">
-        <v>63</v>
+        <v>70.5</v>
       </c>
       <c r="G19" s="2">
-        <v>26.56434475</v>
+        <v>27.19802477</v>
       </c>
       <c r="H19" s="2">
-        <v>0.242857143</v>
-      </c>
-      <c r="I19" s="2">
-        <v>8.9</v>
+        <v>0.19432624100000001</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="J19" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="K19" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L19" s="2">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="M19" s="2">
-        <v>8.9</v>
+        <v>11.59</v>
       </c>
       <c r="N19" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O19" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="P19" s="2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Q19" s="2">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="R19" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S19" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T19" s="2">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="U19" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V19" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19" s="2"/>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="2">
-        <v>2101216</v>
+        <v>2101383</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
-        <v>161</v>
+        <v>155.4</v>
       </c>
       <c r="F20" s="2">
-        <v>70.5</v>
+        <v>61.85</v>
       </c>
       <c r="G20" s="2">
-        <v>27.19802477</v>
+        <v>25.611656889999999</v>
       </c>
       <c r="H20" s="2">
-        <v>0.19432624100000001</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>6</v>
+        <v>0.223120453</v>
+      </c>
+      <c r="I20" s="2">
+        <v>9.89</v>
       </c>
       <c r="J20" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K20" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L20" s="2">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="M20" s="2">
-        <v>11.59</v>
+        <v>9.9</v>
       </c>
       <c r="N20" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O20" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q20" s="2">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="R20" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S20" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T20" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="U20" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V20" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W20" s="2"/>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="2">
-        <v>2101383</v>
+        <v>2101501</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E21" s="2">
-        <v>155.4</v>
+        <v>153.19999999999999</v>
       </c>
       <c r="F21" s="2">
-        <v>61.85</v>
+        <v>66.7</v>
       </c>
       <c r="G21" s="2">
-        <v>25.611656889999999</v>
+        <v>28.418968020000001</v>
       </c>
       <c r="H21" s="2">
-        <v>0.223120453</v>
+        <v>0.28185906999999999</v>
       </c>
       <c r="I21" s="2">
-        <v>9.89</v>
+        <v>9.31</v>
       </c>
       <c r="J21" s="2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K21" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L21" s="2">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="M21" s="2">
-        <v>9.9</v>
+        <v>10.31</v>
       </c>
       <c r="N21" s="2">
         <v>120</v>
@@ -2046,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q21" s="2">
         <v>-5</v>
@@ -2055,58 +2039,58 @@
         <v>17</v>
       </c>
       <c r="S21" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="T21" s="2">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="U21" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V21" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W21" s="2"/>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="2">
-        <v>2101501</v>
+        <v>2101972</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" s="7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2">
-        <v>153.19999999999999</v>
+        <v>149</v>
       </c>
       <c r="F22" s="2">
-        <v>66.7</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2">
-        <v>28.418968020000001</v>
+        <v>27.926669969999999</v>
       </c>
       <c r="H22" s="2">
-        <v>0.28185906999999999</v>
+        <v>0.212903226</v>
       </c>
       <c r="I22" s="2">
-        <v>9.31</v>
+        <v>8.39</v>
       </c>
       <c r="J22" s="2">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K22" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="M22" s="2">
-        <v>10.31</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="N22" s="2">
         <v>120</v>
@@ -2115,22 +2099,22 @@
         <v>0</v>
       </c>
       <c r="P22" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Q22" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R22" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="S22" s="2">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="T22" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U22" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V22" s="2">
         <v>9</v>
@@ -2139,46 +2123,46 @@
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="2">
-        <v>2101972</v>
+        <v>2103619</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="F23" s="2">
-        <v>62</v>
+        <v>48.8</v>
       </c>
       <c r="G23" s="2">
-        <v>27.926669969999999</v>
+        <v>22.129261190000001</v>
       </c>
       <c r="H23" s="2">
-        <v>0.212903226</v>
+        <v>0.16598360700000001</v>
       </c>
       <c r="I23" s="2">
-        <v>8.39</v>
+        <v>19.46</v>
       </c>
       <c r="J23" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="K23" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="M23" s="2">
-        <v>9.0500000000000007</v>
+        <v>19.46</v>
       </c>
       <c r="N23" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O23" s="2">
         <v>0</v>
@@ -2187,19 +2171,19 @@
         <v>125</v>
       </c>
       <c r="Q23" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R23" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S23" s="2">
         <v>36</v>
       </c>
       <c r="T23" s="2">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="U23" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V23" s="2">
         <v>9</v>
@@ -2208,67 +2192,67 @@
     </row>
     <row r="24" spans="1:23">
       <c r="A24" s="2">
-        <v>2103619</v>
+        <v>2201384</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2">
-        <v>148.5</v>
+        <v>153.5</v>
       </c>
       <c r="F24" s="2">
-        <v>48.8</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2">
-        <v>22.129261190000001</v>
+        <v>22.493607359999999</v>
       </c>
       <c r="H24" s="2">
-        <v>0.16598360700000001</v>
-      </c>
-      <c r="I24" s="2">
-        <v>19.46</v>
+        <v>0.22452830200000001</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="J24" s="2">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L24" s="2">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="M24" s="2">
-        <v>19.46</v>
+        <v>10.3</v>
       </c>
       <c r="N24" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O24" s="2">
         <v>0</v>
       </c>
       <c r="P24" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Q24" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R24" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S24" s="2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="T24" s="2">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="U24" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V24" s="2">
         <v>9</v>
@@ -2277,67 +2261,67 @@
     </row>
     <row r="25" spans="1:23">
       <c r="A25" s="2">
-        <v>2201384</v>
+        <v>2201884</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2">
-        <v>153.5</v>
+        <v>145.5</v>
       </c>
       <c r="F25" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G25" s="2">
-        <v>22.493607359999999</v>
+        <v>27.396936740000001</v>
       </c>
       <c r="H25" s="2">
-        <v>0.22452830200000001</v>
-      </c>
-      <c r="I25" s="2" t="s">
+        <v>0.16206896600000001</v>
+      </c>
+      <c r="I25" s="2">
+        <v>8.77</v>
+      </c>
+      <c r="J25" s="2">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2">
         <v>7</v>
       </c>
-      <c r="J25" s="2">
-        <v>28</v>
-      </c>
-      <c r="K25" s="2">
-        <v>13</v>
-      </c>
       <c r="L25" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="M25" s="2">
-        <v>10.3</v>
+        <v>8.77</v>
       </c>
       <c r="N25" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O25" s="2">
         <v>0</v>
       </c>
       <c r="P25" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Q25" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="R25" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S25" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T25" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="U25" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V25" s="2">
         <v>9</v>
@@ -2346,115 +2330,115 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="2">
-        <v>2201884</v>
+        <v>2202167</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" s="7">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2">
-        <v>145.5</v>
+        <v>146.5</v>
       </c>
       <c r="F26" s="2">
         <v>58</v>
       </c>
       <c r="G26" s="2">
-        <v>27.396936740000001</v>
+        <v>27.02419364</v>
       </c>
       <c r="H26" s="2">
-        <v>0.16206896600000001</v>
+        <v>0.22068965500000001</v>
       </c>
       <c r="I26" s="2">
-        <v>8.77</v>
+        <v>10.24</v>
       </c>
       <c r="J26" s="2">
+        <v>32</v>
+      </c>
+      <c r="K26" s="2">
         <v>17</v>
       </c>
-      <c r="K26" s="2">
-        <v>7</v>
-      </c>
       <c r="L26" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M26" s="2">
-        <v>8.77</v>
+        <v>10.69</v>
       </c>
       <c r="N26" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
       </c>
       <c r="P26" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R26" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S26" s="2">
         <v>26</v>
       </c>
       <c r="T26" s="2">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="U26" s="2">
         <v>15</v>
       </c>
       <c r="V26" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W26" s="2"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="2">
-        <v>2202167</v>
+        <v>2202692</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" s="7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2">
-        <v>146.5</v>
+        <v>150</v>
       </c>
       <c r="F27" s="2">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="G27" s="2">
-        <v>27.02419364</v>
+        <v>20.222222219999999</v>
       </c>
       <c r="H27" s="2">
-        <v>0.22068965500000001</v>
+        <v>0.19780219800000001</v>
       </c>
       <c r="I27" s="2">
-        <v>10.24</v>
+        <v>10.39</v>
       </c>
       <c r="J27" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K27" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="M27" s="2">
-        <v>10.69</v>
+        <v>10.35</v>
       </c>
       <c r="N27" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O27" s="2">
         <v>0</v>
@@ -2463,13 +2447,13 @@
         <v>110</v>
       </c>
       <c r="Q27" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R27" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S27" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T27" s="2">
         <v>69</v>
@@ -2478,13 +2462,13 @@
         <v>15</v>
       </c>
       <c r="V27" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W27" s="2"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="2">
-        <v>2202692</v>
+        <v>2203257</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -2493,34 +2477,34 @@
         <v>29</v>
       </c>
       <c r="D28" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2">
-        <v>45.5</v>
+        <v>53.05</v>
       </c>
       <c r="G28" s="2">
-        <v>20.222222219999999</v>
+        <v>22.66222393</v>
       </c>
       <c r="H28" s="2">
-        <v>0.19780219800000001</v>
-      </c>
-      <c r="I28" s="2">
-        <v>10.39</v>
+        <v>0.20923656900000001</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="J28" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K28" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M28" s="2">
-        <v>10.35</v>
+        <v>9.59</v>
       </c>
       <c r="N28" s="2">
         <v>125</v>
@@ -2529,160 +2513,160 @@
         <v>0</v>
       </c>
       <c r="P28" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R28" s="2">
         <v>23</v>
       </c>
       <c r="S28" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T28" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U28" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V28" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W28" s="2"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="2">
-        <v>2203257</v>
+        <v>2203370</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2">
-        <v>153</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="F29" s="2">
-        <v>53.05</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="G29" s="2">
-        <v>22.66222393</v>
+        <v>29.828657549999999</v>
       </c>
       <c r="H29" s="2">
-        <v>0.20923656900000001</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>8</v>
+        <v>0.139800285</v>
+      </c>
+      <c r="I29" s="2">
+        <v>13.29</v>
       </c>
       <c r="J29" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K29" s="2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L29" s="2">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="M29" s="2">
-        <v>9.59</v>
+        <v>13.29</v>
       </c>
       <c r="N29" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O29" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P29" s="2">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="Q29" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R29" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S29" s="2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="T29" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="U29" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V29" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W29" s="2"/>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="2">
-        <v>2203370</v>
+        <v>2204023</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2">
-        <v>153.30000000000001</v>
+        <v>153</v>
       </c>
       <c r="F30" s="2">
-        <v>70.099999999999994</v>
+        <v>73.5</v>
       </c>
       <c r="G30" s="2">
-        <v>29.828657549999999</v>
+        <v>31.398180190000001</v>
       </c>
       <c r="H30" s="2">
-        <v>0.139800285</v>
-      </c>
-      <c r="I30" s="2">
-        <v>13.29</v>
+        <v>0.30204081599999999</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="J30" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K30" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L30" s="2">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="M30" s="2">
-        <v>13.29</v>
+        <v>10.94</v>
       </c>
       <c r="N30" s="2">
+        <v>125</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2">
         <v>115</v>
-      </c>
-      <c r="O30" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P30" s="2">
-        <v>120</v>
       </c>
       <c r="Q30" s="2">
         <v>-15</v>
       </c>
       <c r="R30" s="2">
+        <v>18</v>
+      </c>
+      <c r="S30" s="2">
+        <v>26</v>
+      </c>
+      <c r="T30" s="2">
+        <v>66</v>
+      </c>
+      <c r="U30" s="2">
         <v>12</v>
-      </c>
-      <c r="S30" s="2">
-        <v>14</v>
-      </c>
-      <c r="T30" s="2">
-        <v>28</v>
-      </c>
-      <c r="U30" s="2">
-        <v>15</v>
       </c>
       <c r="V30" s="2">
         <v>11</v>
@@ -2691,7 +2675,7 @@
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="2">
-        <v>2204023</v>
+        <v>2204202</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2700,34 +2684,34 @@
         <v>29</v>
       </c>
       <c r="D31" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F31" s="2">
-        <v>73.5</v>
+        <v>52.5</v>
       </c>
       <c r="G31" s="2">
-        <v>31.398180190000001</v>
+        <v>23.333333329999999</v>
       </c>
       <c r="H31" s="2">
-        <v>0.30204081599999999</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>9</v>
+        <v>0.29142857100000003</v>
+      </c>
+      <c r="I31" s="2">
+        <v>11.23</v>
       </c>
       <c r="J31" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K31" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="M31" s="2">
-        <v>10.94</v>
+        <v>11.23</v>
       </c>
       <c r="N31" s="2">
         <v>125</v>
@@ -2736,31 +2720,31 @@
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R31" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S31" s="2">
         <v>26</v>
       </c>
       <c r="T31" s="2">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="U31" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V31" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W31" s="2"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="2">
-        <v>2204202</v>
+        <v>2204531</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -2769,127 +2753,127 @@
         <v>29</v>
       </c>
       <c r="D32" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2">
-        <v>150</v>
+        <v>142.19999999999999</v>
       </c>
       <c r="F32" s="2">
-        <v>52.5</v>
+        <v>39.9</v>
       </c>
       <c r="G32" s="2">
-        <v>23.333333329999999</v>
+        <v>19.732117949999999</v>
       </c>
       <c r="H32" s="2">
-        <v>0.29142857100000003</v>
+        <v>0.27819548900000002</v>
       </c>
       <c r="I32" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="J32" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K32" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L32" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="M32" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="N32" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O32" s="2">
         <v>0</v>
       </c>
       <c r="P32" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q32" s="2">
         <v>-5</v>
       </c>
       <c r="R32" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S32" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T32" s="2">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="U32" s="2">
         <v>13</v>
       </c>
       <c r="V32" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32" s="2"/>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="2">
-        <v>2204531</v>
+        <v>2204625</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D33" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2">
-        <v>142.19999999999999</v>
+        <v>177</v>
       </c>
       <c r="F33" s="2">
-        <v>39.9</v>
+        <v>104</v>
       </c>
       <c r="G33" s="2">
-        <v>19.732117949999999</v>
+        <v>33.196080309999999</v>
       </c>
       <c r="H33" s="2">
-        <v>0.27819548900000002</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="J33" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K33" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L33" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M33" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="N33" s="2">
         <v>120</v>
       </c>
       <c r="O33" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="P33" s="2">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="Q33" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R33" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S33" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T33" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="U33" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V33" s="2">
         <v>9</v>
@@ -2898,67 +2882,67 @@
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="2">
-        <v>2204625</v>
+        <v>2204766</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F34" s="2">
-        <v>104</v>
+        <v>57.8</v>
       </c>
       <c r="G34" s="2">
-        <v>33.196080309999999</v>
+        <v>26.748114210000001</v>
       </c>
       <c r="H34" s="2">
-        <v>0</v>
+        <v>0.150519031</v>
       </c>
       <c r="I34" s="2">
-        <v>10.69</v>
+        <v>10.54</v>
       </c>
       <c r="J34" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K34" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L34" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M34" s="2">
-        <v>10.69</v>
+        <v>9.49</v>
       </c>
       <c r="N34" s="2">
+        <v>130</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2">
         <v>120</v>
-      </c>
-      <c r="O34" s="2">
-        <v>-10</v>
-      </c>
-      <c r="P34" s="2">
-        <v>140</v>
       </c>
       <c r="Q34" s="2">
         <v>-10</v>
       </c>
       <c r="R34" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S34" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="T34" s="2">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U34" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V34" s="2">
         <v>9</v>
@@ -2967,283 +2951,283 @@
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="2">
-        <v>2204766</v>
+        <v>2300143</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D35" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2">
-        <v>147</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="F35" s="2">
-        <v>57.8</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G35" s="2">
-        <v>26.748114210000001</v>
+        <v>27.794048960000001</v>
       </c>
       <c r="H35" s="2">
-        <v>0.150519031</v>
+        <v>0.19440353499999999</v>
       </c>
       <c r="I35" s="2">
-        <v>10.54</v>
+        <v>12.89</v>
       </c>
       <c r="J35" s="2">
+        <v>48</v>
+      </c>
+      <c r="K35" s="2">
         <v>12</v>
       </c>
-      <c r="K35" s="2">
-        <v>24</v>
-      </c>
       <c r="L35" s="2">
+        <v>125</v>
+      </c>
+      <c r="M35" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="N35" s="2">
         <v>110</v>
       </c>
-      <c r="M35" s="2">
-        <v>9.49</v>
-      </c>
-      <c r="N35" s="2">
-        <v>130</v>
-      </c>
       <c r="O35" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P35" s="2">
         <v>120</v>
       </c>
       <c r="Q35" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R35" s="2">
         <v>20</v>
       </c>
       <c r="S35" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="T35" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U35" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V35" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W35" s="2"/>
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="2">
-        <v>2300143</v>
+        <v>2300176</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2">
-        <v>156.30000000000001</v>
+        <v>152.5</v>
       </c>
       <c r="F36" s="2">
-        <v>67.900000000000006</v>
+        <v>64.8</v>
       </c>
       <c r="G36" s="2">
-        <v>27.794048960000001</v>
+        <v>27.86347756</v>
       </c>
       <c r="H36" s="2">
-        <v>0.19440353499999999</v>
+        <v>0.17129629599999999</v>
       </c>
       <c r="I36" s="2">
-        <v>12.89</v>
+        <v>11.68</v>
       </c>
       <c r="J36" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K36" s="2">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L36" s="2">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="M36" s="2">
-        <v>12.56</v>
+        <v>11.68</v>
       </c>
       <c r="N36" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O36" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P36" s="2">
         <v>120</v>
       </c>
       <c r="Q36" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R36" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" s="2">
         <v>20</v>
       </c>
-      <c r="S36" s="2">
-        <v>32</v>
-      </c>
       <c r="T36" s="2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="U36" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V36" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W36" s="2"/>
     </row>
     <row r="37" spans="1:23">
       <c r="A37" s="2">
-        <v>2300143</v>
+        <v>2300484</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="7">
+        <v>29</v>
+      </c>
+      <c r="D37" s="2">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2">
+        <v>146</v>
+      </c>
+      <c r="F37" s="2">
+        <v>58</v>
+      </c>
+      <c r="G37" s="2">
+        <v>27.209607810000001</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0.212068966</v>
+      </c>
+      <c r="I37" s="2">
+        <v>13.33</v>
+      </c>
+      <c r="J37" s="2">
         <v>24</v>
       </c>
-      <c r="D37" s="2">
-        <v>79</v>
-      </c>
-      <c r="E37" s="2">
-        <v>156.5</v>
-      </c>
-      <c r="F37" s="2">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="G37" s="2">
-        <v>26.9881289</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0.14372163399999999</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J37" s="2">
-        <v>44</v>
-      </c>
       <c r="K37" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L37" s="2">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="M37" s="2">
-        <v>11.75</v>
+        <v>13.33</v>
       </c>
       <c r="N37" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O37" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P37" s="2">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R37" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S37" s="2">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="T37" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="U37" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V37" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W37" s="2"/>
     </row>
     <row r="38" spans="1:23">
       <c r="A38" s="2">
-        <v>2300176</v>
+        <v>2300760</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="7">
         <v>30</v>
       </c>
       <c r="D38" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E38" s="2">
-        <v>152.5</v>
+        <v>164</v>
       </c>
       <c r="F38" s="2">
-        <v>64.8</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="G38" s="2">
-        <v>27.86347756</v>
+        <v>24.390243900000002</v>
       </c>
       <c r="H38" s="2">
-        <v>0.17129629599999999</v>
+        <v>0.33231707300000002</v>
       </c>
       <c r="I38" s="2">
-        <v>11.68</v>
+        <v>10.94</v>
       </c>
       <c r="J38" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K38" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="L38" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M38" s="2">
-        <v>11.68</v>
+        <v>12.29</v>
       </c>
       <c r="N38" s="2">
         <v>115</v>
       </c>
       <c r="O38" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P38" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q38" s="2">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="R38" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="S38" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T38" s="2">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="U38" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V38" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W38" s="2"/>
     </row>
     <row r="39" spans="1:23">
       <c r="A39" s="2">
-        <v>2300484</v>
+        <v>2301202</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -3252,136 +3236,136 @@
         <v>29</v>
       </c>
       <c r="D39" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E39" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="2">
-        <v>58</v>
+        <v>47.15</v>
       </c>
       <c r="G39" s="2">
-        <v>27.209607810000001</v>
+        <v>22.425683710000001</v>
       </c>
       <c r="H39" s="2">
-        <v>0.212068966</v>
+        <v>9.3319193999999994E-2</v>
       </c>
       <c r="I39" s="2">
-        <v>13.33</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="J39" s="2">
+        <v>34</v>
+      </c>
+      <c r="K39" s="2">
+        <v>6</v>
+      </c>
+      <c r="L39" s="2">
+        <v>108</v>
+      </c>
+      <c r="M39" s="2">
+        <v>9.31</v>
+      </c>
+      <c r="N39" s="2">
+        <v>125</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>15</v>
+      </c>
+      <c r="R39" s="2">
+        <v>18</v>
+      </c>
+      <c r="S39" s="2">
         <v>24</v>
       </c>
-      <c r="K39" s="2">
-        <v>17</v>
-      </c>
-      <c r="L39" s="2">
-        <v>121</v>
-      </c>
-      <c r="M39" s="2">
-        <v>13.33</v>
-      </c>
-      <c r="N39" s="2">
-        <v>120</v>
-      </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2">
-        <v>135</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R39" s="2">
-        <v>22</v>
-      </c>
-      <c r="S39" s="2">
-        <v>20</v>
-      </c>
       <c r="T39" s="2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="U39" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V39" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W39" s="2"/>
     </row>
     <row r="40" spans="1:23">
       <c r="A40" s="2">
-        <v>2300760</v>
+        <v>2301202</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D40" s="2">
         <v>74</v>
       </c>
       <c r="E40" s="2">
-        <v>164</v>
+        <v>145.5</v>
       </c>
       <c r="F40" s="2">
-        <v>65.599999999999994</v>
+        <v>49.1</v>
       </c>
       <c r="G40" s="2">
-        <v>24.390243900000002</v>
+        <v>23.19292403</v>
       </c>
       <c r="H40" s="2">
-        <v>0.33231707300000002</v>
+        <v>0.15071283099999999</v>
       </c>
       <c r="I40" s="2">
-        <v>10.94</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="J40" s="2">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K40" s="2">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="M40" s="2">
-        <v>12.29</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="N40" s="2">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="O40" s="2">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2">
+        <v>125</v>
+      </c>
+      <c r="Q40" s="2">
         <v>-5</v>
       </c>
-      <c r="P40" s="2">
-        <v>100</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>-20</v>
-      </c>
       <c r="R40" s="2">
+        <v>22</v>
+      </c>
+      <c r="S40" s="2">
+        <v>28</v>
+      </c>
+      <c r="T40" s="2">
+        <v>71</v>
+      </c>
+      <c r="U40" s="2">
+        <v>11</v>
+      </c>
+      <c r="V40" s="2">
         <v>8</v>
-      </c>
-      <c r="S40" s="2">
-        <v>24</v>
-      </c>
-      <c r="T40" s="2">
-        <v>62</v>
-      </c>
-      <c r="U40" s="2">
-        <v>14</v>
-      </c>
-      <c r="V40" s="2">
-        <v>11</v>
       </c>
       <c r="W40" s="2"/>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="2">
-        <v>2301202</v>
+        <v>2301430</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -3390,136 +3374,136 @@
         <v>29</v>
       </c>
       <c r="D41" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2">
-        <v>145</v>
+        <v>145.30000000000001</v>
       </c>
       <c r="F41" s="2">
-        <v>47.15</v>
+        <v>68.5</v>
       </c>
       <c r="G41" s="2">
-        <v>22.425683710000001</v>
+        <v>32.445863959999997</v>
       </c>
       <c r="H41" s="2">
-        <v>9.3319193999999994E-2</v>
-      </c>
-      <c r="I41" s="2">
-        <v>9.3800000000000008</v>
+        <v>0.12700729899999999</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="J41" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K41" s="2">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L41" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M41" s="2">
-        <v>9.31</v>
+        <v>16.91</v>
       </c>
       <c r="N41" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O41" s="2">
         <v>0</v>
       </c>
       <c r="P41" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q41" s="2">
+        <v>-15</v>
+      </c>
+      <c r="R41" s="2">
+        <v>17</v>
+      </c>
+      <c r="S41" s="2">
+        <v>26</v>
+      </c>
+      <c r="T41" s="2">
+        <v>57</v>
+      </c>
+      <c r="U41" s="2">
         <v>15</v>
       </c>
-      <c r="R41" s="2">
-        <v>18</v>
-      </c>
-      <c r="S41" s="2">
-        <v>24</v>
-      </c>
-      <c r="T41" s="2">
-        <v>56</v>
-      </c>
-      <c r="U41" s="2">
-        <v>12</v>
-      </c>
       <c r="V41" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W41" s="2"/>
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="2">
-        <v>2301202</v>
+        <v>2301506</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" s="7">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D42" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2">
-        <v>145.5</v>
+        <v>158</v>
       </c>
       <c r="F42" s="2">
-        <v>49.1</v>
+        <v>76.7</v>
       </c>
       <c r="G42" s="2">
-        <v>23.19292403</v>
+        <v>30.724242910000001</v>
       </c>
       <c r="H42" s="2">
-        <v>0.15071283099999999</v>
+        <v>0.177314211</v>
       </c>
       <c r="I42" s="2">
-        <v>8.2100000000000009</v>
+        <v>9.9</v>
       </c>
       <c r="J42" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="M42" s="2">
-        <v>8.2100000000000009</v>
+        <v>9.9</v>
       </c>
       <c r="N42" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O42" s="2">
         <v>0</v>
       </c>
       <c r="P42" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q42" s="2">
         <v>-5</v>
       </c>
       <c r="R42" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S42" s="2">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T42" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="U42" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V42" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="2">
-        <v>2301430</v>
+        <v>2301620</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -3528,106 +3512,106 @@
         <v>29</v>
       </c>
       <c r="D43" s="2">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E43" s="2">
-        <v>145.30000000000001</v>
+        <v>149</v>
       </c>
       <c r="F43" s="2">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="G43" s="2">
-        <v>32.445863959999997</v>
+        <v>29.95360569</v>
       </c>
       <c r="H43" s="2">
-        <v>0.12700729899999999</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>11</v>
+        <v>0.19398496200000001</v>
+      </c>
+      <c r="I43" s="2">
+        <v>9.9</v>
       </c>
       <c r="J43" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K43" s="2">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="M43" s="2">
-        <v>16.91</v>
+        <v>9.9</v>
       </c>
       <c r="N43" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="O43" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="P43" s="2">
         <v>115</v>
       </c>
       <c r="Q43" s="2">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="R43" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S43" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T43" s="2">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="U43" s="2">
         <v>15</v>
       </c>
       <c r="V43" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W43" s="2"/>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="2">
-        <v>2301506</v>
+        <v>2301878</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" s="7">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2">
-        <v>158</v>
+        <v>139.5</v>
       </c>
       <c r="F44" s="2">
-        <v>76.7</v>
+        <v>50</v>
       </c>
       <c r="G44" s="2">
-        <v>30.724242910000001</v>
+        <v>25.693400650000001</v>
       </c>
       <c r="H44" s="2">
-        <v>0.177314211</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="I44" s="2">
-        <v>9.9</v>
+        <v>12.19</v>
       </c>
       <c r="J44" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K44" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L44" s="2">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="M44" s="2">
-        <v>9.9</v>
+        <v>12.19</v>
       </c>
       <c r="N44" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
@@ -3636,157 +3620,157 @@
         <v>120</v>
       </c>
       <c r="Q44" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R44" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="S44" s="2">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="T44" s="2">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="U44" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V44" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W44" s="2"/>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="2">
-        <v>2301620</v>
+        <v>2301974</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E45" s="2">
-        <v>149</v>
+        <v>151.5</v>
       </c>
       <c r="F45" s="2">
         <v>66.5</v>
       </c>
       <c r="G45" s="2">
-        <v>29.95360569</v>
+        <v>28.97319435</v>
       </c>
       <c r="H45" s="2">
-        <v>0.19398496200000001</v>
-      </c>
-      <c r="I45" s="2">
-        <v>9.9</v>
+        <v>0.34887217999999998</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="J45" s="2">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K45" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M45" s="2">
-        <v>9.9</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="N45" s="2">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="O45" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="P45" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="Q45" s="2">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="R45" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S45" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T45" s="2">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="U45" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V45" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W45" s="2"/>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="2">
-        <v>2301878</v>
+        <v>2303599</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" s="7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D46" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E46" s="2">
-        <v>139.5</v>
+        <v>148</v>
       </c>
       <c r="F46" s="2">
-        <v>50</v>
+        <v>68.3</v>
       </c>
       <c r="G46" s="2">
-        <v>25.693400650000001</v>
+        <v>31.181519359999999</v>
       </c>
       <c r="H46" s="2">
-        <v>0.32800000000000001</v>
+        <v>9.2240116999999996E-2</v>
       </c>
       <c r="I46" s="2">
-        <v>12.19</v>
+        <v>12.44</v>
       </c>
       <c r="J46" s="2">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K46" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L46" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M46" s="2">
-        <v>12.19</v>
+        <v>12.33</v>
       </c>
       <c r="N46" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O46" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P46" s="2">
-        <v>120</v>
+        <v>-15</v>
       </c>
       <c r="Q46" s="2">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="R46" s="2">
         <v>16</v>
       </c>
       <c r="S46" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="T46" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="U46" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V46" s="2">
         <v>11</v>
@@ -3795,7 +3779,7 @@
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="2">
-        <v>2301974</v>
+        <v>2304093</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -3804,34 +3788,34 @@
         <v>32</v>
       </c>
       <c r="D47" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2">
-        <v>151.5</v>
+        <v>142.5</v>
       </c>
       <c r="F47" s="2">
-        <v>66.5</v>
+        <v>42</v>
       </c>
       <c r="G47" s="2">
-        <v>28.97319435</v>
+        <v>20.68328717</v>
       </c>
       <c r="H47" s="2">
-        <v>0.34887217999999998</v>
+        <v>0.18333333299999999</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J47" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K47" s="2">
         <v>1</v>
       </c>
       <c r="L47" s="2">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="M47" s="2">
-        <v>9.5399999999999991</v>
+        <v>11.69</v>
       </c>
       <c r="N47" s="2">
         <v>130</v>
@@ -3840,169 +3824,169 @@
         <v>0</v>
       </c>
       <c r="P47" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="Q47" s="2">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="R47" s="2">
         <v>23</v>
       </c>
       <c r="S47" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T47" s="2">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="U47" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V47" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W47" s="2"/>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="2">
-        <v>2303599</v>
+        <v>2304321</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E48" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F48" s="2">
-        <v>68.3</v>
+        <v>62.2</v>
       </c>
       <c r="G48" s="2">
-        <v>31.181519359999999</v>
+        <v>29.179958719999998</v>
       </c>
       <c r="H48" s="2">
-        <v>9.2240116999999996E-2</v>
+        <v>0.236334405</v>
       </c>
       <c r="I48" s="2">
-        <v>12.44</v>
+        <v>14.5</v>
       </c>
       <c r="J48" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K48" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L48" s="2">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="M48" s="2">
-        <v>12.33</v>
+        <v>14.5</v>
       </c>
       <c r="N48" s="2">
         <v>120</v>
       </c>
       <c r="O48" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P48" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q48" s="2">
         <v>-15</v>
-      </c>
-      <c r="Q48" s="2">
-        <v>130</v>
       </c>
       <c r="R48" s="2">
         <v>16</v>
       </c>
       <c r="S48" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T48" s="2">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="U48" s="2">
         <v>15</v>
       </c>
       <c r="V48" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W48" s="2"/>
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>2304093</v>
+        <v>2304321</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" s="7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E49" s="2">
-        <v>142.5</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G49" s="2">
-        <v>20.68328717</v>
+        <v>29.08613248</v>
       </c>
       <c r="H49" s="2">
-        <v>0.18333333299999999</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>13</v>
+        <v>0.23548387100000001</v>
+      </c>
+      <c r="I49" s="2">
+        <v>12.28</v>
       </c>
       <c r="J49" s="2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K49" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L49" s="2">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="M49" s="2">
-        <v>11.69</v>
+        <v>11.94</v>
       </c>
       <c r="N49" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O49" s="2">
         <v>0</v>
       </c>
       <c r="P49" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q49" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R49" s="2">
+        <v>16</v>
+      </c>
+      <c r="S49" s="2">
         <v>20</v>
       </c>
-      <c r="R49" s="2">
-        <v>23</v>
-      </c>
-      <c r="S49" s="2">
-        <v>38</v>
-      </c>
       <c r="T49" s="2">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="U49" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V49" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W49" s="2"/>
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>2304321</v>
+        <v>2304669</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -4011,35 +3995,33 @@
         <v>29</v>
       </c>
       <c r="D50" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E50" s="2">
-        <v>146</v>
+        <v>164.5</v>
       </c>
       <c r="F50" s="2">
-        <v>62.2</v>
+        <v>77.8</v>
       </c>
       <c r="G50" s="2">
-        <v>29.179958719999998</v>
+        <v>28.750658250000001</v>
       </c>
       <c r="H50" s="2">
-        <v>0.236334405</v>
+        <v>0.23264781500000001</v>
       </c>
       <c r="I50" s="2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K50" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="L50" s="2">
-        <v>98</v>
-      </c>
-      <c r="M50" s="2">
-        <v>14.5</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="M50" s="1"/>
       <c r="N50" s="2">
         <v>120</v>
       </c>
@@ -4047,31 +4029,31 @@
         <v>0</v>
       </c>
       <c r="P50" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q50" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R50" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S50" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T50" s="2">
         <v>53</v>
       </c>
       <c r="U50" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V50" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W50" s="2"/>
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>2304321</v>
+        <v>2304770</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -4080,34 +4062,34 @@
         <v>29</v>
       </c>
       <c r="D51" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2">
-        <v>146</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F51" s="2">
-        <v>62</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G51" s="2">
-        <v>29.08613248</v>
+        <v>27.80075321</v>
       </c>
       <c r="H51" s="2">
-        <v>0.23548387100000001</v>
+        <v>0.21739130400000001</v>
       </c>
       <c r="I51" s="2">
-        <v>12.28</v>
+        <v>6.93</v>
       </c>
       <c r="J51" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="K51" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L51" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="M51" s="2">
-        <v>11.94</v>
+        <v>6.93</v>
       </c>
       <c r="N51" s="2">
         <v>120</v>
@@ -4116,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Q51" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R51" s="2">
         <v>16</v>
@@ -4128,10 +4110,10 @@
         <v>20</v>
       </c>
       <c r="T51" s="2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="U51" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V51" s="2">
         <v>11</v>
@@ -4140,74 +4122,76 @@
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>2304669</v>
+        <v>2400788</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D52" s="2">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2">
-        <v>164.5</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="F52" s="2">
-        <v>77.8</v>
+        <v>63.8</v>
       </c>
       <c r="G52" s="2">
-        <v>28.750658250000001</v>
+        <v>24.705231349999998</v>
       </c>
       <c r="H52" s="2">
-        <v>0.23264781500000001</v>
+        <v>0.28056426299999998</v>
       </c>
       <c r="I52" s="2">
-        <v>0</v>
+        <v>7.77</v>
       </c>
       <c r="J52" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K52" s="2">
+        <v>5</v>
+      </c>
+      <c r="L52" s="2">
+        <v>146</v>
+      </c>
+      <c r="M52" s="2">
+        <v>7.77</v>
+      </c>
+      <c r="N52" s="2">
+        <v>115</v>
+      </c>
+      <c r="O52" s="2">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2">
+        <v>23</v>
+      </c>
+      <c r="S52" s="2">
         <v>38</v>
       </c>
-      <c r="L52" s="2">
-        <v>107</v>
-      </c>
-      <c r="M52" s="1"/>
-      <c r="N52" s="2">
-        <v>120</v>
-      </c>
-      <c r="O52" s="2">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2">
-        <v>125</v>
-      </c>
-      <c r="Q52" s="2">
-        <v>-5</v>
-      </c>
-      <c r="R52" s="2">
-        <v>19</v>
-      </c>
-      <c r="S52" s="2">
-        <v>24</v>
-      </c>
       <c r="T52" s="2">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="U52" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V52" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W52" s="2"/>
     </row>
     <row r="53" spans="1:23">
       <c r="A53" s="2">
-        <v>2304770</v>
+        <v>2401195</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -4216,205 +4200,205 @@
         <v>29</v>
       </c>
       <c r="D53" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E53" s="2">
-        <v>152.19999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="F53" s="2">
-        <v>64.400000000000006</v>
+        <v>68.3</v>
       </c>
       <c r="G53" s="2">
-        <v>27.80075321</v>
+        <v>29.757431189999998</v>
       </c>
       <c r="H53" s="2">
-        <v>0.21739130400000001</v>
+        <v>0.33967789199999998</v>
       </c>
       <c r="I53" s="2">
-        <v>6.93</v>
+        <v>8.58</v>
       </c>
       <c r="J53" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K53" s="2">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L53" s="2">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="M53" s="2">
-        <v>6.93</v>
+        <v>8.58</v>
       </c>
       <c r="N53" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O53" s="2">
         <v>0</v>
       </c>
       <c r="P53" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q53" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R53" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S53" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="T53" s="2">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="U53" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V53" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W53" s="2"/>
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="2">
-        <v>2400005</v>
+        <v>2401295</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="7">
+        <v>28</v>
+      </c>
+      <c r="D54" s="2">
+        <v>62</v>
+      </c>
+      <c r="E54" s="2">
+        <v>142</v>
+      </c>
+      <c r="F54" s="2">
+        <v>62</v>
+      </c>
+      <c r="G54" s="2">
+        <v>30.747867490000001</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.44193548399999999</v>
+      </c>
+      <c r="I54" s="2">
+        <v>8.92</v>
+      </c>
+      <c r="J54" s="2">
         <v>24</v>
       </c>
-      <c r="D54" s="2">
-        <v>86</v>
-      </c>
-      <c r="E54" s="2">
-        <v>160.80000000000001</v>
-      </c>
-      <c r="F54" s="2">
-        <v>66.7</v>
-      </c>
-      <c r="G54" s="2">
-        <v>25.796081780000002</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0.148425787</v>
-      </c>
-      <c r="I54" s="2">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="J54" s="2">
+      <c r="K54" s="2">
         <v>50</v>
       </c>
-      <c r="K54" s="2">
-        <v>2</v>
-      </c>
       <c r="L54" s="2">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="M54" s="2">
-        <v>9.1999999999999993</v>
+        <v>8.92</v>
       </c>
       <c r="N54" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O54" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P54" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q54" s="2">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="R54" s="2">
         <v>23</v>
       </c>
       <c r="S54" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="T54" s="2">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="U54" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V54" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W54" s="2"/>
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>2400788</v>
+        <v>2401295</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" s="2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E55" s="2">
-        <v>160.69999999999999</v>
+        <v>143</v>
       </c>
       <c r="F55" s="2">
-        <v>63.8</v>
+        <v>61</v>
       </c>
       <c r="G55" s="2">
-        <v>24.705231349999998</v>
+        <v>29.830309549999999</v>
       </c>
       <c r="H55" s="2">
-        <v>0.28056426299999998</v>
+        <v>0.35081967200000003</v>
       </c>
       <c r="I55" s="2">
-        <v>7.77</v>
+        <v>8.93</v>
       </c>
       <c r="J55" s="2">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K55" s="2">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="L55" s="2">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="M55" s="2">
-        <v>7.77</v>
+        <v>8.93</v>
       </c>
       <c r="N55" s="2">
+        <v>110</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2">
         <v>115</v>
       </c>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>120</v>
-      </c>
       <c r="Q55" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="R55" s="2">
         <v>23</v>
       </c>
       <c r="S55" s="2">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="T55" s="2">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="U55" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V55" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W55" s="2"/>
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>2401195</v>
+        <v>2401534</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -4423,172 +4407,172 @@
         <v>29</v>
       </c>
       <c r="D56" s="2">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2">
-        <v>151.5</v>
+        <v>147.5</v>
       </c>
       <c r="F56" s="2">
-        <v>68.3</v>
+        <v>59.2</v>
       </c>
       <c r="G56" s="2">
-        <v>29.757431189999998</v>
+        <v>27.21057167</v>
       </c>
       <c r="H56" s="2">
-        <v>0.33967789199999998</v>
+        <v>0.18243243200000001</v>
       </c>
       <c r="I56" s="2">
-        <v>8.58</v>
+        <v>10.86</v>
       </c>
       <c r="J56" s="2">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K56" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L56" s="2">
         <v>125</v>
       </c>
       <c r="M56" s="2">
-        <v>8.58</v>
+        <v>10.91</v>
       </c>
       <c r="N56" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O56" s="2">
         <v>0</v>
       </c>
       <c r="P56" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q56" s="2">
         <v>-10</v>
       </c>
       <c r="R56" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S56" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T56" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U56" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V56" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W56" s="2"/>
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>2401295</v>
+        <v>2401730</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" s="2">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F57" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G57" s="2">
-        <v>30.747867490000001</v>
+        <v>21.875</v>
       </c>
       <c r="H57" s="2">
-        <v>0.44193548399999999</v>
+        <v>0.14464285700000001</v>
       </c>
       <c r="I57" s="2">
-        <v>8.92</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="J57" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K57" s="2">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="L57" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="M57" s="2">
-        <v>8.92</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N57" s="2">
+        <v>130</v>
+      </c>
+      <c r="O57" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P57" s="2">
         <v>120</v>
       </c>
-      <c r="O57" s="2">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>115</v>
-      </c>
       <c r="Q57" s="2">
-        <v>-20</v>
+        <v>-35</v>
       </c>
       <c r="R57" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S57" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T57" s="2">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="U57" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V57" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W57" s="2"/>
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>2401295</v>
+        <v>2401922</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D58" s="2">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E58" s="2">
-        <v>143</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="F58" s="2">
-        <v>61</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="G58" s="2">
-        <v>29.830309549999999</v>
+        <v>37.568624579999998</v>
       </c>
       <c r="H58" s="2">
-        <v>0.35081967200000003</v>
+        <v>0.16598079600000001</v>
       </c>
       <c r="I58" s="2">
-        <v>8.93</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="J58" s="2">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K58" s="2">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="L58" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="M58" s="2">
-        <v>8.93</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="N58" s="2">
         <v>110</v>
@@ -4597,88 +4581,88 @@
         <v>0</v>
       </c>
       <c r="P58" s="2">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="Q58" s="2">
         <v>-15</v>
       </c>
       <c r="R58" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S58" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T58" s="2">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="U58" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V58" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W58" s="2"/>
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>2401534</v>
+        <v>2402032</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2">
-        <v>147.5</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="F59" s="2">
-        <v>59.2</v>
+        <v>57.3</v>
       </c>
       <c r="G59" s="2">
-        <v>27.21057167</v>
+        <v>25.568839749999999</v>
       </c>
       <c r="H59" s="2">
-        <v>0.18243243200000001</v>
+        <v>0.25828970299999998</v>
       </c>
       <c r="I59" s="2">
-        <v>10.86</v>
+        <v>9.26</v>
       </c>
       <c r="J59" s="2">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K59" s="2">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L59" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="M59" s="2">
-        <v>10.91</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="N59" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O59" s="2">
         <v>0</v>
       </c>
       <c r="P59" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q59" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R59" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S59" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T59" s="2">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="U59" s="2">
         <v>13</v>
@@ -4690,205 +4674,205 @@
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>2401730</v>
+        <v>2402281</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D60" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E60" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F60" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G60" s="2">
-        <v>21.875</v>
+        <v>27.555555559999998</v>
       </c>
       <c r="H60" s="2">
-        <v>0.14464285700000001</v>
+        <v>0.20483871000000001</v>
       </c>
       <c r="I60" s="2">
-        <v>39.229999999999997</v>
+        <v>13.88</v>
       </c>
       <c r="J60" s="2">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K60" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L60" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="M60" s="2">
-        <v>32.799999999999997</v>
+        <v>13.88</v>
       </c>
       <c r="N60" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O60" s="2">
         <v>-5</v>
       </c>
       <c r="P60" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q60" s="2">
-        <v>-35</v>
+        <v>-20</v>
       </c>
       <c r="R60" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S60" s="2">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="T60" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="U60" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V60" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W60" s="2"/>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>2401922</v>
+        <v>2402895</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="7">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D61" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2">
-        <v>139.30000000000001</v>
+        <v>170.5</v>
       </c>
       <c r="F61" s="2">
-        <v>72.900000000000006</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="G61" s="2">
-        <v>37.568624579999998</v>
+        <v>26.453160879999999</v>
       </c>
       <c r="H61" s="2">
-        <v>0.16598079600000001</v>
+        <v>0.13133940199999999</v>
       </c>
       <c r="I61" s="2">
-        <v>17.829999999999998</v>
+        <v>14.13</v>
       </c>
       <c r="J61" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K61" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L61" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="M61" s="2">
-        <v>18.649999999999999</v>
+        <v>14.49</v>
       </c>
       <c r="N61" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O61" s="2">
         <v>0</v>
       </c>
       <c r="P61" s="2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="Q61" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R61" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S61" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T61" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="U61" s="2">
         <v>12</v>
       </c>
       <c r="V61" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W61" s="2"/>
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>2402032</v>
+        <v>2403315</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D62" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E62" s="2">
-        <v>149.69999999999999</v>
+        <v>171</v>
       </c>
       <c r="F62" s="2">
-        <v>57.3</v>
+        <v>92.5</v>
       </c>
       <c r="G62" s="2">
-        <v>25.568839749999999</v>
+        <v>31.633665059999998</v>
       </c>
       <c r="H62" s="2">
-        <v>0.25828970299999998</v>
+        <v>0.23243243199999999</v>
       </c>
       <c r="I62" s="2">
-        <v>9.26</v>
+        <v>12.89</v>
       </c>
       <c r="J62" s="2">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K62" s="2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="L62" s="2">
         <v>135</v>
       </c>
       <c r="M62" s="2">
-        <v>9.0299999999999994</v>
+        <v>12.89</v>
       </c>
       <c r="N62" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O62" s="2">
         <v>0</v>
       </c>
       <c r="P62" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q62" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R62" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S62" s="2">
         <v>28</v>
       </c>
       <c r="T62" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U62" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V62" s="2">
         <v>9</v>
@@ -4897,67 +4881,67 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>2402281</v>
+        <v>2403413</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" s="7">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D63" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E63" s="2">
-        <v>150</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="F63" s="2">
-        <v>62</v>
+        <v>65.2</v>
       </c>
       <c r="G63" s="2">
-        <v>27.555555559999998</v>
+        <v>28.519638310000001</v>
       </c>
       <c r="H63" s="2">
-        <v>0.20483871000000001</v>
+        <v>0.20552147200000001</v>
       </c>
       <c r="I63" s="2">
-        <v>13.88</v>
+        <v>12.39</v>
       </c>
       <c r="J63" s="2">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="K63" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L63" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M63" s="2">
-        <v>13.88</v>
+        <v>12.39</v>
       </c>
       <c r="N63" s="2">
         <v>120</v>
       </c>
       <c r="O63" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P63" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q63" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R63" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S63" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T63" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="U63" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V63" s="2">
         <v>8</v>
@@ -4966,46 +4950,46 @@
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>2402895</v>
+        <v>2403725</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64" s="7">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D64" s="2">
+        <v>71</v>
+      </c>
+      <c r="E64" s="2">
+        <v>165.5</v>
+      </c>
+      <c r="F64" s="2">
         <v>79</v>
       </c>
-      <c r="E64" s="2">
-        <v>170.5</v>
-      </c>
-      <c r="F64" s="2">
-        <v>76.900000000000006</v>
-      </c>
       <c r="G64" s="2">
-        <v>26.453160879999999</v>
+        <v>28.842380039999998</v>
       </c>
       <c r="H64" s="2">
-        <v>0.13133940199999999</v>
+        <v>0.20506329100000001</v>
       </c>
       <c r="I64" s="2">
-        <v>14.13</v>
+        <v>9.64</v>
       </c>
       <c r="J64" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K64" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L64" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="M64" s="2">
-        <v>14.49</v>
+        <v>9.64</v>
       </c>
       <c r="N64" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O64" s="2">
         <v>0</v>
@@ -5014,31 +4998,31 @@
         <v>120</v>
       </c>
       <c r="Q64" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R64" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S64" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T64" s="2">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="U64" s="2">
         <v>12</v>
       </c>
       <c r="V64" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W64" s="2"/>
     </row>
     <row r="65" spans="1:23">
       <c r="A65" s="2">
-        <v>2403315</v>
+        <v>2403883</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="7">
         <v>29</v>
@@ -5047,31 +5031,31 @@
         <v>64</v>
       </c>
       <c r="E65" s="2">
-        <v>171</v>
+        <v>158.1</v>
       </c>
       <c r="F65" s="2">
-        <v>92.5</v>
+        <v>66</v>
       </c>
       <c r="G65" s="2">
-        <v>31.633665059999998</v>
+        <v>26.40463665</v>
       </c>
       <c r="H65" s="2">
-        <v>0.23243243199999999</v>
+        <v>0.192424242</v>
       </c>
       <c r="I65" s="2">
-        <v>12.89</v>
+        <v>9.93</v>
       </c>
       <c r="J65" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K65" s="2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L65" s="2">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="M65" s="2">
-        <v>12.89</v>
+        <v>9.93</v>
       </c>
       <c r="N65" s="2">
         <v>120</v>
@@ -5080,22 +5064,22 @@
         <v>0</v>
       </c>
       <c r="P65" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q65" s="2">
         <v>-10</v>
       </c>
       <c r="R65" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S65" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="T65" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U65" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V65" s="2">
         <v>9</v>
@@ -5104,46 +5088,46 @@
     </row>
     <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>2403413</v>
+        <v>8811223</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2">
-        <v>151.19999999999999</v>
+        <v>154</v>
       </c>
       <c r="F66" s="2">
-        <v>65.2</v>
+        <v>49.4</v>
       </c>
       <c r="G66" s="2">
-        <v>28.519638310000001</v>
+        <v>20.829819530000002</v>
       </c>
       <c r="H66" s="2">
-        <v>0.20552147200000001</v>
+        <v>0.17813765200000001</v>
       </c>
       <c r="I66" s="2">
-        <v>12.39</v>
+        <v>9.11</v>
       </c>
       <c r="J66" s="2">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K66" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L66" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="M66" s="2">
-        <v>12.39</v>
+        <v>10.89</v>
       </c>
       <c r="N66" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O66" s="2">
         <v>0</v>
@@ -5152,133 +5136,133 @@
         <v>120</v>
       </c>
       <c r="Q66" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R66" s="2">
         <v>21</v>
       </c>
       <c r="S66" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="T66" s="2">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="U66" s="2">
+        <v>15</v>
+      </c>
+      <c r="V66" s="2">
         <v>10</v>
-      </c>
-      <c r="V66" s="2">
-        <v>8</v>
       </c>
       <c r="W66" s="2"/>
     </row>
     <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>2403725</v>
+        <v>8852227</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D67" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E67" s="2">
-        <v>165.5</v>
+        <v>151</v>
       </c>
       <c r="F67" s="2">
-        <v>79</v>
+        <v>65.5</v>
       </c>
       <c r="G67" s="2">
-        <v>28.842380039999998</v>
+        <v>28.726810230000002</v>
       </c>
       <c r="H67" s="2">
-        <v>0.20506329100000001</v>
+        <v>0.17251908399999999</v>
       </c>
       <c r="I67" s="2">
-        <v>9.64</v>
+        <v>10.27</v>
       </c>
       <c r="J67" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K67" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L67" s="2">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="M67" s="2">
-        <v>9.64</v>
+        <v>11.38</v>
       </c>
       <c r="N67" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O67" s="2">
         <v>0</v>
       </c>
       <c r="P67" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q67" s="2">
         <v>-5</v>
       </c>
       <c r="R67" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S67" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="T67" s="2">
         <v>66</v>
       </c>
       <c r="U67" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V67" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W67" s="2"/>
     </row>
     <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>2403883</v>
+        <v>8852227</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D68" s="2">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2">
-        <v>158.1</v>
+        <v>151</v>
       </c>
       <c r="F68" s="2">
-        <v>66</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G68" s="2">
-        <v>26.40463665</v>
+        <v>28.244375250000001</v>
       </c>
       <c r="H68" s="2">
-        <v>0.192424242</v>
+        <v>0.189440994</v>
       </c>
       <c r="I68" s="2">
-        <v>9.93</v>
+        <v>10.63</v>
       </c>
       <c r="J68" s="2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K68" s="2">
         <v>25</v>
       </c>
       <c r="L68" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="M68" s="2">
-        <v>9.93</v>
+        <v>10.63</v>
       </c>
       <c r="N68" s="2">
         <v>120</v>
@@ -5287,19 +5271,19 @@
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q68" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R68" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S68" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T68" s="2">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="U68" s="2">
         <v>15</v>
@@ -5311,112 +5295,112 @@
     </row>
     <row r="69" spans="1:23">
       <c r="A69" s="2">
-        <v>8805135</v>
+        <v>9005400</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" s="7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D69" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E69" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F69" s="2">
-        <v>90.3</v>
+        <v>77.3</v>
       </c>
       <c r="G69" s="2">
-        <v>31.99404762</v>
+        <v>30.1953125</v>
       </c>
       <c r="H69" s="2">
-        <v>0.24252491700000001</v>
+        <v>0.168175938</v>
       </c>
       <c r="I69" s="2">
-        <v>7.9</v>
+        <v>17.73</v>
       </c>
       <c r="J69" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K69" s="2">
+        <v>33</v>
+      </c>
+      <c r="L69" s="2">
+        <v>82</v>
+      </c>
+      <c r="M69" s="2">
+        <v>17.73</v>
+      </c>
+      <c r="N69" s="2">
+        <v>120</v>
+      </c>
+      <c r="O69" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P69" s="2">
+        <v>110</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2">
         <v>12</v>
       </c>
-      <c r="L69" s="2">
-        <v>142</v>
-      </c>
-      <c r="M69" s="2">
-        <v>6.34</v>
-      </c>
-      <c r="N69" s="2">
-        <v>130</v>
-      </c>
-      <c r="O69" s="2">
-        <v>0</v>
-      </c>
-      <c r="P69" s="2">
-        <v>130</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R69" s="2">
-        <v>23</v>
-      </c>
       <c r="S69" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="T69" s="2">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="U69" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V69" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W69" s="2"/>
     </row>
     <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>8811223</v>
+        <v>9209245</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D70" s="2">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E70" s="2">
-        <v>154</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="F70" s="2">
-        <v>49.4</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="G70" s="2">
-        <v>20.829819530000002</v>
+        <v>28.97396552</v>
       </c>
       <c r="H70" s="2">
-        <v>0.17813765200000001</v>
+        <v>0.17597765400000001</v>
       </c>
       <c r="I70" s="2">
-        <v>9.11</v>
+        <v>10.62</v>
       </c>
       <c r="J70" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K70" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L70" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="M70" s="2">
-        <v>10.89</v>
+        <v>10.67</v>
       </c>
       <c r="N70" s="2">
         <v>125</v>
@@ -5425,22 +5409,22 @@
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q70" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R70" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="S70" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="T70" s="2">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="U70" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V70" s="2">
         <v>10</v>
@@ -5449,7 +5433,7 @@
     </row>
     <row r="71" spans="1:23">
       <c r="A71" s="2">
-        <v>8852227</v>
+        <v>9301565</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -5458,58 +5442,58 @@
         <v>29</v>
       </c>
       <c r="D71" s="2">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E71" s="2">
-        <v>151</v>
+        <v>152.5</v>
       </c>
       <c r="F71" s="2">
-        <v>65.5</v>
+        <v>78.3</v>
       </c>
       <c r="G71" s="2">
-        <v>28.726810230000002</v>
+        <v>33.668368719999997</v>
       </c>
       <c r="H71" s="2">
-        <v>0.17251908399999999</v>
-      </c>
-      <c r="I71" s="2">
-        <v>10.27</v>
+        <v>0.20945083</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="J71" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K71" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L71" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M71" s="2">
-        <v>11.38</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="N71" s="2">
+        <v>130</v>
+      </c>
+      <c r="O71" s="2">
+        <v>0</v>
+      </c>
+      <c r="P71" s="2">
         <v>120</v>
       </c>
-      <c r="O71" s="2">
-        <v>0</v>
-      </c>
-      <c r="P71" s="2">
-        <v>115</v>
-      </c>
       <c r="Q71" s="2">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="R71" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S71" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T71" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="U71" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V71" s="2">
         <v>13</v>
@@ -5518,502 +5502,238 @@
     </row>
     <row r="72" spans="1:23">
       <c r="A72" s="2">
-        <v>8852227</v>
+        <v>9301565</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72" s="7">
+        <v>29</v>
+      </c>
+      <c r="D72" s="2">
+        <v>58</v>
+      </c>
+      <c r="E72" s="2">
+        <v>153</v>
+      </c>
+      <c r="F72" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="G72" s="2">
+        <v>34.516638899999997</v>
+      </c>
+      <c r="H72" s="2">
+        <v>0.21534653500000001</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" s="2">
+        <v>29</v>
+      </c>
+      <c r="K72" s="2">
+        <v>15</v>
+      </c>
+      <c r="L72" s="2">
+        <v>127</v>
+      </c>
+      <c r="M72" s="2">
+        <v>8.59</v>
+      </c>
+      <c r="N72" s="2">
+        <v>115</v>
+      </c>
+      <c r="O72" s="2">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>105</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R72" s="2">
+        <v>20</v>
+      </c>
+      <c r="S72" s="2">
         <v>30</v>
       </c>
-      <c r="D72" s="2">
-        <v>77</v>
-      </c>
-      <c r="E72" s="2">
-        <v>151</v>
-      </c>
-      <c r="F72" s="2">
-        <v>64.400000000000006</v>
-      </c>
-      <c r="G72" s="2">
-        <v>28.244375250000001</v>
-      </c>
-      <c r="H72" s="2">
-        <v>0.189440994</v>
-      </c>
-      <c r="I72" s="2">
-        <v>10.63</v>
-      </c>
-      <c r="J72" s="2">
-        <v>35</v>
-      </c>
-      <c r="K72" s="2">
-        <v>25</v>
-      </c>
-      <c r="L72" s="2">
-        <v>90</v>
-      </c>
-      <c r="M72" s="2">
-        <v>10.63</v>
-      </c>
-      <c r="N72" s="2">
-        <v>120</v>
-      </c>
-      <c r="O72" s="2">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>0</v>
-      </c>
-      <c r="R72" s="2">
-        <v>16</v>
-      </c>
-      <c r="S72" s="2">
-        <v>22</v>
-      </c>
       <c r="T72" s="2">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="U72" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V72" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W72" s="2"/>
     </row>
     <row r="73" spans="1:23">
       <c r="A73" s="2">
-        <v>9005400</v>
+        <v>9508610</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D73" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E73" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F73" s="2">
-        <v>77.3</v>
+        <v>55.4</v>
       </c>
       <c r="G73" s="2">
-        <v>30.1953125</v>
+        <v>24.29717995</v>
       </c>
       <c r="H73" s="2">
-        <v>0.168175938</v>
+        <v>0.20216606500000001</v>
       </c>
       <c r="I73" s="2">
-        <v>17.73</v>
+        <v>7.96</v>
       </c>
       <c r="J73" s="2">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K73" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L73" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="M73" s="2">
-        <v>17.73</v>
+        <v>8.09</v>
       </c>
       <c r="N73" s="2">
+        <v>125</v>
+      </c>
+      <c r="O73" s="2">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2">
         <v>120</v>
       </c>
-      <c r="O73" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P73" s="2">
-        <v>110</v>
-      </c>
       <c r="Q73" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="R73" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S73" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T73" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="U73" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V73" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W73" s="2"/>
     </row>
     <row r="74" spans="1:23">
-      <c r="A74" s="2">
-        <v>9209245</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" s="7">
-        <v>27</v>
-      </c>
-      <c r="D74" s="2">
-        <v>68</v>
-      </c>
-      <c r="E74" s="2">
-        <v>157.19999999999999</v>
-      </c>
-      <c r="F74" s="2">
-        <v>71.599999999999994</v>
-      </c>
-      <c r="G74" s="2">
-        <v>28.97396552</v>
-      </c>
-      <c r="H74" s="2">
-        <v>0.17597765400000001</v>
-      </c>
-      <c r="I74" s="2">
-        <v>10.62</v>
-      </c>
-      <c r="J74" s="2">
-        <v>25</v>
-      </c>
-      <c r="K74" s="2">
-        <v>12</v>
-      </c>
-      <c r="L74" s="2">
-        <v>104</v>
-      </c>
-      <c r="M74" s="2">
-        <v>10.67</v>
-      </c>
-      <c r="N74" s="2">
-        <v>125</v>
-      </c>
-      <c r="O74" s="2">
-        <v>0</v>
-      </c>
-      <c r="P74" s="2">
-        <v>130</v>
-      </c>
-      <c r="Q74" s="2">
-        <v>-5</v>
-      </c>
-      <c r="R74" s="2">
-        <v>19</v>
-      </c>
-      <c r="S74" s="2">
-        <v>14</v>
-      </c>
-      <c r="T74" s="2">
-        <v>61</v>
-      </c>
-      <c r="U74" s="2">
-        <v>10</v>
-      </c>
-      <c r="V74" s="2">
-        <v>10</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="2"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="2"/>
       <c r="W74" s="2"/>
     </row>
     <row r="75" spans="1:23">
-      <c r="A75" s="2">
-        <v>9301565</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75" s="7">
-        <v>29</v>
-      </c>
-      <c r="D75" s="2">
-        <v>58</v>
-      </c>
-      <c r="E75" s="2">
-        <v>152.5</v>
-      </c>
-      <c r="F75" s="2">
-        <v>78.3</v>
-      </c>
-      <c r="G75" s="2">
-        <v>33.668368719999997</v>
-      </c>
-      <c r="H75" s="2">
-        <v>0.20945083</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J75" s="2">
-        <v>44</v>
-      </c>
-      <c r="K75" s="2">
-        <v>22</v>
-      </c>
-      <c r="L75" s="2">
-        <v>127</v>
-      </c>
-      <c r="M75" s="2">
-        <v>9.0500000000000007</v>
-      </c>
-      <c r="N75" s="2">
-        <v>130</v>
-      </c>
-      <c r="O75" s="2">
-        <v>0</v>
-      </c>
-      <c r="P75" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q75" s="2">
-        <v>-20</v>
-      </c>
-      <c r="R75" s="2">
-        <v>19</v>
-      </c>
-      <c r="S75" s="2">
-        <v>24</v>
-      </c>
-      <c r="T75" s="2">
-        <v>71</v>
-      </c>
-      <c r="U75" s="2">
-        <v>12</v>
-      </c>
-      <c r="V75" s="2">
-        <v>13</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="T75" s="2"/>
+      <c r="V75" s="2"/>
       <c r="W75" s="2"/>
     </row>
     <row r="76" spans="1:23">
-      <c r="A76" s="2">
-        <v>9301565</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76" s="7">
-        <v>29</v>
-      </c>
-      <c r="D76" s="2">
-        <v>58</v>
-      </c>
-      <c r="E76" s="2">
-        <v>153</v>
-      </c>
-      <c r="F76" s="2">
-        <v>80.8</v>
-      </c>
-      <c r="G76" s="2">
-        <v>34.516638899999997</v>
-      </c>
-      <c r="H76" s="2">
-        <v>0.21534653500000001</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="2">
-        <v>29</v>
-      </c>
-      <c r="K76" s="2">
-        <v>15</v>
-      </c>
-      <c r="L76" s="2">
-        <v>127</v>
-      </c>
-      <c r="M76" s="2">
-        <v>8.59</v>
-      </c>
-      <c r="N76" s="2">
-        <v>115</v>
-      </c>
-      <c r="O76" s="2">
-        <v>0</v>
-      </c>
-      <c r="P76" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q76" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R76" s="2">
-        <v>20</v>
-      </c>
-      <c r="S76" s="2">
-        <v>30</v>
-      </c>
-      <c r="T76" s="2">
-        <v>64</v>
-      </c>
-      <c r="U76" s="2">
-        <v>13</v>
-      </c>
-      <c r="V76" s="2">
-        <v>13</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="T76" s="2"/>
+      <c r="V76" s="2"/>
       <c r="W76" s="2"/>
     </row>
     <row r="77" spans="1:23">
-      <c r="A77" s="2">
-        <v>9508610</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77" s="7">
-        <v>29</v>
-      </c>
-      <c r="D77" s="2">
-        <v>72</v>
-      </c>
-      <c r="E77" s="2">
-        <v>151</v>
-      </c>
-      <c r="F77" s="2">
-        <v>55.4</v>
-      </c>
-      <c r="G77" s="2">
-        <v>24.29717995</v>
-      </c>
-      <c r="H77" s="2">
-        <v>0.20216606500000001</v>
-      </c>
-      <c r="I77" s="2">
-        <v>7.96</v>
-      </c>
-      <c r="J77" s="2">
-        <v>34</v>
-      </c>
-      <c r="K77" s="2">
-        <v>17</v>
-      </c>
-      <c r="L77" s="2">
-        <v>115</v>
-      </c>
-      <c r="M77" s="2">
-        <v>8.09</v>
-      </c>
-      <c r="N77" s="2">
-        <v>125</v>
-      </c>
-      <c r="O77" s="2">
-        <v>0</v>
-      </c>
-      <c r="P77" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q77" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R77" s="2">
-        <v>19</v>
-      </c>
-      <c r="S77" s="2">
-        <v>28</v>
-      </c>
-      <c r="T77" s="2">
-        <v>59</v>
-      </c>
-      <c r="U77" s="2">
-        <v>13</v>
-      </c>
-      <c r="V77" s="2">
-        <v>9</v>
-      </c>
-      <c r="W77" s="2"/>
+      <c r="A77" s="1"/>
+      <c r="T77" s="4"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
     </row>
     <row r="78" spans="1:23">
       <c r="A78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="1"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
     </row>
     <row r="79" spans="1:23">
       <c r="A79" s="1"/>
-      <c r="T79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
     </row>
     <row r="80" spans="1:23">
       <c r="A80" s="1"/>
-      <c r="T80" s="2"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="1:23">
+    </row>
+    <row r="81" spans="1:1">
       <c r="A81" s="1"/>
-      <c r="T81" s="4"/>
-      <c r="V81" s="1"/>
-      <c r="W81" s="1"/>
-    </row>
-    <row r="82" spans="1:23">
+    </row>
+    <row r="82" spans="1:1">
       <c r="A82" s="1"/>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:1">
       <c r="A83" s="1"/>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:1">
       <c r="A84" s="1"/>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:1">
       <c r="A85" s="1"/>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:1">
       <c r="A86" s="1"/>
     </row>
-    <row r="87" spans="1:23">
+    <row r="87" spans="1:1">
       <c r="A87" s="1"/>
     </row>
-    <row r="88" spans="1:23">
+    <row r="88" spans="1:1">
       <c r="A88" s="1"/>
     </row>
-    <row r="89" spans="1:23">
+    <row r="89" spans="1:1">
       <c r="A89" s="1"/>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:1">
       <c r="A90" s="1"/>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:1">
       <c r="A91" s="1"/>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:1">
       <c r="A92" s="1"/>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:1">
       <c r="A93" s="1"/>
     </row>
-    <row r="94" spans="1:23">
+    <row r="94" spans="1:1">
       <c r="A94" s="1"/>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:1">
       <c r="A95" s="1"/>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:1">
       <c r="A96" s="1"/>
     </row>
     <row r="97" spans="1:1">
@@ -7293,18 +7013,6 @@
     </row>
     <row r="522" spans="1:1">
       <c r="A522" s="1"/>
-    </row>
-    <row r="523" spans="1:1">
-      <c r="A523" s="1"/>
-    </row>
-    <row r="524" spans="1:1">
-      <c r="A524" s="1"/>
-    </row>
-    <row r="525" spans="1:1">
-      <c r="A525" s="1"/>
-    </row>
-    <row r="526" spans="1:1">
-      <c r="A526" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED1BA3-8C8E-9044-BEA9-B5A1E8BB0E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC060C7-2C2C-944E-BD3F-9A406BB0084C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>年齢（歳）</t>
   </si>
@@ -150,12 +150,35 @@
     <t>sex</t>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Helvetica"/>
+        <family val="2"/>
+      </rPr>
+      <t>平地歩行時の疼痛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>_post</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -208,6 +231,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Hiragino Kaku Gothic ProN"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,7 +290,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -269,6 +313,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -583,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:X522"/>
+  <dimension ref="A1:X520"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -598,6 +645,7 @@
     <col min="21" max="21" width="13.7109375" customWidth="1"/>
     <col min="22" max="22" width="20" customWidth="1"/>
     <col min="23" max="23" width="18.140625" customWidth="1"/>
+    <col min="24" max="24" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -667,10 +715,10 @@
       <c r="V1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="1"/>
-      <c r="X1" s="2" t="s">
-        <v>30</v>
-      </c>
+      <c r="W1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="2"/>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="2">
@@ -739,7 +787,9 @@
       <c r="V2" s="2">
         <v>10</v>
       </c>
-      <c r="W2" s="1"/>
+      <c r="W2" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="2">
@@ -808,7 +858,9 @@
       <c r="V3" s="2">
         <v>10</v>
       </c>
-      <c r="W3" s="2"/>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="2">
@@ -877,7 +929,9 @@
       <c r="V4" s="2">
         <v>15</v>
       </c>
-      <c r="W4" s="2"/>
+      <c r="W4" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="2">
@@ -946,7 +1000,9 @@
       <c r="V5" s="2">
         <v>10</v>
       </c>
-      <c r="W5" s="2"/>
+      <c r="W5" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="2">
@@ -1015,7 +1071,9 @@
       <c r="V6" s="2">
         <v>10</v>
       </c>
-      <c r="W6" s="2"/>
+      <c r="W6" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="2">
@@ -1084,7 +1142,9 @@
       <c r="V7" s="2">
         <v>6</v>
       </c>
-      <c r="W7" s="2"/>
+      <c r="W7" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="2">
@@ -1153,7 +1213,9 @@
       <c r="V8" s="2">
         <v>9</v>
       </c>
-      <c r="W8" s="2"/>
+      <c r="W8" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="2">
@@ -1222,7 +1284,9 @@
       <c r="V9" s="2">
         <v>9</v>
       </c>
-      <c r="W9" s="2"/>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="2">
@@ -1291,7 +1355,9 @@
       <c r="V10" s="2">
         <v>11</v>
       </c>
-      <c r="W10" s="2"/>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="2">
@@ -1360,7 +1426,9 @@
       <c r="V11" s="2">
         <v>9</v>
       </c>
-      <c r="W11" s="2"/>
+      <c r="W11" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="2">
@@ -1429,7 +1497,9 @@
       <c r="V12" s="2">
         <v>6</v>
       </c>
-      <c r="W12" s="2"/>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="2">
@@ -1498,7 +1568,9 @@
       <c r="V13" s="2">
         <v>9</v>
       </c>
-      <c r="W13" s="2"/>
+      <c r="W13" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="2">
@@ -1567,7 +1639,9 @@
       <c r="V14" s="2">
         <v>9</v>
       </c>
-      <c r="W14" s="2"/>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="2">
@@ -1636,7 +1710,9 @@
       <c r="V15" s="2">
         <v>9</v>
       </c>
-      <c r="W15" s="2"/>
+      <c r="W15" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="2">
@@ -1705,7 +1781,9 @@
       <c r="V16" s="2">
         <v>10</v>
       </c>
-      <c r="W16" s="2"/>
+      <c r="W16" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="2">
@@ -1774,7 +1852,9 @@
       <c r="V17" s="2">
         <v>10</v>
       </c>
-      <c r="W17" s="2"/>
+      <c r="W17" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="2">
@@ -1843,7 +1923,9 @@
       <c r="V18" s="2">
         <v>10</v>
       </c>
-      <c r="W18" s="2"/>
+      <c r="W18" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="2">
@@ -1912,7 +1994,9 @@
       <c r="V19" s="2">
         <v>9</v>
       </c>
-      <c r="W19" s="2"/>
+      <c r="W19" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="2">
@@ -1981,7 +2065,9 @@
       <c r="V20" s="2">
         <v>14</v>
       </c>
-      <c r="W20" s="2"/>
+      <c r="W20" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="2">
@@ -2050,7 +2136,9 @@
       <c r="V21" s="2">
         <v>9</v>
       </c>
-      <c r="W21" s="2"/>
+      <c r="W21" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="2">
@@ -2119,7 +2207,9 @@
       <c r="V22" s="2">
         <v>9</v>
       </c>
-      <c r="W22" s="2"/>
+      <c r="W22" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="2">
@@ -2188,7 +2278,9 @@
       <c r="V23" s="2">
         <v>9</v>
       </c>
-      <c r="W23" s="2"/>
+      <c r="W23" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:23">
       <c r="A24" s="2">
@@ -2257,7 +2349,9 @@
       <c r="V24" s="2">
         <v>9</v>
       </c>
-      <c r="W24" s="2"/>
+      <c r="W24" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:23">
       <c r="A25" s="2">
@@ -2326,50 +2420,52 @@
       <c r="V25" s="2">
         <v>9</v>
       </c>
-      <c r="W25" s="2"/>
+      <c r="W25" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="2">
-        <v>2202167</v>
+        <v>2202692</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" s="7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2">
-        <v>146.5</v>
+        <v>150</v>
       </c>
       <c r="F26" s="2">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="G26" s="2">
-        <v>27.02419364</v>
+        <v>20.222222219999999</v>
       </c>
       <c r="H26" s="2">
-        <v>0.22068965500000001</v>
+        <v>0.19780219800000001</v>
       </c>
       <c r="I26" s="2">
-        <v>10.24</v>
+        <v>10.39</v>
       </c>
       <c r="J26" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="M26" s="2">
-        <v>10.69</v>
+        <v>10.35</v>
       </c>
       <c r="N26" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
@@ -2378,13 +2474,13 @@
         <v>110</v>
       </c>
       <c r="Q26" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R26" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S26" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T26" s="2">
         <v>69</v>
@@ -2393,13 +2489,15 @@
         <v>15</v>
       </c>
       <c r="V26" s="2">
-        <v>15</v>
-      </c>
-      <c r="W26" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="W26" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="2">
-        <v>2202692</v>
+        <v>2203257</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -2408,34 +2506,34 @@
         <v>29</v>
       </c>
       <c r="D27" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F27" s="2">
-        <v>45.5</v>
+        <v>53.05</v>
       </c>
       <c r="G27" s="2">
-        <v>20.222222219999999</v>
+        <v>22.66222393</v>
       </c>
       <c r="H27" s="2">
-        <v>0.19780219800000001</v>
-      </c>
-      <c r="I27" s="2">
-        <v>10.39</v>
+        <v>0.20923656900000001</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="J27" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K27" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M27" s="2">
-        <v>10.35</v>
+        <v>9.59</v>
       </c>
       <c r="N27" s="2">
         <v>125</v>
@@ -2444,169 +2542,175 @@
         <v>0</v>
       </c>
       <c r="P27" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R27" s="2">
         <v>23</v>
       </c>
       <c r="S27" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T27" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U27" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V27" s="2">
-        <v>14</v>
-      </c>
-      <c r="W27" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W27" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="2">
-        <v>2203257</v>
+        <v>2203370</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2">
-        <v>153</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="F28" s="2">
-        <v>53.05</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="G28" s="2">
-        <v>22.66222393</v>
+        <v>29.828657549999999</v>
       </c>
       <c r="H28" s="2">
-        <v>0.20923656900000001</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>8</v>
+        <v>0.139800285</v>
+      </c>
+      <c r="I28" s="2">
+        <v>13.29</v>
       </c>
       <c r="J28" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K28" s="2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L28" s="2">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="M28" s="2">
-        <v>9.59</v>
+        <v>13.29</v>
       </c>
       <c r="N28" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O28" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P28" s="2">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R28" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S28" s="2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="T28" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="U28" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V28" s="2">
-        <v>9</v>
-      </c>
-      <c r="W28" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="W28" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="2">
-        <v>2203370</v>
+        <v>2204023</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2">
-        <v>153.30000000000001</v>
+        <v>153</v>
       </c>
       <c r="F29" s="2">
-        <v>70.099999999999994</v>
+        <v>73.5</v>
       </c>
       <c r="G29" s="2">
-        <v>29.828657549999999</v>
+        <v>31.398180190000001</v>
       </c>
       <c r="H29" s="2">
-        <v>0.139800285</v>
-      </c>
-      <c r="I29" s="2">
-        <v>13.29</v>
+        <v>0.30204081599999999</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="J29" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K29" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L29" s="2">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="M29" s="2">
-        <v>13.29</v>
+        <v>10.94</v>
       </c>
       <c r="N29" s="2">
+        <v>125</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
         <v>115</v>
-      </c>
-      <c r="O29" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P29" s="2">
-        <v>120</v>
       </c>
       <c r="Q29" s="2">
         <v>-15</v>
       </c>
       <c r="R29" s="2">
+        <v>18</v>
+      </c>
+      <c r="S29" s="2">
+        <v>26</v>
+      </c>
+      <c r="T29" s="2">
+        <v>66</v>
+      </c>
+      <c r="U29" s="2">
         <v>12</v>
-      </c>
-      <c r="S29" s="2">
-        <v>14</v>
-      </c>
-      <c r="T29" s="2">
-        <v>28</v>
-      </c>
-      <c r="U29" s="2">
-        <v>15</v>
       </c>
       <c r="V29" s="2">
         <v>11</v>
       </c>
-      <c r="W29" s="2"/>
+      <c r="W29" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="2">
-        <v>2204023</v>
+        <v>2204202</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2615,34 +2719,34 @@
         <v>29</v>
       </c>
       <c r="D30" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F30" s="2">
-        <v>73.5</v>
+        <v>52.5</v>
       </c>
       <c r="G30" s="2">
-        <v>31.398180190000001</v>
+        <v>23.333333329999999</v>
       </c>
       <c r="H30" s="2">
-        <v>0.30204081599999999</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>9</v>
+        <v>0.29142857100000003</v>
+      </c>
+      <c r="I30" s="2">
+        <v>11.23</v>
       </c>
       <c r="J30" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K30" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="M30" s="2">
-        <v>10.94</v>
+        <v>11.23</v>
       </c>
       <c r="N30" s="2">
         <v>125</v>
@@ -2651,31 +2755,33 @@
         <v>0</v>
       </c>
       <c r="P30" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R30" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S30" s="2">
         <v>26</v>
       </c>
       <c r="T30" s="2">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="U30" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V30" s="2">
-        <v>11</v>
-      </c>
-      <c r="W30" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W30" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="2">
-        <v>2204202</v>
+        <v>2204531</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2684,546 +2790,562 @@
         <v>29</v>
       </c>
       <c r="D31" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2">
-        <v>150</v>
+        <v>142.19999999999999</v>
       </c>
       <c r="F31" s="2">
-        <v>52.5</v>
+        <v>39.9</v>
       </c>
       <c r="G31" s="2">
-        <v>23.333333329999999</v>
+        <v>19.732117949999999</v>
       </c>
       <c r="H31" s="2">
-        <v>0.29142857100000003</v>
+        <v>0.27819548900000002</v>
       </c>
       <c r="I31" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="J31" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K31" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L31" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="M31" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="N31" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="2">
         <v>-5</v>
       </c>
       <c r="R31" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S31" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T31" s="2">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="U31" s="2">
         <v>13</v>
       </c>
       <c r="V31" s="2">
-        <v>10</v>
-      </c>
-      <c r="W31" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W31" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="2">
-        <v>2204531</v>
+        <v>2204625</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D32" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2">
-        <v>142.19999999999999</v>
+        <v>177</v>
       </c>
       <c r="F32" s="2">
-        <v>39.9</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2">
-        <v>19.732117949999999</v>
+        <v>33.196080309999999</v>
       </c>
       <c r="H32" s="2">
-        <v>0.27819548900000002</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="J32" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K32" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L32" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M32" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="N32" s="2">
         <v>120</v>
       </c>
       <c r="O32" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="P32" s="2">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="Q32" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R32" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S32" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T32" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="U32" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V32" s="2">
         <v>9</v>
       </c>
-      <c r="W32" s="2"/>
+      <c r="W32" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="2">
-        <v>2204625</v>
+        <v>2204766</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E33" s="2">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F33" s="2">
-        <v>104</v>
+        <v>57.8</v>
       </c>
       <c r="G33" s="2">
-        <v>33.196080309999999</v>
+        <v>26.748114210000001</v>
       </c>
       <c r="H33" s="2">
-        <v>0</v>
+        <v>0.150519031</v>
       </c>
       <c r="I33" s="2">
-        <v>10.69</v>
+        <v>10.54</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K33" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M33" s="2">
-        <v>10.69</v>
+        <v>9.49</v>
       </c>
       <c r="N33" s="2">
+        <v>130</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2">
         <v>120</v>
-      </c>
-      <c r="O33" s="2">
-        <v>-10</v>
-      </c>
-      <c r="P33" s="2">
-        <v>140</v>
       </c>
       <c r="Q33" s="2">
         <v>-10</v>
       </c>
       <c r="R33" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S33" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="T33" s="2">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U33" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V33" s="2">
         <v>9</v>
       </c>
-      <c r="W33" s="2"/>
+      <c r="W33" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="2">
-        <v>2204766</v>
+        <v>2300143</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2">
-        <v>147</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="F34" s="2">
-        <v>57.8</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G34" s="2">
-        <v>26.748114210000001</v>
+        <v>27.794048960000001</v>
       </c>
       <c r="H34" s="2">
-        <v>0.150519031</v>
+        <v>0.19440353499999999</v>
       </c>
       <c r="I34" s="2">
-        <v>10.54</v>
+        <v>12.89</v>
       </c>
       <c r="J34" s="2">
+        <v>48</v>
+      </c>
+      <c r="K34" s="2">
         <v>12</v>
       </c>
-      <c r="K34" s="2">
-        <v>24</v>
-      </c>
       <c r="L34" s="2">
+        <v>125</v>
+      </c>
+      <c r="M34" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="N34" s="2">
         <v>110</v>
       </c>
-      <c r="M34" s="2">
-        <v>9.49</v>
-      </c>
-      <c r="N34" s="2">
-        <v>130</v>
-      </c>
       <c r="O34" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P34" s="2">
         <v>120</v>
       </c>
       <c r="Q34" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R34" s="2">
         <v>20</v>
       </c>
       <c r="S34" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="T34" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U34" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V34" s="2">
-        <v>9</v>
-      </c>
-      <c r="W34" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="W34" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="2">
-        <v>2300143</v>
+        <v>2300176</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2">
-        <v>156.30000000000001</v>
+        <v>152.5</v>
       </c>
       <c r="F35" s="2">
-        <v>67.900000000000006</v>
+        <v>64.8</v>
       </c>
       <c r="G35" s="2">
-        <v>27.794048960000001</v>
+        <v>27.86347756</v>
       </c>
       <c r="H35" s="2">
-        <v>0.19440353499999999</v>
+        <v>0.17129629599999999</v>
       </c>
       <c r="I35" s="2">
-        <v>12.89</v>
+        <v>11.68</v>
       </c>
       <c r="J35" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K35" s="2">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L35" s="2">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="M35" s="2">
-        <v>12.56</v>
+        <v>11.68</v>
       </c>
       <c r="N35" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O35" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P35" s="2">
         <v>120</v>
       </c>
       <c r="Q35" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R35" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" s="2">
         <v>20</v>
       </c>
-      <c r="S35" s="2">
-        <v>32</v>
-      </c>
       <c r="T35" s="2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="U35" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V35" s="2">
-        <v>14</v>
-      </c>
-      <c r="W35" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="W35" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="2">
-        <v>2300176</v>
+        <v>2300484</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E36" s="2">
-        <v>152.5</v>
+        <v>146</v>
       </c>
       <c r="F36" s="2">
-        <v>64.8</v>
+        <v>58</v>
       </c>
       <c r="G36" s="2">
-        <v>27.86347756</v>
+        <v>27.209607810000001</v>
       </c>
       <c r="H36" s="2">
-        <v>0.17129629599999999</v>
+        <v>0.212068966</v>
       </c>
       <c r="I36" s="2">
-        <v>11.68</v>
+        <v>13.33</v>
       </c>
       <c r="J36" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L36" s="2">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="M36" s="2">
-        <v>11.68</v>
+        <v>13.33</v>
       </c>
       <c r="N36" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O36" s="2">
         <v>0</v>
       </c>
       <c r="P36" s="2">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R36" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S36" s="2">
         <v>20</v>
       </c>
       <c r="T36" s="2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="U36" s="2">
         <v>13</v>
       </c>
       <c r="V36" s="2">
-        <v>12</v>
-      </c>
-      <c r="W36" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W36" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:23">
       <c r="A37" s="2">
-        <v>2300484</v>
+        <v>2300760</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D37" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F37" s="2">
-        <v>58</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="G37" s="2">
-        <v>27.209607810000001</v>
+        <v>24.390243900000002</v>
       </c>
       <c r="H37" s="2">
-        <v>0.212068966</v>
+        <v>0.33231707300000002</v>
       </c>
       <c r="I37" s="2">
-        <v>13.33</v>
+        <v>10.94</v>
       </c>
       <c r="J37" s="2">
+        <v>30</v>
+      </c>
+      <c r="K37" s="2">
+        <v>21</v>
+      </c>
+      <c r="L37" s="2">
+        <v>105</v>
+      </c>
+      <c r="M37" s="2">
+        <v>12.29</v>
+      </c>
+      <c r="N37" s="2">
+        <v>115</v>
+      </c>
+      <c r="O37" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P37" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R37" s="2">
+        <v>8</v>
+      </c>
+      <c r="S37" s="2">
         <v>24</v>
       </c>
-      <c r="K37" s="2">
-        <v>17</v>
-      </c>
-      <c r="L37" s="2">
-        <v>121</v>
-      </c>
-      <c r="M37" s="2">
-        <v>13.33</v>
-      </c>
-      <c r="N37" s="2">
-        <v>120</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2">
-        <v>135</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R37" s="2">
-        <v>22</v>
-      </c>
-      <c r="S37" s="2">
-        <v>20</v>
-      </c>
       <c r="T37" s="2">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="U37" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V37" s="2">
-        <v>9</v>
-      </c>
-      <c r="W37" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="W37" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:23">
       <c r="A38" s="2">
-        <v>2300760</v>
+        <v>2301202</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2">
         <v>74</v>
       </c>
       <c r="E38" s="2">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2">
-        <v>65.599999999999994</v>
+        <v>47.15</v>
       </c>
       <c r="G38" s="2">
-        <v>24.390243900000002</v>
+        <v>22.425683710000001</v>
       </c>
       <c r="H38" s="2">
-        <v>0.33231707300000002</v>
+        <v>9.3319193999999994E-2</v>
       </c>
       <c r="I38" s="2">
-        <v>10.94</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="J38" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K38" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M38" s="2">
-        <v>12.29</v>
+        <v>9.31</v>
       </c>
       <c r="N38" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O38" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P38" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q38" s="2">
-        <v>-20</v>
+        <v>15</v>
       </c>
       <c r="R38" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S38" s="2">
         <v>24</v>
       </c>
       <c r="T38" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="U38" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V38" s="2">
-        <v>11</v>
-      </c>
-      <c r="W38" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W38" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:23">
       <c r="A39" s="2">
@@ -3233,196 +3355,200 @@
         <v>1</v>
       </c>
       <c r="C39" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39" s="2">
         <v>74</v>
       </c>
       <c r="E39" s="2">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F39" s="2">
-        <v>47.15</v>
+        <v>49.1</v>
       </c>
       <c r="G39" s="2">
-        <v>22.425683710000001</v>
+        <v>23.19292403</v>
       </c>
       <c r="H39" s="2">
-        <v>9.3319193999999994E-2</v>
+        <v>0.15071283099999999</v>
       </c>
       <c r="I39" s="2">
-        <v>9.3800000000000008</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="J39" s="2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K39" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="M39" s="2">
-        <v>9.31</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="N39" s="2">
+        <v>130</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
         <v>125</v>
       </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2">
-        <v>120</v>
-      </c>
       <c r="Q39" s="2">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="R39" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S39" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T39" s="2">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="U39" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V39" s="2">
-        <v>10</v>
-      </c>
-      <c r="W39" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="W39" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:23">
       <c r="A40" s="2">
-        <v>2301202</v>
+        <v>2301430</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" s="7">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2">
-        <v>145.5</v>
+        <v>145.30000000000001</v>
       </c>
       <c r="F40" s="2">
-        <v>49.1</v>
+        <v>68.5</v>
       </c>
       <c r="G40" s="2">
-        <v>23.19292403</v>
+        <v>32.445863959999997</v>
       </c>
       <c r="H40" s="2">
-        <v>0.15071283099999999</v>
-      </c>
-      <c r="I40" s="2">
-        <v>8.2100000000000009</v>
+        <v>0.12700729899999999</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="J40" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K40" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L40" s="2">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="M40" s="2">
-        <v>8.2100000000000009</v>
+        <v>16.91</v>
       </c>
       <c r="N40" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q40" s="2">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="R40" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="S40" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T40" s="2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="U40" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V40" s="2">
+        <v>9</v>
+      </c>
+      <c r="W40" s="2">
         <v>8</v>
       </c>
-      <c r="W40" s="2"/>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="2">
-        <v>2301430</v>
+        <v>2301506</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" s="7">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2">
-        <v>145.30000000000001</v>
+        <v>158</v>
       </c>
       <c r="F41" s="2">
-        <v>68.5</v>
+        <v>76.7</v>
       </c>
       <c r="G41" s="2">
-        <v>32.445863959999997</v>
+        <v>30.724242910000001</v>
       </c>
       <c r="H41" s="2">
-        <v>0.12700729899999999</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>10</v>
+        <v>0.177314211</v>
+      </c>
+      <c r="I41" s="2">
+        <v>9.9</v>
       </c>
       <c r="J41" s="2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2">
+        <v>150</v>
+      </c>
+      <c r="M41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="N41" s="2">
+        <v>125</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>-5</v>
+      </c>
+      <c r="R41" s="2">
         <v>24</v>
       </c>
-      <c r="L41" s="2">
-        <v>109</v>
-      </c>
-      <c r="M41" s="2">
-        <v>16.91</v>
-      </c>
-      <c r="N41" s="2">
-        <v>115</v>
-      </c>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2">
-        <v>115</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R41" s="2">
-        <v>17</v>
-      </c>
       <c r="S41" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="T41" s="2">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="U41" s="2">
         <v>15</v>
@@ -3430,421 +3556,435 @@
       <c r="V41" s="2">
         <v>9</v>
       </c>
-      <c r="W41" s="2"/>
+      <c r="W41" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="2">
-        <v>2301506</v>
+        <v>2301620</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" s="7">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E42" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F42" s="2">
-        <v>76.7</v>
+        <v>66.5</v>
       </c>
       <c r="G42" s="2">
-        <v>30.724242910000001</v>
+        <v>29.95360569</v>
       </c>
       <c r="H42" s="2">
-        <v>0.177314211</v>
+        <v>0.19398496200000001</v>
       </c>
       <c r="I42" s="2">
         <v>9.9</v>
       </c>
       <c r="J42" s="2">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K42" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M42" s="2">
         <v>9.9</v>
       </c>
       <c r="N42" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="O42" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="P42" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q42" s="2">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="R42" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="S42" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T42" s="2">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="U42" s="2">
         <v>15</v>
       </c>
       <c r="V42" s="2">
-        <v>9</v>
-      </c>
-      <c r="W42" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="W42" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="2">
-        <v>2301620</v>
+        <v>2301878</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2">
-        <v>149</v>
+        <v>139.5</v>
       </c>
       <c r="F43" s="2">
-        <v>66.5</v>
+        <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>29.95360569</v>
+        <v>25.693400650000001</v>
       </c>
       <c r="H43" s="2">
-        <v>0.19398496200000001</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="I43" s="2">
-        <v>9.9</v>
+        <v>12.19</v>
       </c>
       <c r="J43" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K43" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L43" s="2">
+        <v>76</v>
+      </c>
+      <c r="M43" s="2">
+        <v>12.19</v>
+      </c>
+      <c r="N43" s="2">
+        <v>115</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
         <v>120</v>
       </c>
-      <c r="M43" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="N43" s="2">
-        <v>110</v>
-      </c>
-      <c r="O43" s="2">
-        <v>-15</v>
-      </c>
-      <c r="P43" s="2">
-        <v>115</v>
-      </c>
       <c r="Q43" s="2">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="R43" s="2">
+        <v>16</v>
+      </c>
+      <c r="S43" s="2">
         <v>18</v>
       </c>
-      <c r="S43" s="2">
-        <v>28</v>
-      </c>
       <c r="T43" s="2">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="U43" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V43" s="2">
-        <v>8</v>
-      </c>
-      <c r="W43" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="W43" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="2">
-        <v>2301878</v>
+        <v>2301974</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" s="7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2">
-        <v>139.5</v>
+        <v>151.5</v>
       </c>
       <c r="F44" s="2">
-        <v>50</v>
+        <v>66.5</v>
       </c>
       <c r="G44" s="2">
-        <v>25.693400650000001</v>
+        <v>28.97319435</v>
       </c>
       <c r="H44" s="2">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="I44" s="2">
-        <v>12.19</v>
+        <v>0.34887217999999998</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="J44" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K44" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="M44" s="2">
-        <v>12.19</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="N44" s="2">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q44" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R44" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S44" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="T44" s="2">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="U44" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V44" s="2">
-        <v>11</v>
-      </c>
-      <c r="W44" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W44" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="2">
-        <v>2301974</v>
+        <v>2303599</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" s="7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2">
-        <v>151.5</v>
+        <v>148</v>
       </c>
       <c r="F45" s="2">
-        <v>66.5</v>
+        <v>68.3</v>
       </c>
       <c r="G45" s="2">
-        <v>28.97319435</v>
+        <v>31.181519359999999</v>
       </c>
       <c r="H45" s="2">
-        <v>0.34887217999999998</v>
-      </c>
-      <c r="I45" s="2" t="s">
+        <v>9.2240116999999996E-2</v>
+      </c>
+      <c r="I45" s="2">
+        <v>12.44</v>
+      </c>
+      <c r="J45" s="2">
+        <v>41</v>
+      </c>
+      <c r="K45" s="2">
+        <v>31</v>
+      </c>
+      <c r="L45" s="2">
+        <v>83</v>
+      </c>
+      <c r="M45" s="2">
+        <v>12.33</v>
+      </c>
+      <c r="N45" s="2">
+        <v>120</v>
+      </c>
+      <c r="O45" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P45" s="2">
+        <v>-15</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>130</v>
+      </c>
+      <c r="R45" s="2">
+        <v>16</v>
+      </c>
+      <c r="S45" s="2">
+        <v>22</v>
+      </c>
+      <c r="T45" s="2">
+        <v>34</v>
+      </c>
+      <c r="U45" s="2">
+        <v>15</v>
+      </c>
+      <c r="V45" s="2">
         <v>11</v>
       </c>
-      <c r="J45" s="2">
-        <v>25</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2">
-        <v>118</v>
-      </c>
-      <c r="M45" s="2">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="N45" s="2">
-        <v>130</v>
-      </c>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R45" s="2">
-        <v>23</v>
-      </c>
-      <c r="S45" s="2">
-        <v>32</v>
-      </c>
-      <c r="T45" s="2">
-        <v>53</v>
-      </c>
-      <c r="U45" s="2">
-        <v>12</v>
-      </c>
-      <c r="V45" s="2">
-        <v>10</v>
-      </c>
-      <c r="W45" s="2"/>
+      <c r="W45" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="2">
-        <v>2303599</v>
+        <v>2304093</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2">
-        <v>148</v>
+        <v>142.5</v>
       </c>
       <c r="F46" s="2">
-        <v>68.3</v>
+        <v>42</v>
       </c>
       <c r="G46" s="2">
-        <v>31.181519359999999</v>
+        <v>20.68328717</v>
       </c>
       <c r="H46" s="2">
-        <v>9.2240116999999996E-2</v>
-      </c>
-      <c r="I46" s="2">
-        <v>12.44</v>
+        <v>0.18333333299999999</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="J46" s="2">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K46" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="M46" s="2">
-        <v>12.33</v>
+        <v>11.69</v>
       </c>
       <c r="N46" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O46" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P46" s="2">
-        <v>-15</v>
+        <v>130</v>
       </c>
       <c r="Q46" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="R46" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S46" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="T46" s="2">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="U46" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V46" s="2">
-        <v>11</v>
-      </c>
-      <c r="W46" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="W46" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="2">
-        <v>2304093</v>
+        <v>2304321</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" s="7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E47" s="2">
-        <v>142.5</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2">
-        <v>42</v>
+        <v>62.2</v>
       </c>
       <c r="G47" s="2">
-        <v>20.68328717</v>
+        <v>29.179958719999998</v>
       </c>
       <c r="H47" s="2">
-        <v>0.18333333299999999</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>12</v>
+        <v>0.236334405</v>
+      </c>
+      <c r="I47" s="2">
+        <v>14.5</v>
       </c>
       <c r="J47" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K47" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L47" s="2">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="M47" s="2">
-        <v>11.69</v>
+        <v>14.5</v>
       </c>
       <c r="N47" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O47" s="2">
         <v>0</v>
       </c>
       <c r="P47" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q47" s="2">
+        <v>-15</v>
+      </c>
+      <c r="R47" s="2">
+        <v>16</v>
+      </c>
+      <c r="S47" s="2">
         <v>20</v>
       </c>
-      <c r="R47" s="2">
-        <v>23</v>
-      </c>
-      <c r="S47" s="2">
-        <v>38</v>
-      </c>
       <c r="T47" s="2">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="U47" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V47" s="2">
-        <v>7</v>
-      </c>
-      <c r="W47" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W47" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="2">
@@ -3863,28 +4003,28 @@
         <v>146</v>
       </c>
       <c r="F48" s="2">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="G48" s="2">
-        <v>29.179958719999998</v>
+        <v>29.08613248</v>
       </c>
       <c r="H48" s="2">
-        <v>0.236334405</v>
+        <v>0.23548387100000001</v>
       </c>
       <c r="I48" s="2">
-        <v>14.5</v>
+        <v>12.28</v>
       </c>
       <c r="J48" s="2">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K48" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L48" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M48" s="2">
-        <v>14.5</v>
+        <v>11.94</v>
       </c>
       <c r="N48" s="2">
         <v>120</v>
@@ -3893,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Q48" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R48" s="2">
         <v>16</v>
@@ -3905,19 +4045,21 @@
         <v>20</v>
       </c>
       <c r="T48" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U48" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V48" s="2">
-        <v>9</v>
-      </c>
-      <c r="W48" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="W48" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>2304321</v>
+        <v>2304669</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -3926,35 +4068,33 @@
         <v>29</v>
       </c>
       <c r="D49" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E49" s="2">
-        <v>146</v>
+        <v>164.5</v>
       </c>
       <c r="F49" s="2">
-        <v>62</v>
+        <v>77.8</v>
       </c>
       <c r="G49" s="2">
-        <v>29.08613248</v>
+        <v>28.750658250000001</v>
       </c>
       <c r="H49" s="2">
-        <v>0.23548387100000001</v>
+        <v>0.23264781500000001</v>
       </c>
       <c r="I49" s="2">
-        <v>12.28</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="K49" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L49" s="2">
-        <v>102</v>
-      </c>
-      <c r="M49" s="2">
-        <v>11.94</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="M49" s="1"/>
       <c r="N49" s="2">
         <v>120</v>
       </c>
@@ -3962,31 +4102,33 @@
         <v>0</v>
       </c>
       <c r="P49" s="2">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="Q49" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R49" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S49" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T49" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U49" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V49" s="2">
         <v>11</v>
       </c>
-      <c r="W49" s="2"/>
+      <c r="W49" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>2304669</v>
+        <v>2304770</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -3995,33 +4137,35 @@
         <v>29</v>
       </c>
       <c r="D50" s="2">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E50" s="2">
-        <v>164.5</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F50" s="2">
-        <v>77.8</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G50" s="2">
-        <v>28.750658250000001</v>
+        <v>27.80075321</v>
       </c>
       <c r="H50" s="2">
-        <v>0.23264781500000001</v>
+        <v>0.21739130400000001</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="J50" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" s="2">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L50" s="2">
-        <v>107</v>
-      </c>
-      <c r="M50" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="M50" s="2">
+        <v>6.93</v>
+      </c>
       <c r="N50" s="2">
         <v>120</v>
       </c>
@@ -4029,70 +4173,72 @@
         <v>0</v>
       </c>
       <c r="P50" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q50" s="2">
         <v>-5</v>
       </c>
       <c r="R50" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S50" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T50" s="2">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="U50" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V50" s="2">
         <v>11</v>
       </c>
-      <c r="W50" s="2"/>
+      <c r="W50" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>2304770</v>
+        <v>2400788</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D51" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E51" s="2">
-        <v>152.19999999999999</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="F51" s="2">
-        <v>64.400000000000006</v>
+        <v>63.8</v>
       </c>
       <c r="G51" s="2">
-        <v>27.80075321</v>
+        <v>24.705231349999998</v>
       </c>
       <c r="H51" s="2">
-        <v>0.21739130400000001</v>
+        <v>0.28056426299999998</v>
       </c>
       <c r="I51" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="J51" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K51" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L51" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="M51" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="N51" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O51" s="2">
         <v>0</v>
@@ -4101,162 +4247,168 @@
         <v>120</v>
       </c>
       <c r="Q51" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R51" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S51" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="T51" s="2">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="U51" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V51" s="2">
-        <v>11</v>
-      </c>
-      <c r="W51" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W51" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>2400788</v>
+        <v>2401195</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E52" s="2">
-        <v>160.69999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="F52" s="2">
-        <v>63.8</v>
+        <v>68.3</v>
       </c>
       <c r="G52" s="2">
-        <v>24.705231349999998</v>
+        <v>29.757431189999998</v>
       </c>
       <c r="H52" s="2">
-        <v>0.28056426299999998</v>
+        <v>0.33967789199999998</v>
       </c>
       <c r="I52" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="J52" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K52" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L52" s="2">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="M52" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="N52" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O52" s="2">
         <v>0</v>
       </c>
       <c r="P52" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q52" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R52" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="S52" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T52" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="U52" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V52" s="2">
-        <v>10</v>
-      </c>
-      <c r="W52" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="W52" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="1:23">
       <c r="A53" s="2">
-        <v>2401195</v>
+        <v>2401295</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E53" s="2">
-        <v>151.5</v>
+        <v>142</v>
       </c>
       <c r="F53" s="2">
-        <v>68.3</v>
+        <v>62</v>
       </c>
       <c r="G53" s="2">
-        <v>29.757431189999998</v>
+        <v>30.747867490000001</v>
       </c>
       <c r="H53" s="2">
-        <v>0.33967789199999998</v>
+        <v>0.44193548399999999</v>
       </c>
       <c r="I53" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="J53" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="L53" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M53" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="N53" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O53" s="2">
         <v>0</v>
       </c>
       <c r="P53" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q53" s="2">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="R53" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S53" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T53" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U53" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V53" s="2">
-        <v>8</v>
-      </c>
-      <c r="W53" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="W53" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="2">
@@ -4266,40 +4418,40 @@
         <v>1</v>
       </c>
       <c r="C54" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F54" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G54" s="2">
-        <v>30.747867490000001</v>
+        <v>29.830309549999999</v>
       </c>
       <c r="H54" s="2">
-        <v>0.44193548399999999</v>
+        <v>0.35081967200000003</v>
       </c>
       <c r="I54" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="J54" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K54" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L54" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="M54" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="N54" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O54" s="2">
         <v>0</v>
@@ -4308,16 +4460,16 @@
         <v>115</v>
       </c>
       <c r="Q54" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R54" s="2">
         <v>23</v>
       </c>
       <c r="S54" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T54" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="U54" s="2">
         <v>15</v>
@@ -4325,80 +4477,84 @@
       <c r="V54" s="2">
         <v>15</v>
       </c>
-      <c r="W54" s="2"/>
+      <c r="W54" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>2401295</v>
+        <v>2401534</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" s="7">
+        <v>29</v>
+      </c>
+      <c r="D55" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2">
+        <v>147.5</v>
+      </c>
+      <c r="F55" s="2">
+        <v>59.2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>27.21057167</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0.18243243200000001</v>
+      </c>
+      <c r="I55" s="2">
+        <v>10.86</v>
+      </c>
+      <c r="J55" s="2">
+        <v>25</v>
+      </c>
+      <c r="K55" s="2">
+        <v>10</v>
+      </c>
+      <c r="L55" s="2">
+        <v>125</v>
+      </c>
+      <c r="M55" s="2">
+        <v>10.91</v>
+      </c>
+      <c r="N55" s="2">
+        <v>120</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R55" s="2">
+        <v>18</v>
+      </c>
+      <c r="S55" s="2">
         <v>30</v>
       </c>
-      <c r="D55" s="2">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2">
-        <v>143</v>
-      </c>
-      <c r="F55" s="2">
-        <v>61</v>
-      </c>
-      <c r="G55" s="2">
-        <v>29.830309549999999</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0.35081967200000003</v>
-      </c>
-      <c r="I55" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="J55" s="2">
-        <v>50</v>
-      </c>
-      <c r="K55" s="2">
-        <v>47</v>
-      </c>
-      <c r="L55" s="2">
-        <v>93</v>
-      </c>
-      <c r="M55" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="N55" s="2">
-        <v>110</v>
-      </c>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>115</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R55" s="2">
-        <v>23</v>
-      </c>
-      <c r="S55" s="2">
-        <v>18</v>
-      </c>
       <c r="T55" s="2">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="U55" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V55" s="2">
-        <v>15</v>
-      </c>
-      <c r="W55" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W55" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>2401534</v>
+        <v>2401730</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -4407,67 +4563,69 @@
         <v>29</v>
       </c>
       <c r="D56" s="2">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E56" s="2">
-        <v>147.5</v>
+        <v>160</v>
       </c>
       <c r="F56" s="2">
-        <v>59.2</v>
+        <v>56</v>
       </c>
       <c r="G56" s="2">
-        <v>27.21057167</v>
+        <v>21.875</v>
       </c>
       <c r="H56" s="2">
-        <v>0.18243243200000001</v>
+        <v>0.14464285700000001</v>
       </c>
       <c r="I56" s="2">
-        <v>10.86</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="J56" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K56" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L56" s="2">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="M56" s="2">
-        <v>10.91</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N56" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O56" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P56" s="2">
         <v>120</v>
       </c>
       <c r="Q56" s="2">
-        <v>-10</v>
+        <v>-35</v>
       </c>
       <c r="R56" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S56" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="T56" s="2">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="U56" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V56" s="2">
-        <v>9</v>
-      </c>
-      <c r="W56" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="W56" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>2401730</v>
+        <v>2401922</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -4476,103 +4634,105 @@
         <v>29</v>
       </c>
       <c r="D57" s="2">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2">
-        <v>160</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="F57" s="2">
-        <v>56</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="G57" s="2">
-        <v>21.875</v>
+        <v>37.568624579999998</v>
       </c>
       <c r="H57" s="2">
-        <v>0.14464285700000001</v>
+        <v>0.16598079600000001</v>
       </c>
       <c r="I57" s="2">
-        <v>39.229999999999997</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="J57" s="2">
         <v>29</v>
       </c>
       <c r="K57" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L57" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M57" s="2">
-        <v>32.799999999999997</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="N57" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O57" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P57" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q57" s="2">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="R57" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S57" s="2">
+        <v>24</v>
+      </c>
+      <c r="T57" s="2">
+        <v>29</v>
+      </c>
+      <c r="U57" s="2">
         <v>12</v>
       </c>
-      <c r="T57" s="2">
-        <v>38</v>
-      </c>
-      <c r="U57" s="2">
-        <v>11</v>
-      </c>
       <c r="V57" s="2">
-        <v>11</v>
-      </c>
-      <c r="W57" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W57" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>2401922</v>
+        <v>2402032</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D58" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2">
-        <v>139.30000000000001</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="F58" s="2">
-        <v>72.900000000000006</v>
+        <v>57.3</v>
       </c>
       <c r="G58" s="2">
-        <v>37.568624579999998</v>
+        <v>25.568839749999999</v>
       </c>
       <c r="H58" s="2">
-        <v>0.16598079600000001</v>
+        <v>0.25828970299999998</v>
       </c>
       <c r="I58" s="2">
-        <v>17.829999999999998</v>
+        <v>9.26</v>
       </c>
       <c r="J58" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K58" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L58" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="M58" s="2">
-        <v>18.649999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="N58" s="2">
         <v>110</v>
@@ -4581,31 +4741,33 @@
         <v>0</v>
       </c>
       <c r="P58" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="R58" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S58" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T58" s="2">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="U58" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V58" s="2">
         <v>9</v>
       </c>
-      <c r="W58" s="2"/>
+      <c r="W58" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>2402032</v>
+        <v>2402281</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -4614,172 +4776,176 @@
         <v>31</v>
       </c>
       <c r="D59" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2">
-        <v>149.69999999999999</v>
+        <v>150</v>
       </c>
       <c r="F59" s="2">
-        <v>57.3</v>
+        <v>62</v>
       </c>
       <c r="G59" s="2">
-        <v>25.568839749999999</v>
+        <v>27.555555559999998</v>
       </c>
       <c r="H59" s="2">
-        <v>0.25828970299999998</v>
+        <v>0.20483871000000001</v>
       </c>
       <c r="I59" s="2">
-        <v>9.26</v>
+        <v>13.88</v>
       </c>
       <c r="J59" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K59" s="2">
+        <v>20</v>
+      </c>
+      <c r="L59" s="2">
+        <v>101</v>
+      </c>
+      <c r="M59" s="2">
+        <v>13.88</v>
+      </c>
+      <c r="N59" s="2">
+        <v>120</v>
+      </c>
+      <c r="O59" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P59" s="2">
+        <v>130</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R59" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" s="2">
         <v>26</v>
       </c>
-      <c r="L59" s="2">
-        <v>135</v>
-      </c>
-      <c r="M59" s="2">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="N59" s="2">
-        <v>110</v>
-      </c>
-      <c r="O59" s="2">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2">
-        <v>100</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2">
-        <v>19</v>
-      </c>
-      <c r="S59" s="2">
-        <v>28</v>
-      </c>
       <c r="T59" s="2">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="U59" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V59" s="2">
-        <v>9</v>
-      </c>
-      <c r="W59" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="W59" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>2402281</v>
+        <v>2403315</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E60" s="2">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F60" s="2">
-        <v>62</v>
+        <v>92.5</v>
       </c>
       <c r="G60" s="2">
-        <v>27.555555559999998</v>
+        <v>31.633665059999998</v>
       </c>
       <c r="H60" s="2">
-        <v>0.20483871000000001</v>
+        <v>0.23243243199999999</v>
       </c>
       <c r="I60" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="J60" s="2">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K60" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L60" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M60" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="N60" s="2">
         <v>120</v>
       </c>
       <c r="O60" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P60" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q60" s="2">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="R60" s="2">
         <v>20</v>
       </c>
       <c r="S60" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T60" s="2">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="U60" s="2">
         <v>14</v>
       </c>
       <c r="V60" s="2">
-        <v>8</v>
-      </c>
-      <c r="W60" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W60" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>2402895</v>
+        <v>2403413</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D61" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2">
-        <v>170.5</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="F61" s="2">
-        <v>76.900000000000006</v>
+        <v>65.2</v>
       </c>
       <c r="G61" s="2">
-        <v>26.453160879999999</v>
+        <v>28.519638310000001</v>
       </c>
       <c r="H61" s="2">
-        <v>0.13133940199999999</v>
+        <v>0.20552147200000001</v>
       </c>
       <c r="I61" s="2">
-        <v>14.13</v>
+        <v>12.39</v>
       </c>
       <c r="J61" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K61" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L61" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="M61" s="2">
-        <v>14.49</v>
+        <v>12.39</v>
       </c>
       <c r="N61" s="2">
         <v>120</v>
@@ -4791,67 +4957,69 @@
         <v>120</v>
       </c>
       <c r="Q61" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R61" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S61" s="2">
         <v>22</v>
       </c>
       <c r="T61" s="2">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U61" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V61" s="2">
         <v>8</v>
       </c>
-      <c r="W61" s="2"/>
+      <c r="W61" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>2403315</v>
+        <v>2403725</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D62" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E62" s="2">
-        <v>171</v>
+        <v>165.5</v>
       </c>
       <c r="F62" s="2">
-        <v>92.5</v>
+        <v>79</v>
       </c>
       <c r="G62" s="2">
-        <v>31.633665059999998</v>
+        <v>28.842380039999998</v>
       </c>
       <c r="H62" s="2">
-        <v>0.23243243199999999</v>
+        <v>0.20506329100000001</v>
       </c>
       <c r="I62" s="2">
-        <v>12.89</v>
+        <v>9.64</v>
       </c>
       <c r="J62" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K62" s="2">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L62" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="M62" s="2">
-        <v>12.89</v>
+        <v>9.64</v>
       </c>
       <c r="N62" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O62" s="2">
         <v>0</v>
@@ -4860,64 +5028,66 @@
         <v>120</v>
       </c>
       <c r="Q62" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R62" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S62" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T62" s="2">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="U62" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V62" s="2">
         <v>9</v>
       </c>
-      <c r="W62" s="2"/>
+      <c r="W62" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>2403413</v>
+        <v>2403883</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" s="7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D63" s="2">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E63" s="2">
-        <v>151.19999999999999</v>
+        <v>158.1</v>
       </c>
       <c r="F63" s="2">
-        <v>65.2</v>
+        <v>66</v>
       </c>
       <c r="G63" s="2">
-        <v>28.519638310000001</v>
+        <v>26.40463665</v>
       </c>
       <c r="H63" s="2">
-        <v>0.20552147200000001</v>
+        <v>0.192424242</v>
       </c>
       <c r="I63" s="2">
-        <v>12.39</v>
+        <v>9.93</v>
       </c>
       <c r="J63" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K63" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L63" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="M63" s="2">
-        <v>12.39</v>
+        <v>9.93</v>
       </c>
       <c r="N63" s="2">
         <v>120</v>
@@ -4926,67 +5096,69 @@
         <v>0</v>
       </c>
       <c r="P63" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q63" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R63" s="2">
         <v>21</v>
       </c>
       <c r="S63" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T63" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="U63" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V63" s="2">
-        <v>8</v>
-      </c>
-      <c r="W63" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W63" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>2403725</v>
+        <v>8811223</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="7">
         <v>30</v>
       </c>
       <c r="D64" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2">
-        <v>165.5</v>
+        <v>154</v>
       </c>
       <c r="F64" s="2">
-        <v>79</v>
+        <v>49.4</v>
       </c>
       <c r="G64" s="2">
-        <v>28.842380039999998</v>
+        <v>20.829819530000002</v>
       </c>
       <c r="H64" s="2">
-        <v>0.20506329100000001</v>
+        <v>0.17813765200000001</v>
       </c>
       <c r="I64" s="2">
-        <v>9.64</v>
+        <v>9.11</v>
       </c>
       <c r="J64" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K64" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L64" s="2">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="M64" s="2">
-        <v>9.64</v>
+        <v>10.89</v>
       </c>
       <c r="N64" s="2">
         <v>125</v>
@@ -4998,28 +5170,30 @@
         <v>120</v>
       </c>
       <c r="Q64" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R64" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S64" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="T64" s="2">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="U64" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V64" s="2">
-        <v>9</v>
-      </c>
-      <c r="W64" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W64" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" spans="1:23">
       <c r="A65" s="2">
-        <v>2403883</v>
+        <v>8852227</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -5028,34 +5202,34 @@
         <v>29</v>
       </c>
       <c r="D65" s="2">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E65" s="2">
-        <v>158.1</v>
+        <v>151</v>
       </c>
       <c r="F65" s="2">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="G65" s="2">
-        <v>26.40463665</v>
+        <v>28.726810230000002</v>
       </c>
       <c r="H65" s="2">
-        <v>0.192424242</v>
+        <v>0.17251908399999999</v>
       </c>
       <c r="I65" s="2">
-        <v>9.93</v>
+        <v>10.27</v>
       </c>
       <c r="J65" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K65" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L65" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M65" s="2">
-        <v>9.93</v>
+        <v>11.38</v>
       </c>
       <c r="N65" s="2">
         <v>120</v>
@@ -5064,31 +5238,33 @@
         <v>0</v>
       </c>
       <c r="P65" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="Q65" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R65" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S65" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="T65" s="2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="U65" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V65" s="2">
-        <v>9</v>
-      </c>
-      <c r="W65" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="W65" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>8811223</v>
+        <v>8852227</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -5097,37 +5273,37 @@
         <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F66" s="2">
-        <v>49.4</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G66" s="2">
-        <v>20.829819530000002</v>
+        <v>28.244375250000001</v>
       </c>
       <c r="H66" s="2">
-        <v>0.17813765200000001</v>
+        <v>0.189440994</v>
       </c>
       <c r="I66" s="2">
-        <v>9.11</v>
+        <v>10.63</v>
       </c>
       <c r="J66" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K66" s="2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L66" s="2">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="M66" s="2">
-        <v>10.89</v>
+        <v>10.63</v>
       </c>
       <c r="N66" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O66" s="2">
         <v>0</v>
@@ -5136,304 +5312,314 @@
         <v>120</v>
       </c>
       <c r="Q66" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R66" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S66" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T66" s="2">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="U66" s="2">
         <v>15</v>
       </c>
       <c r="V66" s="2">
-        <v>10</v>
-      </c>
-      <c r="W66" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W66" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>8852227</v>
+        <v>9005400</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D67" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E67" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F67" s="2">
-        <v>65.5</v>
+        <v>77.3</v>
       </c>
       <c r="G67" s="2">
-        <v>28.726810230000002</v>
+        <v>30.1953125</v>
       </c>
       <c r="H67" s="2">
-        <v>0.17251908399999999</v>
+        <v>0.168175938</v>
       </c>
       <c r="I67" s="2">
-        <v>10.27</v>
+        <v>17.73</v>
       </c>
       <c r="J67" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K67" s="2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="L67" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="M67" s="2">
-        <v>11.38</v>
+        <v>17.73</v>
       </c>
       <c r="N67" s="2">
         <v>120</v>
       </c>
       <c r="O67" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P67" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Q67" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R67" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S67" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="T67" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="U67" s="2">
+        <v>12</v>
+      </c>
+      <c r="V67" s="2">
         <v>10</v>
       </c>
-      <c r="V67" s="2">
-        <v>13</v>
-      </c>
-      <c r="W67" s="2"/>
+      <c r="W67" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>8852227</v>
+        <v>9209245</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D68" s="2">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E68" s="2">
-        <v>151</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="F68" s="2">
-        <v>64.400000000000006</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="G68" s="2">
-        <v>28.244375250000001</v>
+        <v>28.97396552</v>
       </c>
       <c r="H68" s="2">
-        <v>0.189440994</v>
+        <v>0.17597765400000001</v>
       </c>
       <c r="I68" s="2">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
       <c r="J68" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K68" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L68" s="2">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="M68" s="2">
-        <v>10.63</v>
+        <v>10.67</v>
       </c>
       <c r="N68" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O68" s="2">
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q68" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R68" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S68" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T68" s="2">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="U68" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V68" s="2">
-        <v>9</v>
-      </c>
-      <c r="W68" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="W68" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:23">
       <c r="A69" s="2">
-        <v>9005400</v>
+        <v>9301565</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D69" s="2">
+        <v>58</v>
+      </c>
+      <c r="E69" s="2">
+        <v>152.5</v>
+      </c>
+      <c r="F69" s="2">
+        <v>78.3</v>
+      </c>
+      <c r="G69" s="2">
+        <v>33.668368719999997</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0.20945083</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="2">
+        <v>44</v>
+      </c>
+      <c r="K69" s="2">
+        <v>22</v>
+      </c>
+      <c r="L69" s="2">
+        <v>127</v>
+      </c>
+      <c r="M69" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="N69" s="2">
+        <v>130</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R69" s="2">
+        <v>19</v>
+      </c>
+      <c r="S69" s="2">
+        <v>24</v>
+      </c>
+      <c r="T69" s="2">
         <v>71</v>
-      </c>
-      <c r="E69" s="2">
-        <v>160</v>
-      </c>
-      <c r="F69" s="2">
-        <v>77.3</v>
-      </c>
-      <c r="G69" s="2">
-        <v>30.1953125</v>
-      </c>
-      <c r="H69" s="2">
-        <v>0.168175938</v>
-      </c>
-      <c r="I69" s="2">
-        <v>17.73</v>
-      </c>
-      <c r="J69" s="2">
-        <v>41</v>
-      </c>
-      <c r="K69" s="2">
-        <v>33</v>
-      </c>
-      <c r="L69" s="2">
-        <v>82</v>
-      </c>
-      <c r="M69" s="2">
-        <v>17.73</v>
-      </c>
-      <c r="N69" s="2">
-        <v>120</v>
-      </c>
-      <c r="O69" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P69" s="2">
-        <v>110</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2">
-        <v>12</v>
-      </c>
-      <c r="S69" s="2">
-        <v>14</v>
-      </c>
-      <c r="T69" s="2">
-        <v>46</v>
       </c>
       <c r="U69" s="2">
         <v>12</v>
       </c>
       <c r="V69" s="2">
-        <v>10</v>
-      </c>
-      <c r="W69" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="W69" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>9209245</v>
+        <v>9301565</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" s="7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E70" s="2">
-        <v>157.19999999999999</v>
+        <v>153</v>
       </c>
       <c r="F70" s="2">
-        <v>71.599999999999994</v>
+        <v>80.8</v>
       </c>
       <c r="G70" s="2">
-        <v>28.97396552</v>
+        <v>34.516638899999997</v>
       </c>
       <c r="H70" s="2">
-        <v>0.17597765400000001</v>
-      </c>
-      <c r="I70" s="2">
-        <v>10.62</v>
+        <v>0.21534653500000001</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="J70" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K70" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L70" s="2">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="M70" s="2">
-        <v>10.67</v>
+        <v>8.59</v>
       </c>
       <c r="N70" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O70" s="2">
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="Q70" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R70" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S70" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="T70" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U70" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V70" s="2">
-        <v>10</v>
-      </c>
-      <c r="W70" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="W70" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:23">
       <c r="A71" s="2">
-        <v>9301565</v>
+        <v>9508610</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -5442,37 +5628,37 @@
         <v>29</v>
       </c>
       <c r="D71" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E71" s="2">
-        <v>152.5</v>
+        <v>151</v>
       </c>
       <c r="F71" s="2">
-        <v>78.3</v>
+        <v>55.4</v>
       </c>
       <c r="G71" s="2">
-        <v>33.668368719999997</v>
+        <v>24.29717995</v>
       </c>
       <c r="H71" s="2">
-        <v>0.20945083</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>13</v>
+        <v>0.20216606500000001</v>
+      </c>
+      <c r="I71" s="2">
+        <v>7.96</v>
       </c>
       <c r="J71" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K71" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L71" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M71" s="2">
-        <v>9.0500000000000007</v>
+        <v>8.09</v>
       </c>
       <c r="N71" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O71" s="2">
         <v>0</v>
@@ -5481,206 +5667,91 @@
         <v>120</v>
       </c>
       <c r="Q71" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R71" s="2">
         <v>19</v>
       </c>
       <c r="S71" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T71" s="2">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="U71" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V71" s="2">
-        <v>13</v>
-      </c>
-      <c r="W71" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="W71" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="72" spans="1:23">
-      <c r="A72" s="2">
-        <v>9301565</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" s="7">
-        <v>29</v>
-      </c>
-      <c r="D72" s="2">
-        <v>58</v>
-      </c>
-      <c r="E72" s="2">
-        <v>153</v>
-      </c>
-      <c r="F72" s="2">
-        <v>80.8</v>
-      </c>
-      <c r="G72" s="2">
-        <v>34.516638899999997</v>
-      </c>
-      <c r="H72" s="2">
-        <v>0.21534653500000001</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J72" s="2">
-        <v>29</v>
-      </c>
-      <c r="K72" s="2">
-        <v>15</v>
-      </c>
-      <c r="L72" s="2">
-        <v>127</v>
-      </c>
-      <c r="M72" s="2">
-        <v>8.59</v>
-      </c>
-      <c r="N72" s="2">
-        <v>115</v>
-      </c>
-      <c r="O72" s="2">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R72" s="2">
-        <v>20</v>
-      </c>
-      <c r="S72" s="2">
-        <v>30</v>
-      </c>
-      <c r="T72" s="2">
-        <v>64</v>
-      </c>
-      <c r="U72" s="2">
-        <v>13</v>
-      </c>
-      <c r="V72" s="2">
-        <v>13</v>
-      </c>
-      <c r="W72" s="2"/>
+      <c r="A72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="73" spans="1:23">
-      <c r="A73" s="2">
-        <v>9508610</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73" s="7">
-        <v>29</v>
-      </c>
-      <c r="D73" s="2">
-        <v>72</v>
-      </c>
-      <c r="E73" s="2">
-        <v>151</v>
-      </c>
-      <c r="F73" s="2">
-        <v>55.4</v>
-      </c>
-      <c r="G73" s="2">
-        <v>24.29717995</v>
-      </c>
-      <c r="H73" s="2">
-        <v>0.20216606500000001</v>
-      </c>
-      <c r="I73" s="2">
-        <v>7.96</v>
-      </c>
-      <c r="J73" s="2">
-        <v>34</v>
-      </c>
-      <c r="K73" s="2">
-        <v>17</v>
-      </c>
-      <c r="L73" s="2">
-        <v>115</v>
-      </c>
-      <c r="M73" s="2">
-        <v>8.09</v>
-      </c>
-      <c r="N73" s="2">
-        <v>125</v>
-      </c>
-      <c r="O73" s="2">
-        <v>0</v>
-      </c>
-      <c r="P73" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q73" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R73" s="2">
-        <v>19</v>
-      </c>
-      <c r="S73" s="2">
-        <v>28</v>
-      </c>
-      <c r="T73" s="2">
-        <v>59</v>
-      </c>
-      <c r="U73" s="2">
-        <v>13</v>
-      </c>
-      <c r="V73" s="2">
-        <v>9</v>
-      </c>
-      <c r="W73" s="2"/>
+      <c r="A73" s="1"/>
+      <c r="T73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
       <c r="T74" s="2"/>
-      <c r="U74" s="1"/>
       <c r="V74" s="2"/>
-      <c r="W74" s="2"/>
+      <c r="W74" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:23">
       <c r="A75" s="1"/>
-      <c r="T75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
+      <c r="T75" s="4"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:23">
       <c r="A76" s="1"/>
-      <c r="T76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
+      <c r="W76" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:23">
       <c r="A77" s="1"/>
-      <c r="T77" s="4"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
+      <c r="W77" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="78" spans="1:23">
       <c r="A78" s="1"/>
+      <c r="W78" s="1"/>
     </row>
     <row r="79" spans="1:23">
       <c r="A79" s="1"/>
@@ -7007,12 +7078,6 @@
     </row>
     <row r="520" spans="1:1">
       <c r="A520" s="1"/>
-    </row>
-    <row r="521" spans="1:1">
-      <c r="A521" s="1"/>
-    </row>
-    <row r="522" spans="1:1">
-      <c r="A522" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/main.xlsx
+++ b/main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuk\Desktop\TKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ED1BA3-8C8E-9044-BEA9-B5A1E8BB0E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068A53A5-A7BF-45D5-AB94-C1745E4B07CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>年齢（歳）</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>11’69</t>
-  </si>
-  <si>
-    <t>9’05</t>
   </si>
   <si>
     <t>9’20</t>
@@ -148,6 +145,10 @@
   </si>
   <si>
     <t>sex</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>9’05</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -287,9 +288,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -327,7 +328,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -433,7 +434,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -575,7 +576,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -583,32 +584,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:X522"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <dimension ref="A1:W520"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.69140625" customWidth="1"/>
+    <col min="3" max="3" width="17.3046875" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.84375" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
-    <col min="16" max="16" width="22.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.69140625" customWidth="1"/>
+    <col min="16" max="16" width="22.3828125" customWidth="1"/>
+    <col min="17" max="17" width="23.69140625" customWidth="1"/>
     <col min="18" max="18" width="24" customWidth="1"/>
-    <col min="19" max="20" width="22.42578125" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="19" max="20" width="22.3828125" customWidth="1"/>
+    <col min="21" max="21" width="13.69140625" customWidth="1"/>
     <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="18.140625" customWidth="1"/>
+    <col min="23" max="23" width="18.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:23">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -629,50 +630,47 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="W1" s="1"/>
-      <c r="X1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="2">
         <v>508469</v>
       </c>
@@ -741,7 +739,7 @@
       </c>
       <c r="W2" s="1"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:23">
       <c r="A3" s="2">
         <v>910870</v>
       </c>
@@ -810,7 +808,7 @@
       </c>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:23">
       <c r="A4" s="2">
         <v>1400396</v>
       </c>
@@ -879,7 +877,7 @@
       </c>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:23">
       <c r="A5" s="2">
         <v>1403057</v>
       </c>
@@ -948,7 +946,7 @@
       </c>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:23">
       <c r="A6" s="2">
         <v>1501605</v>
       </c>
@@ -1017,7 +1015,7 @@
       </c>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:23">
       <c r="A7" s="2">
         <v>1900753</v>
       </c>
@@ -1086,7 +1084,7 @@
       </c>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:23">
       <c r="A8" s="2">
         <v>1902085</v>
       </c>
@@ -1155,7 +1153,7 @@
       </c>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:23">
       <c r="A9" s="2">
         <v>1902300</v>
       </c>
@@ -1224,7 +1222,7 @@
       </c>
       <c r="W9" s="2"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:23">
       <c r="A10" s="2">
         <v>1905031</v>
       </c>
@@ -1293,7 +1291,7 @@
       </c>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:23">
       <c r="A11" s="2">
         <v>2001975</v>
       </c>
@@ -1362,7 +1360,7 @@
       </c>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:23">
       <c r="A12" s="2">
         <v>2002759</v>
       </c>
@@ -1431,7 +1429,7 @@
       </c>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:23">
       <c r="A13" s="2">
         <v>2003119</v>
       </c>
@@ -1500,7 +1498,7 @@
       </c>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:23">
       <c r="A14" s="2">
         <v>2003509</v>
       </c>
@@ -1569,7 +1567,7 @@
       </c>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:23">
       <c r="A15" s="2">
         <v>2003509</v>
       </c>
@@ -1638,7 +1636,7 @@
       </c>
       <c r="W15" s="2"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:23">
       <c r="A16" s="2">
         <v>2003643</v>
       </c>
@@ -2330,46 +2328,46 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="2">
-        <v>2202167</v>
+        <v>2202692</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" s="7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2">
-        <v>146.5</v>
+        <v>150</v>
       </c>
       <c r="F26" s="2">
-        <v>58</v>
+        <v>45.5</v>
       </c>
       <c r="G26" s="2">
-        <v>27.02419364</v>
+        <v>20.222222219999999</v>
       </c>
       <c r="H26" s="2">
-        <v>0.22068965500000001</v>
+        <v>0.19780219800000001</v>
       </c>
       <c r="I26" s="2">
-        <v>10.24</v>
+        <v>10.39</v>
       </c>
       <c r="J26" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K26" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="M26" s="2">
-        <v>10.69</v>
+        <v>10.35</v>
       </c>
       <c r="N26" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O26" s="2">
         <v>0</v>
@@ -2378,13 +2376,13 @@
         <v>110</v>
       </c>
       <c r="Q26" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R26" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S26" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T26" s="2">
         <v>69</v>
@@ -2393,13 +2391,13 @@
         <v>15</v>
       </c>
       <c r="V26" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W26" s="2"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="2">
-        <v>2202692</v>
+        <v>2203257</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -2408,34 +2406,34 @@
         <v>29</v>
       </c>
       <c r="D27" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F27" s="2">
-        <v>45.5</v>
+        <v>53.05</v>
       </c>
       <c r="G27" s="2">
-        <v>20.222222219999999</v>
+        <v>22.66222393</v>
       </c>
       <c r="H27" s="2">
-        <v>0.19780219800000001</v>
-      </c>
-      <c r="I27" s="2">
-        <v>10.39</v>
+        <v>0.20923656900000001</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="J27" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K27" s="2">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M27" s="2">
-        <v>10.35</v>
+        <v>9.59</v>
       </c>
       <c r="N27" s="2">
         <v>125</v>
@@ -2444,160 +2442,160 @@
         <v>0</v>
       </c>
       <c r="P27" s="2">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R27" s="2">
         <v>23</v>
       </c>
       <c r="S27" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T27" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U27" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V27" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W27" s="2"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="2">
-        <v>2203257</v>
+        <v>2203370</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2">
-        <v>153</v>
+        <v>153.30000000000001</v>
       </c>
       <c r="F28" s="2">
-        <v>53.05</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="G28" s="2">
-        <v>22.66222393</v>
+        <v>29.828657549999999</v>
       </c>
       <c r="H28" s="2">
-        <v>0.20923656900000001</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>8</v>
+        <v>0.139800285</v>
+      </c>
+      <c r="I28" s="2">
+        <v>13.29</v>
       </c>
       <c r="J28" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K28" s="2">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L28" s="2">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="M28" s="2">
-        <v>9.59</v>
+        <v>13.29</v>
       </c>
       <c r="N28" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O28" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P28" s="2">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R28" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="S28" s="2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="T28" s="2">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="U28" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V28" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W28" s="2"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="2">
-        <v>2203370</v>
+        <v>2204023</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2">
-        <v>153.30000000000001</v>
+        <v>153</v>
       </c>
       <c r="F29" s="2">
-        <v>70.099999999999994</v>
+        <v>73.5</v>
       </c>
       <c r="G29" s="2">
-        <v>29.828657549999999</v>
+        <v>31.398180190000001</v>
       </c>
       <c r="H29" s="2">
-        <v>0.139800285</v>
-      </c>
-      <c r="I29" s="2">
-        <v>13.29</v>
+        <v>0.30204081599999999</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="J29" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K29" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L29" s="2">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="M29" s="2">
-        <v>13.29</v>
+        <v>10.94</v>
       </c>
       <c r="N29" s="2">
+        <v>125</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
         <v>115</v>
-      </c>
-      <c r="O29" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P29" s="2">
-        <v>120</v>
       </c>
       <c r="Q29" s="2">
         <v>-15</v>
       </c>
       <c r="R29" s="2">
+        <v>18</v>
+      </c>
+      <c r="S29" s="2">
+        <v>26</v>
+      </c>
+      <c r="T29" s="2">
+        <v>66</v>
+      </c>
+      <c r="U29" s="2">
         <v>12</v>
-      </c>
-      <c r="S29" s="2">
-        <v>14</v>
-      </c>
-      <c r="T29" s="2">
-        <v>28</v>
-      </c>
-      <c r="U29" s="2">
-        <v>15</v>
       </c>
       <c r="V29" s="2">
         <v>11</v>
@@ -2606,7 +2604,7 @@
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="2">
-        <v>2204023</v>
+        <v>2204202</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2615,34 +2613,34 @@
         <v>29</v>
       </c>
       <c r="D30" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F30" s="2">
-        <v>73.5</v>
+        <v>52.5</v>
       </c>
       <c r="G30" s="2">
-        <v>31.398180190000001</v>
+        <v>23.333333329999999</v>
       </c>
       <c r="H30" s="2">
-        <v>0.30204081599999999</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>9</v>
+        <v>0.29142857100000003</v>
+      </c>
+      <c r="I30" s="2">
+        <v>11.23</v>
       </c>
       <c r="J30" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K30" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="M30" s="2">
-        <v>10.94</v>
+        <v>11.23</v>
       </c>
       <c r="N30" s="2">
         <v>125</v>
@@ -2651,31 +2649,31 @@
         <v>0</v>
       </c>
       <c r="P30" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R30" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S30" s="2">
         <v>26</v>
       </c>
       <c r="T30" s="2">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="U30" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V30" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W30" s="2"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="2">
-        <v>2204202</v>
+        <v>2204531</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2684,127 +2682,127 @@
         <v>29</v>
       </c>
       <c r="D31" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2">
-        <v>150</v>
+        <v>142.19999999999999</v>
       </c>
       <c r="F31" s="2">
-        <v>52.5</v>
+        <v>39.9</v>
       </c>
       <c r="G31" s="2">
-        <v>23.333333329999999</v>
+        <v>19.732117949999999</v>
       </c>
       <c r="H31" s="2">
-        <v>0.29142857100000003</v>
+        <v>0.27819548900000002</v>
       </c>
       <c r="I31" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="J31" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K31" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L31" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="M31" s="2">
-        <v>11.23</v>
+        <v>11.75</v>
       </c>
       <c r="N31" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O31" s="2">
         <v>0</v>
       </c>
       <c r="P31" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="2">
         <v>-5</v>
       </c>
       <c r="R31" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="S31" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T31" s="2">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="U31" s="2">
         <v>13</v>
       </c>
       <c r="V31" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31" s="2"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="2">
-        <v>2204531</v>
+        <v>2204625</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D32" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2">
-        <v>142.19999999999999</v>
+        <v>177</v>
       </c>
       <c r="F32" s="2">
-        <v>39.9</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2">
-        <v>19.732117949999999</v>
+        <v>33.196080309999999</v>
       </c>
       <c r="H32" s="2">
-        <v>0.27819548900000002</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="J32" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K32" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L32" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M32" s="2">
-        <v>11.75</v>
+        <v>10.69</v>
       </c>
       <c r="N32" s="2">
         <v>120</v>
       </c>
       <c r="O32" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="P32" s="2">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="Q32" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R32" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S32" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T32" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="U32" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V32" s="2">
         <v>9</v>
@@ -2813,67 +2811,67 @@
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="2">
-        <v>2204625</v>
+        <v>2204766</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D33" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E33" s="2">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F33" s="2">
-        <v>104</v>
+        <v>57.8</v>
       </c>
       <c r="G33" s="2">
-        <v>33.196080309999999</v>
+        <v>26.748114210000001</v>
       </c>
       <c r="H33" s="2">
-        <v>0</v>
+        <v>0.150519031</v>
       </c>
       <c r="I33" s="2">
-        <v>10.69</v>
+        <v>10.54</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K33" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M33" s="2">
-        <v>10.69</v>
+        <v>9.49</v>
       </c>
       <c r="N33" s="2">
+        <v>130</v>
+      </c>
+      <c r="O33" s="2">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2">
         <v>120</v>
-      </c>
-      <c r="O33" s="2">
-        <v>-10</v>
-      </c>
-      <c r="P33" s="2">
-        <v>140</v>
       </c>
       <c r="Q33" s="2">
         <v>-10</v>
       </c>
       <c r="R33" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S33" s="2">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="T33" s="2">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U33" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V33" s="2">
         <v>9</v>
@@ -2882,346 +2880,346 @@
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="2">
-        <v>2204766</v>
+        <v>2300143</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2">
-        <v>147</v>
+        <v>156.30000000000001</v>
       </c>
       <c r="F34" s="2">
-        <v>57.8</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G34" s="2">
-        <v>26.748114210000001</v>
+        <v>27.794048960000001</v>
       </c>
       <c r="H34" s="2">
-        <v>0.150519031</v>
+        <v>0.19440353499999999</v>
       </c>
       <c r="I34" s="2">
-        <v>10.54</v>
+        <v>12.89</v>
       </c>
       <c r="J34" s="2">
+        <v>48</v>
+      </c>
+      <c r="K34" s="2">
         <v>12</v>
       </c>
-      <c r="K34" s="2">
-        <v>24</v>
-      </c>
       <c r="L34" s="2">
+        <v>125</v>
+      </c>
+      <c r="M34" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="N34" s="2">
         <v>110</v>
       </c>
-      <c r="M34" s="2">
-        <v>9.49</v>
-      </c>
-      <c r="N34" s="2">
-        <v>130</v>
-      </c>
       <c r="O34" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P34" s="2">
         <v>120</v>
       </c>
       <c r="Q34" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R34" s="2">
         <v>20</v>
       </c>
       <c r="S34" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="T34" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U34" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V34" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W34" s="2"/>
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="2">
-        <v>2300143</v>
+        <v>2300176</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2">
-        <v>156.30000000000001</v>
+        <v>152.5</v>
       </c>
       <c r="F35" s="2">
-        <v>67.900000000000006</v>
+        <v>64.8</v>
       </c>
       <c r="G35" s="2">
-        <v>27.794048960000001</v>
+        <v>27.86347756</v>
       </c>
       <c r="H35" s="2">
-        <v>0.19440353499999999</v>
+        <v>0.17129629599999999</v>
       </c>
       <c r="I35" s="2">
-        <v>12.89</v>
+        <v>11.68</v>
       </c>
       <c r="J35" s="2">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K35" s="2">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="L35" s="2">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="M35" s="2">
-        <v>12.56</v>
+        <v>11.68</v>
       </c>
       <c r="N35" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O35" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P35" s="2">
         <v>120</v>
       </c>
       <c r="Q35" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R35" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" s="2">
         <v>20</v>
       </c>
-      <c r="S35" s="2">
-        <v>32</v>
-      </c>
       <c r="T35" s="2">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="U35" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V35" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W35" s="2"/>
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="2">
-        <v>2300176</v>
+        <v>2300484</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E36" s="2">
-        <v>152.5</v>
+        <v>146</v>
       </c>
       <c r="F36" s="2">
-        <v>64.8</v>
+        <v>58</v>
       </c>
       <c r="G36" s="2">
-        <v>27.86347756</v>
+        <v>27.209607810000001</v>
       </c>
       <c r="H36" s="2">
-        <v>0.17129629599999999</v>
+        <v>0.212068966</v>
       </c>
       <c r="I36" s="2">
-        <v>11.68</v>
+        <v>13.33</v>
       </c>
       <c r="J36" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="L36" s="2">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="M36" s="2">
-        <v>11.68</v>
+        <v>13.33</v>
       </c>
       <c r="N36" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O36" s="2">
         <v>0</v>
       </c>
       <c r="P36" s="2">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R36" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S36" s="2">
         <v>20</v>
       </c>
       <c r="T36" s="2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="U36" s="2">
         <v>13</v>
       </c>
       <c r="V36" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W36" s="2"/>
     </row>
     <row r="37" spans="1:23">
       <c r="A37" s="2">
-        <v>2300484</v>
+        <v>2300760</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D37" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F37" s="2">
-        <v>58</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="G37" s="2">
-        <v>27.209607810000001</v>
+        <v>24.390243900000002</v>
       </c>
       <c r="H37" s="2">
-        <v>0.212068966</v>
+        <v>0.33231707300000002</v>
       </c>
       <c r="I37" s="2">
-        <v>13.33</v>
+        <v>10.94</v>
       </c>
       <c r="J37" s="2">
+        <v>30</v>
+      </c>
+      <c r="K37" s="2">
+        <v>21</v>
+      </c>
+      <c r="L37" s="2">
+        <v>105</v>
+      </c>
+      <c r="M37" s="2">
+        <v>12.29</v>
+      </c>
+      <c r="N37" s="2">
+        <v>115</v>
+      </c>
+      <c r="O37" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P37" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R37" s="2">
+        <v>8</v>
+      </c>
+      <c r="S37" s="2">
         <v>24</v>
       </c>
-      <c r="K37" s="2">
-        <v>17</v>
-      </c>
-      <c r="L37" s="2">
-        <v>121</v>
-      </c>
-      <c r="M37" s="2">
-        <v>13.33</v>
-      </c>
-      <c r="N37" s="2">
-        <v>120</v>
-      </c>
-      <c r="O37" s="2">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2">
-        <v>135</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R37" s="2">
-        <v>22</v>
-      </c>
-      <c r="S37" s="2">
-        <v>20</v>
-      </c>
       <c r="T37" s="2">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="U37" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V37" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W37" s="2"/>
     </row>
     <row r="38" spans="1:23">
       <c r="A38" s="2">
-        <v>2300760</v>
+        <v>2301202</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2">
         <v>74</v>
       </c>
       <c r="E38" s="2">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2">
-        <v>65.599999999999994</v>
+        <v>47.15</v>
       </c>
       <c r="G38" s="2">
-        <v>24.390243900000002</v>
+        <v>22.425683710000001</v>
       </c>
       <c r="H38" s="2">
-        <v>0.33231707300000002</v>
+        <v>9.3319193999999994E-2</v>
       </c>
       <c r="I38" s="2">
-        <v>10.94</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="J38" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K38" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M38" s="2">
-        <v>12.29</v>
+        <v>9.31</v>
       </c>
       <c r="N38" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O38" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P38" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Q38" s="2">
-        <v>-20</v>
+        <v>15</v>
       </c>
       <c r="R38" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S38" s="2">
         <v>24</v>
       </c>
       <c r="T38" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="U38" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V38" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W38" s="2"/>
     </row>
@@ -3233,196 +3231,196 @@
         <v>1</v>
       </c>
       <c r="C39" s="7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39" s="2">
         <v>74</v>
       </c>
       <c r="E39" s="2">
-        <v>145</v>
+        <v>145.5</v>
       </c>
       <c r="F39" s="2">
-        <v>47.15</v>
+        <v>49.1</v>
       </c>
       <c r="G39" s="2">
-        <v>22.425683710000001</v>
+        <v>23.19292403</v>
       </c>
       <c r="H39" s="2">
-        <v>9.3319193999999994E-2</v>
+        <v>0.15071283099999999</v>
       </c>
       <c r="I39" s="2">
-        <v>9.3800000000000008</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="J39" s="2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K39" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="M39" s="2">
-        <v>9.31</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="N39" s="2">
+        <v>130</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
         <v>125</v>
       </c>
-      <c r="O39" s="2">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2">
-        <v>120</v>
-      </c>
       <c r="Q39" s="2">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="R39" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S39" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T39" s="2">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="U39" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V39" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W39" s="2"/>
     </row>
     <row r="40" spans="1:23">
       <c r="A40" s="2">
-        <v>2301202</v>
+        <v>2301430</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" s="7">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2">
-        <v>145.5</v>
+        <v>145.30000000000001</v>
       </c>
       <c r="F40" s="2">
-        <v>49.1</v>
+        <v>68.5</v>
       </c>
       <c r="G40" s="2">
-        <v>23.19292403</v>
+        <v>32.445863959999997</v>
       </c>
       <c r="H40" s="2">
-        <v>0.15071283099999999</v>
-      </c>
-      <c r="I40" s="2">
-        <v>8.2100000000000009</v>
+        <v>0.12700729899999999</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="J40" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K40" s="2">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L40" s="2">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="M40" s="2">
-        <v>8.2100000000000009</v>
+        <v>16.91</v>
       </c>
       <c r="N40" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="O40" s="2">
         <v>0</v>
       </c>
       <c r="P40" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q40" s="2">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="R40" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="S40" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="T40" s="2">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="U40" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V40" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40" s="2"/>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="2">
-        <v>2301430</v>
+        <v>2301506</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" s="7">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D41" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2">
-        <v>145.30000000000001</v>
+        <v>158</v>
       </c>
       <c r="F41" s="2">
-        <v>68.5</v>
+        <v>76.7</v>
       </c>
       <c r="G41" s="2">
-        <v>32.445863959999997</v>
+        <v>30.724242910000001</v>
       </c>
       <c r="H41" s="2">
-        <v>0.12700729899999999</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>10</v>
+        <v>0.177314211</v>
+      </c>
+      <c r="I41" s="2">
+        <v>9.9</v>
       </c>
       <c r="J41" s="2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2">
+        <v>150</v>
+      </c>
+      <c r="M41" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="N41" s="2">
+        <v>125</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>-5</v>
+      </c>
+      <c r="R41" s="2">
         <v>24</v>
       </c>
-      <c r="L41" s="2">
-        <v>109</v>
-      </c>
-      <c r="M41" s="2">
-        <v>16.91</v>
-      </c>
-      <c r="N41" s="2">
-        <v>115</v>
-      </c>
-      <c r="O41" s="2">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2">
-        <v>115</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R41" s="2">
-        <v>17</v>
-      </c>
       <c r="S41" s="2">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="T41" s="2">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="U41" s="2">
         <v>15</v>
@@ -3434,415 +3432,415 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="2">
-        <v>2301506</v>
+        <v>2301620</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" s="7">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E42" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F42" s="2">
-        <v>76.7</v>
+        <v>66.5</v>
       </c>
       <c r="G42" s="2">
-        <v>30.724242910000001</v>
+        <v>29.95360569</v>
       </c>
       <c r="H42" s="2">
-        <v>0.177314211</v>
+        <v>0.19398496200000001</v>
       </c>
       <c r="I42" s="2">
         <v>9.9</v>
       </c>
       <c r="J42" s="2">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K42" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M42" s="2">
         <v>9.9</v>
       </c>
       <c r="N42" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="O42" s="2">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="P42" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q42" s="2">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="R42" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="S42" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T42" s="2">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="U42" s="2">
         <v>15</v>
       </c>
       <c r="V42" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W42" s="2"/>
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="2">
-        <v>2301620</v>
+        <v>2301878</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2">
-        <v>149</v>
+        <v>139.5</v>
       </c>
       <c r="F43" s="2">
-        <v>66.5</v>
+        <v>50</v>
       </c>
       <c r="G43" s="2">
-        <v>29.95360569</v>
+        <v>25.693400650000001</v>
       </c>
       <c r="H43" s="2">
-        <v>0.19398496200000001</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="I43" s="2">
-        <v>9.9</v>
+        <v>12.19</v>
       </c>
       <c r="J43" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K43" s="2">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L43" s="2">
+        <v>76</v>
+      </c>
+      <c r="M43" s="2">
+        <v>12.19</v>
+      </c>
+      <c r="N43" s="2">
+        <v>115</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2">
         <v>120</v>
       </c>
-      <c r="M43" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="N43" s="2">
-        <v>110</v>
-      </c>
-      <c r="O43" s="2">
-        <v>-15</v>
-      </c>
-      <c r="P43" s="2">
-        <v>115</v>
-      </c>
       <c r="Q43" s="2">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="R43" s="2">
+        <v>16</v>
+      </c>
+      <c r="S43" s="2">
         <v>18</v>
       </c>
-      <c r="S43" s="2">
-        <v>28</v>
-      </c>
       <c r="T43" s="2">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="U43" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V43" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W43" s="2"/>
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="2">
-        <v>2301878</v>
+        <v>2301974</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44" s="7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2">
-        <v>139.5</v>
+        <v>151.5</v>
       </c>
       <c r="F44" s="2">
-        <v>50</v>
+        <v>66.5</v>
       </c>
       <c r="G44" s="2">
-        <v>25.693400650000001</v>
+        <v>28.97319435</v>
       </c>
       <c r="H44" s="2">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="I44" s="2">
-        <v>12.19</v>
+        <v>0.34887217999999998</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="J44" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K44" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="M44" s="2">
-        <v>12.19</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="N44" s="2">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="O44" s="2">
         <v>0</v>
       </c>
       <c r="P44" s="2">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q44" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R44" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S44" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="T44" s="2">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="U44" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V44" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W44" s="2"/>
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="2">
-        <v>2301974</v>
+        <v>2303599</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" s="7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2">
-        <v>151.5</v>
+        <v>148</v>
       </c>
       <c r="F45" s="2">
-        <v>66.5</v>
+        <v>68.3</v>
       </c>
       <c r="G45" s="2">
-        <v>28.97319435</v>
+        <v>31.181519359999999</v>
       </c>
       <c r="H45" s="2">
-        <v>0.34887217999999998</v>
-      </c>
-      <c r="I45" s="2" t="s">
+        <v>9.2240116999999996E-2</v>
+      </c>
+      <c r="I45" s="2">
+        <v>12.44</v>
+      </c>
+      <c r="J45" s="2">
+        <v>41</v>
+      </c>
+      <c r="K45" s="2">
+        <v>31</v>
+      </c>
+      <c r="L45" s="2">
+        <v>83</v>
+      </c>
+      <c r="M45" s="2">
+        <v>12.33</v>
+      </c>
+      <c r="N45" s="2">
+        <v>120</v>
+      </c>
+      <c r="O45" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P45" s="2">
+        <v>-15</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>130</v>
+      </c>
+      <c r="R45" s="2">
+        <v>16</v>
+      </c>
+      <c r="S45" s="2">
+        <v>22</v>
+      </c>
+      <c r="T45" s="2">
+        <v>34</v>
+      </c>
+      <c r="U45" s="2">
+        <v>15</v>
+      </c>
+      <c r="V45" s="2">
         <v>11</v>
-      </c>
-      <c r="J45" s="2">
-        <v>25</v>
-      </c>
-      <c r="K45" s="2">
-        <v>1</v>
-      </c>
-      <c r="L45" s="2">
-        <v>118</v>
-      </c>
-      <c r="M45" s="2">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="N45" s="2">
-        <v>130</v>
-      </c>
-      <c r="O45" s="2">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R45" s="2">
-        <v>23</v>
-      </c>
-      <c r="S45" s="2">
-        <v>32</v>
-      </c>
-      <c r="T45" s="2">
-        <v>53</v>
-      </c>
-      <c r="U45" s="2">
-        <v>12</v>
-      </c>
-      <c r="V45" s="2">
-        <v>10</v>
       </c>
       <c r="W45" s="2"/>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="2">
-        <v>2303599</v>
+        <v>2304093</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2">
-        <v>148</v>
+        <v>142.5</v>
       </c>
       <c r="F46" s="2">
-        <v>68.3</v>
+        <v>42</v>
       </c>
       <c r="G46" s="2">
-        <v>31.181519359999999</v>
+        <v>20.68328717</v>
       </c>
       <c r="H46" s="2">
-        <v>9.2240116999999996E-2</v>
-      </c>
-      <c r="I46" s="2">
-        <v>12.44</v>
+        <v>0.18333333299999999</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="J46" s="2">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K46" s="2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="M46" s="2">
-        <v>12.33</v>
+        <v>11.69</v>
       </c>
       <c r="N46" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O46" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P46" s="2">
-        <v>-15</v>
+        <v>130</v>
       </c>
       <c r="Q46" s="2">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="R46" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S46" s="2">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="T46" s="2">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="U46" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V46" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W46" s="2"/>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="2">
-        <v>2304093</v>
+        <v>2304321</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" s="7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E47" s="2">
-        <v>142.5</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2">
-        <v>42</v>
+        <v>62.2</v>
       </c>
       <c r="G47" s="2">
-        <v>20.68328717</v>
+        <v>29.179958719999998</v>
       </c>
       <c r="H47" s="2">
-        <v>0.18333333299999999</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>12</v>
+        <v>0.236334405</v>
+      </c>
+      <c r="I47" s="2">
+        <v>14.5</v>
       </c>
       <c r="J47" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K47" s="2">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L47" s="2">
-        <v>157</v>
+        <v>98</v>
       </c>
       <c r="M47" s="2">
-        <v>11.69</v>
+        <v>14.5</v>
       </c>
       <c r="N47" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="O47" s="2">
         <v>0</v>
       </c>
       <c r="P47" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q47" s="2">
+        <v>-15</v>
+      </c>
+      <c r="R47" s="2">
+        <v>16</v>
+      </c>
+      <c r="S47" s="2">
         <v>20</v>
       </c>
-      <c r="R47" s="2">
-        <v>23</v>
-      </c>
-      <c r="S47" s="2">
-        <v>38</v>
-      </c>
       <c r="T47" s="2">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="U47" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V47" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W47" s="2"/>
     </row>
@@ -3863,28 +3861,28 @@
         <v>146</v>
       </c>
       <c r="F48" s="2">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="G48" s="2">
-        <v>29.179958719999998</v>
+        <v>29.08613248</v>
       </c>
       <c r="H48" s="2">
-        <v>0.236334405</v>
+        <v>0.23548387100000001</v>
       </c>
       <c r="I48" s="2">
-        <v>14.5</v>
+        <v>12.28</v>
       </c>
       <c r="J48" s="2">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K48" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L48" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M48" s="2">
-        <v>14.5</v>
+        <v>11.94</v>
       </c>
       <c r="N48" s="2">
         <v>120</v>
@@ -3893,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Q48" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R48" s="2">
         <v>16</v>
@@ -3905,19 +3903,19 @@
         <v>20</v>
       </c>
       <c r="T48" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U48" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V48" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W48" s="2"/>
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>2304321</v>
+        <v>2304669</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -3926,35 +3924,33 @@
         <v>29</v>
       </c>
       <c r="D49" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E49" s="2">
-        <v>146</v>
+        <v>164.5</v>
       </c>
       <c r="F49" s="2">
-        <v>62</v>
+        <v>77.8</v>
       </c>
       <c r="G49" s="2">
-        <v>29.08613248</v>
+        <v>28.750658250000001</v>
       </c>
       <c r="H49" s="2">
-        <v>0.23548387100000001</v>
+        <v>0.23264781500000001</v>
       </c>
       <c r="I49" s="2">
-        <v>12.28</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="K49" s="2">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L49" s="2">
-        <v>102</v>
-      </c>
-      <c r="M49" s="2">
-        <v>11.94</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="M49" s="1"/>
       <c r="N49" s="2">
         <v>120</v>
       </c>
@@ -3962,22 +3958,22 @@
         <v>0</v>
       </c>
       <c r="P49" s="2">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="Q49" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R49" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S49" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T49" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U49" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V49" s="2">
         <v>11</v>
@@ -3986,7 +3982,7 @@
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>2304669</v>
+        <v>2304770</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -3995,33 +3991,35 @@
         <v>29</v>
       </c>
       <c r="D50" s="2">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E50" s="2">
-        <v>164.5</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F50" s="2">
-        <v>77.8</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G50" s="2">
-        <v>28.750658250000001</v>
+        <v>27.80075321</v>
       </c>
       <c r="H50" s="2">
-        <v>0.23264781500000001</v>
+        <v>0.21739130400000001</v>
       </c>
       <c r="I50" s="2">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="J50" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" s="2">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L50" s="2">
-        <v>107</v>
-      </c>
-      <c r="M50" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="M50" s="2">
+        <v>6.93</v>
+      </c>
       <c r="N50" s="2">
         <v>120</v>
       </c>
@@ -4029,22 +4027,22 @@
         <v>0</v>
       </c>
       <c r="P50" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q50" s="2">
         <v>-5</v>
       </c>
       <c r="R50" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S50" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T50" s="2">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="U50" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V50" s="2">
         <v>11</v>
@@ -4053,46 +4051,46 @@
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>2304770</v>
+        <v>2400788</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D51" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E51" s="2">
-        <v>152.19999999999999</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="F51" s="2">
-        <v>64.400000000000006</v>
+        <v>63.8</v>
       </c>
       <c r="G51" s="2">
-        <v>27.80075321</v>
+        <v>24.705231349999998</v>
       </c>
       <c r="H51" s="2">
-        <v>0.21739130400000001</v>
+        <v>0.28056426299999998</v>
       </c>
       <c r="I51" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="J51" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K51" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L51" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="M51" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="N51" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O51" s="2">
         <v>0</v>
@@ -4101,160 +4099,160 @@
         <v>120</v>
       </c>
       <c r="Q51" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R51" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S51" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="T51" s="2">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="U51" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V51" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W51" s="2"/>
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>2400788</v>
+        <v>2401195</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E52" s="2">
-        <v>160.69999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="F52" s="2">
-        <v>63.8</v>
+        <v>68.3</v>
       </c>
       <c r="G52" s="2">
-        <v>24.705231349999998</v>
+        <v>29.757431189999998</v>
       </c>
       <c r="H52" s="2">
-        <v>0.28056426299999998</v>
+        <v>0.33967789199999998</v>
       </c>
       <c r="I52" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="J52" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K52" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L52" s="2">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="M52" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="N52" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O52" s="2">
         <v>0</v>
       </c>
       <c r="P52" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q52" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R52" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="S52" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T52" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="U52" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V52" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W52" s="2"/>
     </row>
     <row r="53" spans="1:23">
       <c r="A53" s="2">
-        <v>2401195</v>
+        <v>2401295</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E53" s="2">
-        <v>151.5</v>
+        <v>142</v>
       </c>
       <c r="F53" s="2">
-        <v>68.3</v>
+        <v>62</v>
       </c>
       <c r="G53" s="2">
-        <v>29.757431189999998</v>
+        <v>30.747867490000001</v>
       </c>
       <c r="H53" s="2">
-        <v>0.33967789199999998</v>
+        <v>0.44193548399999999</v>
       </c>
       <c r="I53" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="J53" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="L53" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M53" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="N53" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O53" s="2">
         <v>0</v>
       </c>
       <c r="P53" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q53" s="2">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="R53" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S53" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T53" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U53" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V53" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W53" s="2"/>
     </row>
@@ -4266,40 +4264,40 @@
         <v>1</v>
       </c>
       <c r="C54" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F54" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G54" s="2">
-        <v>30.747867490000001</v>
+        <v>29.830309549999999</v>
       </c>
       <c r="H54" s="2">
-        <v>0.44193548399999999</v>
+        <v>0.35081967200000003</v>
       </c>
       <c r="I54" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="J54" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K54" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L54" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="M54" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="N54" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O54" s="2">
         <v>0</v>
@@ -4308,16 +4306,16 @@
         <v>115</v>
       </c>
       <c r="Q54" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R54" s="2">
         <v>23</v>
       </c>
       <c r="S54" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T54" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="U54" s="2">
         <v>15</v>
@@ -4329,76 +4327,76 @@
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>2401295</v>
+        <v>2401534</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" s="7">
+        <v>29</v>
+      </c>
+      <c r="D55" s="2">
+        <v>81</v>
+      </c>
+      <c r="E55" s="2">
+        <v>147.5</v>
+      </c>
+      <c r="F55" s="2">
+        <v>59.2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>27.21057167</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0.18243243200000001</v>
+      </c>
+      <c r="I55" s="2">
+        <v>10.86</v>
+      </c>
+      <c r="J55" s="2">
+        <v>25</v>
+      </c>
+      <c r="K55" s="2">
+        <v>10</v>
+      </c>
+      <c r="L55" s="2">
+        <v>125</v>
+      </c>
+      <c r="M55" s="2">
+        <v>10.91</v>
+      </c>
+      <c r="N55" s="2">
+        <v>120</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R55" s="2">
+        <v>18</v>
+      </c>
+      <c r="S55" s="2">
         <v>30</v>
       </c>
-      <c r="D55" s="2">
-        <v>63</v>
-      </c>
-      <c r="E55" s="2">
-        <v>143</v>
-      </c>
-      <c r="F55" s="2">
-        <v>61</v>
-      </c>
-      <c r="G55" s="2">
-        <v>29.830309549999999</v>
-      </c>
-      <c r="H55" s="2">
-        <v>0.35081967200000003</v>
-      </c>
-      <c r="I55" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="J55" s="2">
-        <v>50</v>
-      </c>
-      <c r="K55" s="2">
-        <v>47</v>
-      </c>
-      <c r="L55" s="2">
-        <v>93</v>
-      </c>
-      <c r="M55" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="N55" s="2">
-        <v>110</v>
-      </c>
-      <c r="O55" s="2">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2">
-        <v>115</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R55" s="2">
-        <v>23</v>
-      </c>
-      <c r="S55" s="2">
-        <v>18</v>
-      </c>
       <c r="T55" s="2">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="U55" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V55" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W55" s="2"/>
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>2401534</v>
+        <v>2401730</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -4407,67 +4405,67 @@
         <v>29</v>
       </c>
       <c r="D56" s="2">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E56" s="2">
-        <v>147.5</v>
+        <v>160</v>
       </c>
       <c r="F56" s="2">
-        <v>59.2</v>
+        <v>56</v>
       </c>
       <c r="G56" s="2">
-        <v>27.21057167</v>
+        <v>21.875</v>
       </c>
       <c r="H56" s="2">
-        <v>0.18243243200000001</v>
+        <v>0.14464285700000001</v>
       </c>
       <c r="I56" s="2">
-        <v>10.86</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="J56" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K56" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L56" s="2">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="M56" s="2">
-        <v>10.91</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N56" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O56" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P56" s="2">
         <v>120</v>
       </c>
       <c r="Q56" s="2">
-        <v>-10</v>
+        <v>-35</v>
       </c>
       <c r="R56" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S56" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="T56" s="2">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="U56" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V56" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W56" s="2"/>
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>2401730</v>
+        <v>2401922</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -4476,103 +4474,103 @@
         <v>29</v>
       </c>
       <c r="D57" s="2">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2">
-        <v>160</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="F57" s="2">
-        <v>56</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="G57" s="2">
-        <v>21.875</v>
+        <v>37.568624579999998</v>
       </c>
       <c r="H57" s="2">
-        <v>0.14464285700000001</v>
+        <v>0.16598079600000001</v>
       </c>
       <c r="I57" s="2">
-        <v>39.229999999999997</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="J57" s="2">
         <v>29</v>
       </c>
       <c r="K57" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L57" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M57" s="2">
-        <v>32.799999999999997</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="N57" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O57" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P57" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q57" s="2">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="R57" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S57" s="2">
+        <v>24</v>
+      </c>
+      <c r="T57" s="2">
+        <v>29</v>
+      </c>
+      <c r="U57" s="2">
         <v>12</v>
       </c>
-      <c r="T57" s="2">
-        <v>38</v>
-      </c>
-      <c r="U57" s="2">
-        <v>11</v>
-      </c>
       <c r="V57" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W57" s="2"/>
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>2401922</v>
+        <v>2402032</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D58" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E58" s="2">
-        <v>139.30000000000001</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="F58" s="2">
-        <v>72.900000000000006</v>
+        <v>57.3</v>
       </c>
       <c r="G58" s="2">
-        <v>37.568624579999998</v>
+        <v>25.568839749999999</v>
       </c>
       <c r="H58" s="2">
-        <v>0.16598079600000001</v>
+        <v>0.25828970299999998</v>
       </c>
       <c r="I58" s="2">
-        <v>17.829999999999998</v>
+        <v>9.26</v>
       </c>
       <c r="J58" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K58" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L58" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="M58" s="2">
-        <v>18.649999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="N58" s="2">
         <v>110</v>
@@ -4581,22 +4579,22 @@
         <v>0</v>
       </c>
       <c r="P58" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q58" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="R58" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S58" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T58" s="2">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="U58" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V58" s="2">
         <v>9</v>
@@ -4605,7 +4603,7 @@
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>2402032</v>
+        <v>2402281</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -4614,172 +4612,172 @@
         <v>31</v>
       </c>
       <c r="D59" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2">
-        <v>149.69999999999999</v>
+        <v>150</v>
       </c>
       <c r="F59" s="2">
-        <v>57.3</v>
+        <v>62</v>
       </c>
       <c r="G59" s="2">
-        <v>25.568839749999999</v>
+        <v>27.555555559999998</v>
       </c>
       <c r="H59" s="2">
-        <v>0.25828970299999998</v>
+        <v>0.20483871000000001</v>
       </c>
       <c r="I59" s="2">
-        <v>9.26</v>
+        <v>13.88</v>
       </c>
       <c r="J59" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K59" s="2">
+        <v>20</v>
+      </c>
+      <c r="L59" s="2">
+        <v>101</v>
+      </c>
+      <c r="M59" s="2">
+        <v>13.88</v>
+      </c>
+      <c r="N59" s="2">
+        <v>120</v>
+      </c>
+      <c r="O59" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P59" s="2">
+        <v>130</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R59" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" s="2">
         <v>26</v>
       </c>
-      <c r="L59" s="2">
-        <v>135</v>
-      </c>
-      <c r="M59" s="2">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="N59" s="2">
-        <v>110</v>
-      </c>
-      <c r="O59" s="2">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2">
-        <v>100</v>
-      </c>
-      <c r="Q59" s="2">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2">
-        <v>19</v>
-      </c>
-      <c r="S59" s="2">
-        <v>28</v>
-      </c>
       <c r="T59" s="2">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="U59" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V59" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W59" s="2"/>
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>2402281</v>
+        <v>2403315</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E60" s="2">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F60" s="2">
-        <v>62</v>
+        <v>92.5</v>
       </c>
       <c r="G60" s="2">
-        <v>27.555555559999998</v>
+        <v>31.633665059999998</v>
       </c>
       <c r="H60" s="2">
-        <v>0.20483871000000001</v>
+        <v>0.23243243199999999</v>
       </c>
       <c r="I60" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="J60" s="2">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K60" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L60" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M60" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="N60" s="2">
         <v>120</v>
       </c>
       <c r="O60" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P60" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q60" s="2">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="R60" s="2">
         <v>20</v>
       </c>
       <c r="S60" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T60" s="2">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="U60" s="2">
         <v>14</v>
       </c>
       <c r="V60" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W60" s="2"/>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>2402895</v>
+        <v>2403413</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D61" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2">
-        <v>170.5</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="F61" s="2">
-        <v>76.900000000000006</v>
+        <v>65.2</v>
       </c>
       <c r="G61" s="2">
-        <v>26.453160879999999</v>
+        <v>28.519638310000001</v>
       </c>
       <c r="H61" s="2">
-        <v>0.13133940199999999</v>
+        <v>0.20552147200000001</v>
       </c>
       <c r="I61" s="2">
-        <v>14.13</v>
+        <v>12.39</v>
       </c>
       <c r="J61" s="2">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="K61" s="2">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L61" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="M61" s="2">
-        <v>14.49</v>
+        <v>12.39</v>
       </c>
       <c r="N61" s="2">
         <v>120</v>
@@ -4791,19 +4789,19 @@
         <v>120</v>
       </c>
       <c r="Q61" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R61" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S61" s="2">
         <v>22</v>
       </c>
       <c r="T61" s="2">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U61" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V61" s="2">
         <v>8</v>
@@ -4812,46 +4810,46 @@
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>2403315</v>
+        <v>2403725</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
       <c r="C62" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D62" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E62" s="2">
-        <v>171</v>
+        <v>165.5</v>
       </c>
       <c r="F62" s="2">
-        <v>92.5</v>
+        <v>79</v>
       </c>
       <c r="G62" s="2">
-        <v>31.633665059999998</v>
+        <v>28.842380039999998</v>
       </c>
       <c r="H62" s="2">
-        <v>0.23243243199999999</v>
+        <v>0.20506329100000001</v>
       </c>
       <c r="I62" s="2">
-        <v>12.89</v>
+        <v>9.64</v>
       </c>
       <c r="J62" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K62" s="2">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L62" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="M62" s="2">
-        <v>12.89</v>
+        <v>9.64</v>
       </c>
       <c r="N62" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O62" s="2">
         <v>0</v>
@@ -4860,19 +4858,19 @@
         <v>120</v>
       </c>
       <c r="Q62" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R62" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S62" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T62" s="2">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="U62" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V62" s="2">
         <v>9</v>
@@ -4881,43 +4879,43 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>2403413</v>
+        <v>2403883</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" s="7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D63" s="2">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="E63" s="2">
-        <v>151.19999999999999</v>
+        <v>158.1</v>
       </c>
       <c r="F63" s="2">
-        <v>65.2</v>
+        <v>66</v>
       </c>
       <c r="G63" s="2">
-        <v>28.519638310000001</v>
+        <v>26.40463665</v>
       </c>
       <c r="H63" s="2">
-        <v>0.20552147200000001</v>
+        <v>0.192424242</v>
       </c>
       <c r="I63" s="2">
-        <v>12.39</v>
+        <v>9.93</v>
       </c>
       <c r="J63" s="2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K63" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L63" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="M63" s="2">
-        <v>12.39</v>
+        <v>9.93</v>
       </c>
       <c r="N63" s="2">
         <v>120</v>
@@ -4926,67 +4924,67 @@
         <v>0</v>
       </c>
       <c r="P63" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q63" s="2">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="R63" s="2">
         <v>21</v>
       </c>
       <c r="S63" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T63" s="2">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="U63" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V63" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W63" s="2"/>
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>2403725</v>
+        <v>8811223</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="7">
         <v>30</v>
       </c>
       <c r="D64" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2">
-        <v>165.5</v>
+        <v>154</v>
       </c>
       <c r="F64" s="2">
-        <v>79</v>
+        <v>49.4</v>
       </c>
       <c r="G64" s="2">
-        <v>28.842380039999998</v>
+        <v>20.829819530000002</v>
       </c>
       <c r="H64" s="2">
-        <v>0.20506329100000001</v>
+        <v>0.17813765200000001</v>
       </c>
       <c r="I64" s="2">
-        <v>9.64</v>
+        <v>9.11</v>
       </c>
       <c r="J64" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K64" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L64" s="2">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="M64" s="2">
-        <v>9.64</v>
+        <v>10.89</v>
       </c>
       <c r="N64" s="2">
         <v>125</v>
@@ -4998,28 +4996,28 @@
         <v>120</v>
       </c>
       <c r="Q64" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R64" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S64" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="T64" s="2">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="U64" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V64" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W64" s="2"/>
     </row>
     <row r="65" spans="1:23">
       <c r="A65" s="2">
-        <v>2403883</v>
+        <v>8852227</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -5028,34 +5026,34 @@
         <v>29</v>
       </c>
       <c r="D65" s="2">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E65" s="2">
-        <v>158.1</v>
+        <v>151</v>
       </c>
       <c r="F65" s="2">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="G65" s="2">
-        <v>26.40463665</v>
+        <v>28.726810230000002</v>
       </c>
       <c r="H65" s="2">
-        <v>0.192424242</v>
+        <v>0.17251908399999999</v>
       </c>
       <c r="I65" s="2">
-        <v>9.93</v>
+        <v>10.27</v>
       </c>
       <c r="J65" s="2">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K65" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L65" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M65" s="2">
-        <v>9.93</v>
+        <v>11.38</v>
       </c>
       <c r="N65" s="2">
         <v>120</v>
@@ -5064,31 +5062,31 @@
         <v>0</v>
       </c>
       <c r="P65" s="2">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="Q65" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R65" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S65" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="T65" s="2">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="U65" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V65" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W65" s="2"/>
     </row>
     <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>8811223</v>
+        <v>8852227</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -5097,37 +5095,37 @@
         <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E66" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F66" s="2">
-        <v>49.4</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G66" s="2">
-        <v>20.829819530000002</v>
+        <v>28.244375250000001</v>
       </c>
       <c r="H66" s="2">
-        <v>0.17813765200000001</v>
+        <v>0.189440994</v>
       </c>
       <c r="I66" s="2">
-        <v>9.11</v>
+        <v>10.63</v>
       </c>
       <c r="J66" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K66" s="2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="L66" s="2">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="M66" s="2">
-        <v>10.89</v>
+        <v>10.63</v>
       </c>
       <c r="N66" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O66" s="2">
         <v>0</v>
@@ -5136,304 +5134,304 @@
         <v>120</v>
       </c>
       <c r="Q66" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R66" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="S66" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T66" s="2">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="U66" s="2">
         <v>15</v>
       </c>
       <c r="V66" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W66" s="2"/>
     </row>
     <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>8852227</v>
+        <v>9005400</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D67" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E67" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F67" s="2">
-        <v>65.5</v>
+        <v>77.3</v>
       </c>
       <c r="G67" s="2">
-        <v>28.726810230000002</v>
+        <v>30.1953125</v>
       </c>
       <c r="H67" s="2">
-        <v>0.17251908399999999</v>
+        <v>0.168175938</v>
       </c>
       <c r="I67" s="2">
-        <v>10.27</v>
+        <v>17.73</v>
       </c>
       <c r="J67" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K67" s="2">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="L67" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="M67" s="2">
-        <v>11.38</v>
+        <v>17.73</v>
       </c>
       <c r="N67" s="2">
         <v>120</v>
       </c>
       <c r="O67" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P67" s="2">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="Q67" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R67" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S67" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="T67" s="2">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="U67" s="2">
+        <v>12</v>
+      </c>
+      <c r="V67" s="2">
         <v>10</v>
-      </c>
-      <c r="V67" s="2">
-        <v>13</v>
       </c>
       <c r="W67" s="2"/>
     </row>
     <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>8852227</v>
+        <v>9209245</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D68" s="2">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E68" s="2">
-        <v>151</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="F68" s="2">
-        <v>64.400000000000006</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="G68" s="2">
-        <v>28.244375250000001</v>
+        <v>28.97396552</v>
       </c>
       <c r="H68" s="2">
-        <v>0.189440994</v>
+        <v>0.17597765400000001</v>
       </c>
       <c r="I68" s="2">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
       <c r="J68" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K68" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L68" s="2">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="M68" s="2">
-        <v>10.63</v>
+        <v>10.67</v>
       </c>
       <c r="N68" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O68" s="2">
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Q68" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R68" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S68" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T68" s="2">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="U68" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V68" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W68" s="2"/>
     </row>
     <row r="69" spans="1:23">
       <c r="A69" s="2">
-        <v>9005400</v>
+        <v>9301565</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69" s="7">
+        <v>29</v>
+      </c>
+      <c r="D69" s="2">
+        <v>58</v>
+      </c>
+      <c r="E69" s="2">
+        <v>152.5</v>
+      </c>
+      <c r="F69" s="2">
+        <v>78.3</v>
+      </c>
+      <c r="G69" s="2">
+        <v>33.668368719999997</v>
+      </c>
+      <c r="H69" s="2">
+        <v>0.20945083</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="2">
+      <c r="J69" s="2">
+        <v>44</v>
+      </c>
+      <c r="K69" s="2">
+        <v>22</v>
+      </c>
+      <c r="L69" s="2">
+        <v>127</v>
+      </c>
+      <c r="M69" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="N69" s="2">
+        <v>130</v>
+      </c>
+      <c r="O69" s="2">
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R69" s="2">
+        <v>19</v>
+      </c>
+      <c r="S69" s="2">
+        <v>24</v>
+      </c>
+      <c r="T69" s="2">
         <v>71</v>
-      </c>
-      <c r="E69" s="2">
-        <v>160</v>
-      </c>
-      <c r="F69" s="2">
-        <v>77.3</v>
-      </c>
-      <c r="G69" s="2">
-        <v>30.1953125</v>
-      </c>
-      <c r="H69" s="2">
-        <v>0.168175938</v>
-      </c>
-      <c r="I69" s="2">
-        <v>17.73</v>
-      </c>
-      <c r="J69" s="2">
-        <v>41</v>
-      </c>
-      <c r="K69" s="2">
-        <v>33</v>
-      </c>
-      <c r="L69" s="2">
-        <v>82</v>
-      </c>
-      <c r="M69" s="2">
-        <v>17.73</v>
-      </c>
-      <c r="N69" s="2">
-        <v>120</v>
-      </c>
-      <c r="O69" s="2">
-        <v>-5</v>
-      </c>
-      <c r="P69" s="2">
-        <v>110</v>
-      </c>
-      <c r="Q69" s="2">
-        <v>0</v>
-      </c>
-      <c r="R69" s="2">
-        <v>12</v>
-      </c>
-      <c r="S69" s="2">
-        <v>14</v>
-      </c>
-      <c r="T69" s="2">
-        <v>46</v>
       </c>
       <c r="U69" s="2">
         <v>12</v>
       </c>
       <c r="V69" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W69" s="2"/>
     </row>
     <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>9209245</v>
+        <v>9301565</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" s="7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E70" s="2">
-        <v>157.19999999999999</v>
+        <v>153</v>
       </c>
       <c r="F70" s="2">
-        <v>71.599999999999994</v>
+        <v>80.8</v>
       </c>
       <c r="G70" s="2">
-        <v>28.97396552</v>
+        <v>34.516638899999997</v>
       </c>
       <c r="H70" s="2">
-        <v>0.17597765400000001</v>
-      </c>
-      <c r="I70" s="2">
-        <v>10.62</v>
+        <v>0.21534653500000001</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="J70" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K70" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L70" s="2">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="M70" s="2">
-        <v>10.67</v>
+        <v>8.59</v>
       </c>
       <c r="N70" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O70" s="2">
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="Q70" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R70" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S70" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="T70" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U70" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V70" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W70" s="2"/>
     </row>
     <row r="71" spans="1:23">
       <c r="A71" s="2">
-        <v>9301565</v>
+        <v>9508610</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -5442,37 +5440,37 @@
         <v>29</v>
       </c>
       <c r="D71" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E71" s="2">
-        <v>152.5</v>
+        <v>151</v>
       </c>
       <c r="F71" s="2">
-        <v>78.3</v>
+        <v>55.4</v>
       </c>
       <c r="G71" s="2">
-        <v>33.668368719999997</v>
+        <v>24.29717995</v>
       </c>
       <c r="H71" s="2">
-        <v>0.20945083</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>13</v>
+        <v>0.20216606500000001</v>
+      </c>
+      <c r="I71" s="2">
+        <v>7.96</v>
       </c>
       <c r="J71" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K71" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L71" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M71" s="2">
-        <v>9.0500000000000007</v>
+        <v>8.09</v>
       </c>
       <c r="N71" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="O71" s="2">
         <v>0</v>
@@ -5481,203 +5479,71 @@
         <v>120</v>
       </c>
       <c r="Q71" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R71" s="2">
         <v>19</v>
       </c>
       <c r="S71" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T71" s="2">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="U71" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V71" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W71" s="2"/>
     </row>
     <row r="72" spans="1:23">
-      <c r="A72" s="2">
-        <v>9301565</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" s="7">
-        <v>29</v>
-      </c>
-      <c r="D72" s="2">
-        <v>58</v>
-      </c>
-      <c r="E72" s="2">
-        <v>153</v>
-      </c>
-      <c r="F72" s="2">
-        <v>80.8</v>
-      </c>
-      <c r="G72" s="2">
-        <v>34.516638899999997</v>
-      </c>
-      <c r="H72" s="2">
-        <v>0.21534653500000001</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J72" s="2">
-        <v>29</v>
-      </c>
-      <c r="K72" s="2">
-        <v>15</v>
-      </c>
-      <c r="L72" s="2">
-        <v>127</v>
-      </c>
-      <c r="M72" s="2">
-        <v>8.59</v>
-      </c>
-      <c r="N72" s="2">
-        <v>115</v>
-      </c>
-      <c r="O72" s="2">
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <v>105</v>
-      </c>
-      <c r="Q72" s="2">
-        <v>-10</v>
-      </c>
-      <c r="R72" s="2">
-        <v>20</v>
-      </c>
-      <c r="S72" s="2">
-        <v>30</v>
-      </c>
-      <c r="T72" s="2">
-        <v>64</v>
-      </c>
-      <c r="U72" s="2">
-        <v>13</v>
-      </c>
-      <c r="V72" s="2">
-        <v>13</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="2"/>
       <c r="W72" s="2"/>
     </row>
     <row r="73" spans="1:23">
-      <c r="A73" s="2">
-        <v>9508610</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73" s="7">
-        <v>29</v>
-      </c>
-      <c r="D73" s="2">
-        <v>72</v>
-      </c>
-      <c r="E73" s="2">
-        <v>151</v>
-      </c>
-      <c r="F73" s="2">
-        <v>55.4</v>
-      </c>
-      <c r="G73" s="2">
-        <v>24.29717995</v>
-      </c>
-      <c r="H73" s="2">
-        <v>0.20216606500000001</v>
-      </c>
-      <c r="I73" s="2">
-        <v>7.96</v>
-      </c>
-      <c r="J73" s="2">
-        <v>34</v>
-      </c>
-      <c r="K73" s="2">
-        <v>17</v>
-      </c>
-      <c r="L73" s="2">
-        <v>115</v>
-      </c>
-      <c r="M73" s="2">
-        <v>8.09</v>
-      </c>
-      <c r="N73" s="2">
-        <v>125</v>
-      </c>
-      <c r="O73" s="2">
-        <v>0</v>
-      </c>
-      <c r="P73" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q73" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R73" s="2">
-        <v>19</v>
-      </c>
-      <c r="S73" s="2">
-        <v>28</v>
-      </c>
-      <c r="T73" s="2">
-        <v>59</v>
-      </c>
-      <c r="U73" s="2">
-        <v>13</v>
-      </c>
-      <c r="V73" s="2">
-        <v>9</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="T73" s="2"/>
+      <c r="V73" s="2"/>
       <c r="W73" s="2"/>
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
       <c r="T74" s="2"/>
-      <c r="U74" s="1"/>
       <c r="V74" s="2"/>
       <c r="W74" s="2"/>
     </row>
     <row r="75" spans="1:23">
       <c r="A75" s="1"/>
-      <c r="T75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
+      <c r="T75" s="4"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
     </row>
     <row r="76" spans="1:23">
       <c r="A76" s="1"/>
-      <c r="T76" s="2"/>
-      <c r="V76" s="2"/>
-      <c r="W76" s="2"/>
     </row>
     <row r="77" spans="1:23">
       <c r="A77" s="1"/>
-      <c r="T77" s="4"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
     </row>
     <row r="78" spans="1:23">
       <c r="A78" s="1"/>
@@ -7007,12 +6873,6 @@
     </row>
     <row r="520" spans="1:1">
       <c r="A520" s="1"/>
-    </row>
-    <row r="521" spans="1:1">
-      <c r="A521" s="1"/>
-    </row>
-    <row r="522" spans="1:1">
-      <c r="A522" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC060C7-2C2C-944E-BD3F-9A406BB0084C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7421C2-6C20-3F48-A2C7-27DFBC19EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7421C2-6C20-3F48-A2C7-27DFBC19EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3431F5-77E1-2D4D-9459-BD0A22DFFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
@@ -630,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
-  <dimension ref="A1:X520"/>
+  <dimension ref="A1:X519"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>2304669</v>
+        <v>2304770</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -4068,33 +4068,35 @@
         <v>29</v>
       </c>
       <c r="D49" s="2">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E49" s="2">
-        <v>164.5</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F49" s="2">
-        <v>77.8</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G49" s="2">
-        <v>28.750658250000001</v>
+        <v>27.80075321</v>
       </c>
       <c r="H49" s="2">
-        <v>0.23264781500000001</v>
+        <v>0.21739130400000001</v>
       </c>
       <c r="I49" s="2">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="J49" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" s="2">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L49" s="2">
-        <v>107</v>
-      </c>
-      <c r="M49" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="M49" s="2">
+        <v>6.93</v>
+      </c>
       <c r="N49" s="2">
         <v>120</v>
       </c>
@@ -4102,72 +4104,72 @@
         <v>0</v>
       </c>
       <c r="P49" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="Q49" s="2">
         <v>-5</v>
       </c>
       <c r="R49" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S49" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T49" s="2">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="U49" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V49" s="2">
         <v>11</v>
       </c>
       <c r="W49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>2304770</v>
+        <v>2400788</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D50" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E50" s="2">
-        <v>152.19999999999999</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="F50" s="2">
-        <v>64.400000000000006</v>
+        <v>63.8</v>
       </c>
       <c r="G50" s="2">
-        <v>27.80075321</v>
+        <v>24.705231349999998</v>
       </c>
       <c r="H50" s="2">
-        <v>0.21739130400000001</v>
+        <v>0.28056426299999998</v>
       </c>
       <c r="I50" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="J50" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K50" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="L50" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="M50" s="2">
-        <v>6.93</v>
+        <v>7.77</v>
       </c>
       <c r="N50" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O50" s="2">
         <v>0</v>
@@ -4176,22 +4178,22 @@
         <v>120</v>
       </c>
       <c r="Q50" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R50" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="S50" s="2">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="T50" s="2">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="U50" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V50" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W50" s="2">
         <v>2</v>
@@ -4199,70 +4201,70 @@
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>2400788</v>
+        <v>2401195</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D51" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E51" s="2">
-        <v>160.69999999999999</v>
+        <v>151.5</v>
       </c>
       <c r="F51" s="2">
-        <v>63.8</v>
+        <v>68.3</v>
       </c>
       <c r="G51" s="2">
-        <v>24.705231349999998</v>
+        <v>29.757431189999998</v>
       </c>
       <c r="H51" s="2">
-        <v>0.28056426299999998</v>
+        <v>0.33967789199999998</v>
       </c>
       <c r="I51" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="J51" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K51" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L51" s="2">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="M51" s="2">
-        <v>7.77</v>
+        <v>8.58</v>
       </c>
       <c r="N51" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O51" s="2">
         <v>0</v>
       </c>
       <c r="P51" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Q51" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="R51" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="S51" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T51" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="U51" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V51" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W51" s="2">
         <v>2</v>
@@ -4270,73 +4272,73 @@
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>2401195</v>
+        <v>2401295</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" s="2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2">
-        <v>151.5</v>
+        <v>142</v>
       </c>
       <c r="F52" s="2">
-        <v>68.3</v>
+        <v>62</v>
       </c>
       <c r="G52" s="2">
-        <v>29.757431189999998</v>
+        <v>30.747867490000001</v>
       </c>
       <c r="H52" s="2">
-        <v>0.33967789199999998</v>
+        <v>0.44193548399999999</v>
       </c>
       <c r="I52" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="J52" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K52" s="2">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="L52" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M52" s="2">
-        <v>8.58</v>
+        <v>8.92</v>
       </c>
       <c r="N52" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O52" s="2">
         <v>0</v>
       </c>
       <c r="P52" s="2">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q52" s="2">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="R52" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S52" s="2">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="T52" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U52" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="V52" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W52" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:23">
@@ -4347,40 +4349,40 @@
         <v>1</v>
       </c>
       <c r="C53" s="7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D53" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E53" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G53" s="2">
-        <v>30.747867490000001</v>
+        <v>29.830309549999999</v>
       </c>
       <c r="H53" s="2">
-        <v>0.44193548399999999</v>
+        <v>0.35081967200000003</v>
       </c>
       <c r="I53" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="J53" s="2">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K53" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L53" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="M53" s="2">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="N53" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O53" s="2">
         <v>0</v>
@@ -4389,16 +4391,16 @@
         <v>115</v>
       </c>
       <c r="Q53" s="2">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="R53" s="2">
         <v>23</v>
       </c>
       <c r="S53" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T53" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="U53" s="2">
         <v>15</v>
@@ -4412,78 +4414,78 @@
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="2">
-        <v>2401295</v>
+        <v>2401534</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" s="7">
+        <v>29</v>
+      </c>
+      <c r="D54" s="2">
+        <v>81</v>
+      </c>
+      <c r="E54" s="2">
+        <v>147.5</v>
+      </c>
+      <c r="F54" s="2">
+        <v>59.2</v>
+      </c>
+      <c r="G54" s="2">
+        <v>27.21057167</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.18243243200000001</v>
+      </c>
+      <c r="I54" s="2">
+        <v>10.86</v>
+      </c>
+      <c r="J54" s="2">
+        <v>25</v>
+      </c>
+      <c r="K54" s="2">
+        <v>10</v>
+      </c>
+      <c r="L54" s="2">
+        <v>125</v>
+      </c>
+      <c r="M54" s="2">
+        <v>10.91</v>
+      </c>
+      <c r="N54" s="2">
+        <v>120</v>
+      </c>
+      <c r="O54" s="2">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2">
+        <v>120</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>-10</v>
+      </c>
+      <c r="R54" s="2">
+        <v>18</v>
+      </c>
+      <c r="S54" s="2">
         <v>30</v>
       </c>
-      <c r="D54" s="2">
-        <v>63</v>
-      </c>
-      <c r="E54" s="2">
-        <v>143</v>
-      </c>
-      <c r="F54" s="2">
-        <v>61</v>
-      </c>
-      <c r="G54" s="2">
-        <v>29.830309549999999</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0.35081967200000003</v>
-      </c>
-      <c r="I54" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="J54" s="2">
-        <v>50</v>
-      </c>
-      <c r="K54" s="2">
-        <v>47</v>
-      </c>
-      <c r="L54" s="2">
-        <v>93</v>
-      </c>
-      <c r="M54" s="2">
-        <v>8.93</v>
-      </c>
-      <c r="N54" s="2">
-        <v>110</v>
-      </c>
-      <c r="O54" s="2">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2">
-        <v>115</v>
-      </c>
-      <c r="Q54" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R54" s="2">
-        <v>23</v>
-      </c>
-      <c r="S54" s="2">
-        <v>18</v>
-      </c>
       <c r="T54" s="2">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="U54" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V54" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>2401534</v>
+        <v>2401730</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -4492,69 +4494,69 @@
         <v>29</v>
       </c>
       <c r="D55" s="2">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E55" s="2">
-        <v>147.5</v>
+        <v>160</v>
       </c>
       <c r="F55" s="2">
-        <v>59.2</v>
+        <v>56</v>
       </c>
       <c r="G55" s="2">
-        <v>27.21057167</v>
+        <v>21.875</v>
       </c>
       <c r="H55" s="2">
-        <v>0.18243243200000001</v>
+        <v>0.14464285700000001</v>
       </c>
       <c r="I55" s="2">
-        <v>10.86</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="J55" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K55" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L55" s="2">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="M55" s="2">
-        <v>10.91</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N55" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="O55" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P55" s="2">
         <v>120</v>
       </c>
       <c r="Q55" s="2">
-        <v>-10</v>
+        <v>-35</v>
       </c>
       <c r="R55" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S55" s="2">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="T55" s="2">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="U55" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V55" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>2401730</v>
+        <v>2401922</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -4563,61 +4565,61 @@
         <v>29</v>
       </c>
       <c r="D56" s="2">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2">
-        <v>160</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="F56" s="2">
-        <v>56</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="G56" s="2">
-        <v>21.875</v>
+        <v>37.568624579999998</v>
       </c>
       <c r="H56" s="2">
-        <v>0.14464285700000001</v>
+        <v>0.16598079600000001</v>
       </c>
       <c r="I56" s="2">
-        <v>39.229999999999997</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="J56" s="2">
         <v>29</v>
       </c>
       <c r="K56" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L56" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M56" s="2">
-        <v>32.799999999999997</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="N56" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="O56" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P56" s="2">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="Q56" s="2">
-        <v>-35</v>
+        <v>-15</v>
       </c>
       <c r="R56" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="S56" s="2">
+        <v>24</v>
+      </c>
+      <c r="T56" s="2">
+        <v>29</v>
+      </c>
+      <c r="U56" s="2">
         <v>12</v>
       </c>
-      <c r="T56" s="2">
-        <v>38</v>
-      </c>
-      <c r="U56" s="2">
-        <v>11</v>
-      </c>
       <c r="V56" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W56" s="2">
         <v>1</v>
@@ -4625,43 +4627,43 @@
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>2401922</v>
+        <v>2402032</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" s="7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D57" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E57" s="2">
-        <v>139.30000000000001</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="F57" s="2">
-        <v>72.900000000000006</v>
+        <v>57.3</v>
       </c>
       <c r="G57" s="2">
-        <v>37.568624579999998</v>
+        <v>25.568839749999999</v>
       </c>
       <c r="H57" s="2">
-        <v>0.16598079600000001</v>
+        <v>0.25828970299999998</v>
       </c>
       <c r="I57" s="2">
-        <v>17.829999999999998</v>
+        <v>9.26</v>
       </c>
       <c r="J57" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K57" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L57" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="M57" s="2">
-        <v>18.649999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="N57" s="2">
         <v>110</v>
@@ -4670,22 +4672,22 @@
         <v>0</v>
       </c>
       <c r="P57" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="2">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="R57" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S57" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T57" s="2">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="U57" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V57" s="2">
         <v>9</v>
@@ -4696,7 +4698,7 @@
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>2402032</v>
+        <v>2402281</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -4705,176 +4707,176 @@
         <v>31</v>
       </c>
       <c r="D58" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2">
-        <v>149.69999999999999</v>
+        <v>150</v>
       </c>
       <c r="F58" s="2">
-        <v>57.3</v>
+        <v>62</v>
       </c>
       <c r="G58" s="2">
-        <v>25.568839749999999</v>
+        <v>27.555555559999998</v>
       </c>
       <c r="H58" s="2">
-        <v>0.25828970299999998</v>
+        <v>0.20483871000000001</v>
       </c>
       <c r="I58" s="2">
-        <v>9.26</v>
+        <v>13.88</v>
       </c>
       <c r="J58" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K58" s="2">
+        <v>20</v>
+      </c>
+      <c r="L58" s="2">
+        <v>101</v>
+      </c>
+      <c r="M58" s="2">
+        <v>13.88</v>
+      </c>
+      <c r="N58" s="2">
+        <v>120</v>
+      </c>
+      <c r="O58" s="2">
+        <v>-5</v>
+      </c>
+      <c r="P58" s="2">
+        <v>130</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>-20</v>
+      </c>
+      <c r="R58" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" s="2">
         <v>26</v>
       </c>
-      <c r="L58" s="2">
-        <v>135</v>
-      </c>
-      <c r="M58" s="2">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="N58" s="2">
-        <v>110</v>
-      </c>
-      <c r="O58" s="2">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2">
-        <v>100</v>
-      </c>
-      <c r="Q58" s="2">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2">
-        <v>19</v>
-      </c>
-      <c r="S58" s="2">
-        <v>28</v>
-      </c>
       <c r="T58" s="2">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="U58" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V58" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>2402281</v>
+        <v>2403315</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D59" s="2">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E59" s="2">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="F59" s="2">
-        <v>62</v>
+        <v>92.5</v>
       </c>
       <c r="G59" s="2">
-        <v>27.555555559999998</v>
+        <v>31.633665059999998</v>
       </c>
       <c r="H59" s="2">
-        <v>0.20483871000000001</v>
+        <v>0.23243243199999999</v>
       </c>
       <c r="I59" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="J59" s="2">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K59" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L59" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M59" s="2">
-        <v>13.88</v>
+        <v>12.89</v>
       </c>
       <c r="N59" s="2">
         <v>120</v>
       </c>
       <c r="O59" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="P59" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q59" s="2">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="R59" s="2">
         <v>20</v>
       </c>
       <c r="S59" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T59" s="2">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="U59" s="2">
         <v>14</v>
       </c>
       <c r="V59" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>2403315</v>
+        <v>2403413</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D60" s="2">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E60" s="2">
-        <v>171</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="F60" s="2">
-        <v>92.5</v>
+        <v>65.2</v>
       </c>
       <c r="G60" s="2">
-        <v>31.633665059999998</v>
+        <v>28.519638310000001</v>
       </c>
       <c r="H60" s="2">
-        <v>0.23243243199999999</v>
+        <v>0.20552147200000001</v>
       </c>
       <c r="I60" s="2">
-        <v>12.89</v>
+        <v>12.39</v>
       </c>
       <c r="J60" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K60" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L60" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M60" s="2">
-        <v>12.89</v>
+        <v>12.39</v>
       </c>
       <c r="N60" s="2">
         <v>120</v>
@@ -4886,69 +4888,69 @@
         <v>120</v>
       </c>
       <c r="Q60" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R60" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S60" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="T60" s="2">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="U60" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V60" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W60" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>2403413</v>
+        <v>2403725</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D61" s="2">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E61" s="2">
-        <v>151.19999999999999</v>
+        <v>165.5</v>
       </c>
       <c r="F61" s="2">
-        <v>65.2</v>
+        <v>79</v>
       </c>
       <c r="G61" s="2">
-        <v>28.519638310000001</v>
+        <v>28.842380039999998</v>
       </c>
       <c r="H61" s="2">
-        <v>0.20552147200000001</v>
+        <v>0.20506329100000001</v>
       </c>
       <c r="I61" s="2">
-        <v>12.39</v>
+        <v>9.64</v>
       </c>
       <c r="J61" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K61" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="L61" s="2">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="M61" s="2">
-        <v>12.39</v>
+        <v>9.64</v>
       </c>
       <c r="N61" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O61" s="2">
         <v>0</v>
@@ -4957,90 +4959,90 @@
         <v>120</v>
       </c>
       <c r="Q61" s="2">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="R61" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="S61" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T61" s="2">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="U61" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V61" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W61" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>2403725</v>
+        <v>2403883</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D62" s="2">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E62" s="2">
-        <v>165.5</v>
+        <v>158.1</v>
       </c>
       <c r="F62" s="2">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G62" s="2">
-        <v>28.842380039999998</v>
+        <v>26.40463665</v>
       </c>
       <c r="H62" s="2">
-        <v>0.20506329100000001</v>
+        <v>0.192424242</v>
       </c>
       <c r="I62" s="2">
-        <v>9.64</v>
+        <v>9.93</v>
       </c>
       <c r="J62" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K62" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L62" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M62" s="2">
-        <v>9.64</v>
+        <v>9.93</v>
       </c>
       <c r="N62" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O62" s="2">
         <v>0</v>
       </c>
       <c r="P62" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q62" s="2">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="R62" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S62" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T62" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U62" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V62" s="2">
         <v>9</v>
@@ -5051,52 +5053,52 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>2403883</v>
+        <v>8811223</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D63" s="2">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E63" s="2">
-        <v>158.1</v>
+        <v>154</v>
       </c>
       <c r="F63" s="2">
-        <v>66</v>
+        <v>49.4</v>
       </c>
       <c r="G63" s="2">
-        <v>26.40463665</v>
+        <v>20.829819530000002</v>
       </c>
       <c r="H63" s="2">
-        <v>0.192424242</v>
+        <v>0.17813765200000001</v>
       </c>
       <c r="I63" s="2">
-        <v>9.93</v>
+        <v>9.11</v>
       </c>
       <c r="J63" s="2">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K63" s="2">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="L63" s="2">
+        <v>145</v>
+      </c>
+      <c r="M63" s="2">
+        <v>10.89</v>
+      </c>
+      <c r="N63" s="2">
+        <v>125</v>
+      </c>
+      <c r="O63" s="2">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2">
         <v>120</v>
-      </c>
-      <c r="M63" s="2">
-        <v>9.93</v>
-      </c>
-      <c r="N63" s="2">
-        <v>120</v>
-      </c>
-      <c r="O63" s="2">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2">
-        <v>100</v>
       </c>
       <c r="Q63" s="2">
         <v>-10</v>
@@ -5105,16 +5107,16 @@
         <v>21</v>
       </c>
       <c r="S63" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="T63" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="U63" s="2">
         <v>15</v>
       </c>
       <c r="V63" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W63" s="2">
         <v>2</v>
@@ -5122,73 +5124,73 @@
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>8811223</v>
+        <v>8852227</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" s="7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D64" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E64" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F64" s="2">
-        <v>49.4</v>
+        <v>65.5</v>
       </c>
       <c r="G64" s="2">
-        <v>20.829819530000002</v>
+        <v>28.726810230000002</v>
       </c>
       <c r="H64" s="2">
-        <v>0.17813765200000001</v>
+        <v>0.17251908399999999</v>
       </c>
       <c r="I64" s="2">
-        <v>9.11</v>
+        <v>10.27</v>
       </c>
       <c r="J64" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K64" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L64" s="2">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="M64" s="2">
-        <v>10.89</v>
+        <v>11.38</v>
       </c>
       <c r="N64" s="2">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="O64" s="2">
         <v>0</v>
       </c>
       <c r="P64" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="Q64" s="2">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="R64" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S64" s="2">
         <v>26</v>
       </c>
       <c r="T64" s="2">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="U64" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V64" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:23">
@@ -5199,37 +5201,37 @@
         <v>1</v>
       </c>
       <c r="C65" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D65" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2">
         <v>151</v>
       </c>
       <c r="F65" s="2">
-        <v>65.5</v>
+        <v>64.400000000000006</v>
       </c>
       <c r="G65" s="2">
-        <v>28.726810230000002</v>
+        <v>28.244375250000001</v>
       </c>
       <c r="H65" s="2">
-        <v>0.17251908399999999</v>
+        <v>0.189440994</v>
       </c>
       <c r="I65" s="2">
-        <v>10.27</v>
+        <v>10.63</v>
       </c>
       <c r="J65" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K65" s="2">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L65" s="2">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="M65" s="2">
-        <v>11.38</v>
+        <v>10.63</v>
       </c>
       <c r="N65" s="2">
         <v>120</v>
@@ -5238,25 +5240,25 @@
         <v>0</v>
       </c>
       <c r="P65" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q65" s="2">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="R65" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S65" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="T65" s="2">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="U65" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V65" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W65" s="2">
         <v>1</v>
@@ -5264,7 +5266,7 @@
     </row>
     <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>8852227</v>
+        <v>9005400</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -5273,206 +5275,206 @@
         <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E66" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F66" s="2">
-        <v>64.400000000000006</v>
+        <v>77.3</v>
       </c>
       <c r="G66" s="2">
-        <v>28.244375250000001</v>
+        <v>30.1953125</v>
       </c>
       <c r="H66" s="2">
-        <v>0.189440994</v>
+        <v>0.168175938</v>
       </c>
       <c r="I66" s="2">
-        <v>10.63</v>
+        <v>17.73</v>
       </c>
       <c r="J66" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K66" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L66" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M66" s="2">
-        <v>10.63</v>
+        <v>17.73</v>
       </c>
       <c r="N66" s="2">
         <v>120</v>
       </c>
       <c r="O66" s="2">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P66" s="2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Q66" s="2">
         <v>0</v>
       </c>
       <c r="R66" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S66" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T66" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U66" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V66" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>9005400</v>
+        <v>9209245</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" s="7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D67" s="2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E67" s="2">
-        <v>160</v>
+        <v>157.19999999999999</v>
       </c>
       <c r="F67" s="2">
-        <v>77.3</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="G67" s="2">
-        <v>30.1953125</v>
+        <v>28.97396552</v>
       </c>
       <c r="H67" s="2">
-        <v>0.168175938</v>
+        <v>0.17597765400000001</v>
       </c>
       <c r="I67" s="2">
-        <v>17.73</v>
+        <v>10.62</v>
       </c>
       <c r="J67" s="2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K67" s="2">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="L67" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="M67" s="2">
-        <v>17.73</v>
+        <v>10.67</v>
       </c>
       <c r="N67" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O67" s="2">
+        <v>0</v>
+      </c>
+      <c r="P67" s="2">
+        <v>130</v>
+      </c>
+      <c r="Q67" s="2">
         <v>-5</v>
       </c>
-      <c r="P67" s="2">
-        <v>110</v>
-      </c>
-      <c r="Q67" s="2">
-        <v>0</v>
-      </c>
       <c r="R67" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="S67" s="2">
         <v>14</v>
       </c>
       <c r="T67" s="2">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="U67" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V67" s="2">
         <v>10</v>
       </c>
       <c r="W67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>9209245</v>
+        <v>9301565</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" s="7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D68" s="2">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E68" s="2">
-        <v>157.19999999999999</v>
+        <v>152.5</v>
       </c>
       <c r="F68" s="2">
-        <v>71.599999999999994</v>
+        <v>78.3</v>
       </c>
       <c r="G68" s="2">
-        <v>28.97396552</v>
+        <v>33.668368719999997</v>
       </c>
       <c r="H68" s="2">
-        <v>0.17597765400000001</v>
-      </c>
-      <c r="I68" s="2">
-        <v>10.62</v>
+        <v>0.20945083</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="J68" s="2">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="K68" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L68" s="2">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="M68" s="2">
-        <v>10.67</v>
+        <v>9.0500000000000007</v>
       </c>
       <c r="N68" s="2">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="O68" s="2">
         <v>0</v>
       </c>
       <c r="P68" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q68" s="2">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="R68" s="2">
         <v>19</v>
       </c>
       <c r="S68" s="2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="T68" s="2">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="U68" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V68" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5489,66 +5491,66 @@
         <v>58</v>
       </c>
       <c r="E69" s="2">
-        <v>152.5</v>
+        <v>153</v>
       </c>
       <c r="F69" s="2">
-        <v>78.3</v>
+        <v>80.8</v>
       </c>
       <c r="G69" s="2">
-        <v>33.668368719999997</v>
+        <v>34.516638899999997</v>
       </c>
       <c r="H69" s="2">
-        <v>0.20945083</v>
+        <v>0.21534653500000001</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J69" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="K69" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L69" s="2">
         <v>127</v>
       </c>
       <c r="M69" s="2">
-        <v>9.0500000000000007</v>
+        <v>8.59</v>
       </c>
       <c r="N69" s="2">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="O69" s="2">
         <v>0</v>
       </c>
       <c r="P69" s="2">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="Q69" s="2">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="R69" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S69" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T69" s="2">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="U69" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V69" s="2">
         <v>13</v>
       </c>
       <c r="W69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>9301565</v>
+        <v>9508610</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -5557,160 +5559,97 @@
         <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E70" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F70" s="2">
-        <v>80.8</v>
+        <v>55.4</v>
       </c>
       <c r="G70" s="2">
-        <v>34.516638899999997</v>
+        <v>24.29717995</v>
       </c>
       <c r="H70" s="2">
-        <v>0.21534653500000001</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>14</v>
+        <v>0.20216606500000001</v>
+      </c>
+      <c r="I70" s="2">
+        <v>7.96</v>
       </c>
       <c r="J70" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K70" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L70" s="2">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="M70" s="2">
-        <v>8.59</v>
+        <v>8.09</v>
       </c>
       <c r="N70" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O70" s="2">
         <v>0</v>
       </c>
       <c r="P70" s="2">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="Q70" s="2">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="R70" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S70" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T70" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U70" s="2">
         <v>13</v>
       </c>
       <c r="V70" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W70" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:23">
-      <c r="A71" s="2">
-        <v>9508610</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" s="7">
-        <v>29</v>
-      </c>
-      <c r="D71" s="2">
-        <v>72</v>
-      </c>
-      <c r="E71" s="2">
-        <v>151</v>
-      </c>
-      <c r="F71" s="2">
-        <v>55.4</v>
-      </c>
-      <c r="G71" s="2">
-        <v>24.29717995</v>
-      </c>
-      <c r="H71" s="2">
-        <v>0.20216606500000001</v>
-      </c>
-      <c r="I71" s="2">
-        <v>7.96</v>
-      </c>
-      <c r="J71" s="2">
-        <v>34</v>
-      </c>
-      <c r="K71" s="2">
-        <v>17</v>
-      </c>
-      <c r="L71" s="2">
-        <v>115</v>
-      </c>
-      <c r="M71" s="2">
-        <v>8.09</v>
-      </c>
-      <c r="N71" s="2">
-        <v>125</v>
-      </c>
-      <c r="O71" s="2">
-        <v>0</v>
-      </c>
-      <c r="P71" s="2">
-        <v>120</v>
-      </c>
-      <c r="Q71" s="2">
-        <v>-15</v>
-      </c>
-      <c r="R71" s="2">
-        <v>19</v>
-      </c>
-      <c r="S71" s="2">
-        <v>28</v>
-      </c>
-      <c r="T71" s="2">
-        <v>59</v>
-      </c>
-      <c r="U71" s="2">
-        <v>13</v>
-      </c>
-      <c r="V71" s="2">
-        <v>9</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="2"/>
       <c r="W71" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:23">
       <c r="A72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
       <c r="T72" s="2"/>
-      <c r="U72" s="1"/>
       <c r="V72" s="2"/>
       <c r="W72" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:23">
@@ -5718,21 +5657,19 @@
       <c r="T73" s="2"/>
       <c r="V73" s="2"/>
       <c r="W73" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="1"/>
-      <c r="T74" s="2"/>
-      <c r="V74" s="2"/>
+      <c r="T74" s="4"/>
+      <c r="V74" s="1"/>
       <c r="W74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:23">
       <c r="A75" s="1"/>
-      <c r="T75" s="4"/>
-      <c r="V75" s="1"/>
       <c r="W75" s="2">
         <v>1</v>
       </c>
@@ -5740,18 +5677,15 @@
     <row r="76" spans="1:23">
       <c r="A76" s="1"/>
       <c r="W76" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:23">
       <c r="A77" s="1"/>
-      <c r="W77" s="2">
-        <v>2</v>
-      </c>
+      <c r="W77" s="1"/>
     </row>
     <row r="78" spans="1:23">
       <c r="A78" s="1"/>
-      <c r="W78" s="1"/>
     </row>
     <row r="79" spans="1:23">
       <c r="A79" s="1"/>
@@ -7075,9 +7009,6 @@
     </row>
     <row r="519" spans="1:1">
       <c r="A519" s="1"/>
-    </row>
-    <row r="520" spans="1:1">
-      <c r="A520" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuk\Desktop\TKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068A53A5-A7BF-45D5-AB94-C1745E4B07CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA24E51-192E-4016-A3BF-FC648D11195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
@@ -109,10 +109,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>symptoms _post</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>TUG_post</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -149,6 +145,10 @@
   </si>
   <si>
     <t>9’05</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>symptoms_post</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -603,13 +603,13 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>14</v>
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>16</v>
@@ -654,10 +654,10 @@
         <v>19</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>20</v>
@@ -666,7 +666,7 @@
         <v>21</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W1" s="1"/>
     </row>
@@ -5317,7 +5317,7 @@
         <v>0.20945083</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J69" s="2">
         <v>44</v>

--- a/main.xlsx
+++ b/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3431F5-77E1-2D4D-9459-BD0A22DFFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEEF446-4B65-3E41-BCB2-8FBFBDB1222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>

--- a/main.xlsx
+++ b/main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kanekokento/Desktop/TKA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuk\Desktop\TKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEEF446-4B65-3E41-BCB2-8FBFBDB1222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA5F470-A242-4877-B83E-A05016682B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1DB3A42A-FCFA-144D-81D8-756DBB8F2B23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,10 +112,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>symptoms _post</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>TUG_post</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -171,6 +167,10 @@
       </rPr>
       <t>_post</t>
     </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>symptoms_post</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -334,9 +334,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -374,7 +374,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -480,7 +480,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -622,7 +622,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -631,32 +631,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86FFC766-68F8-FC45-AD51-E021E5F2FD10}">
   <dimension ref="A1:X519"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="20"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.69140625" customWidth="1"/>
+    <col min="3" max="3" width="17.3046875" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.84375" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
-    <col min="16" max="16" width="22.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.69140625" customWidth="1"/>
+    <col min="16" max="16" width="22.3828125" customWidth="1"/>
+    <col min="17" max="17" width="23.69140625" customWidth="1"/>
     <col min="18" max="18" width="24" customWidth="1"/>
-    <col min="19" max="20" width="22.42578125" customWidth="1"/>
-    <col min="21" max="21" width="13.7109375" customWidth="1"/>
+    <col min="19" max="20" width="22.3828125" customWidth="1"/>
+    <col min="21" max="21" width="13.69140625" customWidth="1"/>
     <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="18.140625" customWidth="1"/>
-    <col min="24" max="24" width="26.28515625" customWidth="1"/>
+    <col min="23" max="23" width="18.15234375" customWidth="1"/>
+    <col min="24" max="24" width="26.3046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -677,7 +677,7 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>15</v>
@@ -686,7 +686,7 @@
         <v>16</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>17</v>
@@ -701,10 +701,10 @@
         <v>20</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>21</v>
@@ -713,10 +713,10 @@
         <v>22</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X1" s="2"/>
     </row>
